--- a/file/temp/ExcelTableToMarkDownSample2.xlsx
+++ b/file/temp/ExcelTableToMarkDownSample2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.HydroTools\file\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94DC7489-4B6F-4288-9376-DE771CE64F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E6ED6F-E33C-47EA-9402-75AE6B77B339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{D94F812B-BC61-4A22-9692-634766FE0D40}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="11">
   <si>
     <t>Creación de tablas en formato .md</t>
   </si>
@@ -61,106 +61,16 @@
     <t>Texto para 13 columnas</t>
   </si>
   <si>
-    <t>Descripción litológica</t>
+    <t>Descripción</t>
   </si>
   <si>
-    <t>A</t>
+    <t>Pedegosidad superficial</t>
   </si>
   <si>
-    <t>B</t>
+    <t>p</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>Aluviones y coluviones actuales</t>
-  </si>
-  <si>
-    <t>Arenas y margas</t>
-  </si>
-  <si>
-    <t>Areniscas rojas, filitas, cuarcitas y pizarras</t>
-  </si>
-  <si>
-    <t>Basaltos</t>
-  </si>
-  <si>
-    <t>Calizas recristalizadas cremas</t>
-  </si>
-  <si>
-    <t>Calizas tableadas azules</t>
-  </si>
-  <si>
-    <t>Coluvial</t>
-  </si>
-  <si>
-    <t>Conos de deyección</t>
-  </si>
-  <si>
-    <t>Cuarcitas blancas, micaesquistos plateados y gneises albíticos</t>
-  </si>
-  <si>
-    <t>Cuarcitas micaceas</t>
-  </si>
-  <si>
-    <t>Diabasas</t>
-  </si>
-  <si>
-    <t>Dolomitas negras y calizas</t>
-  </si>
-  <si>
-    <t>Filitas, cuarcitas y calcoesquistos</t>
-  </si>
-  <si>
-    <t>Glacis. Limos negros y rojos y cantos encostrados</t>
-  </si>
-  <si>
-    <t>Indiferenciado***</t>
-  </si>
-  <si>
-    <t>Limos y arcillas rojas con episodios de caliche</t>
-  </si>
-  <si>
-    <t>Margas arenosas y margas</t>
-  </si>
-  <si>
-    <t>Margas blancas</t>
-  </si>
-  <si>
-    <t>Margas grises</t>
-  </si>
-  <si>
-    <t>Margas y areníscas</t>
-  </si>
-  <si>
-    <t>Mármoles calizos y dolomíticos</t>
-  </si>
-  <si>
-    <t>Mármoles fajeados y mármoles blancos y crema</t>
-  </si>
-  <si>
-    <t>Micacitas con granates</t>
-  </si>
-  <si>
-    <t>Micaesquistos y cuarcitas</t>
-  </si>
-  <si>
-    <t>Pizarras micaceas y micacitas</t>
-  </si>
-  <si>
-    <t>Terrazas</t>
-  </si>
-  <si>
-    <t>Yesos</t>
-  </si>
-  <si>
-    <t>Conteo</t>
-  </si>
-  <si>
-    <t>✓</t>
+    <t>Abundante</t>
   </si>
 </sst>
 </file>
@@ -1062,9 +972,9 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="42.5703125" style="1" customWidth="1"/>
-    <col min="3" max="6" width="8.28515625" style="1" customWidth="1"/>
-    <col min="7" max="14" width="4.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.92578125" style="1" customWidth="1"/>
+    <col min="4" max="14" width="3.42578125" style="1" customWidth="1"/>
     <col min="15" max="15" width="2.7109375" style="1" customWidth="1"/>
     <col min="16" max="20" width="74.140625" style="1" customWidth="1"/>
     <col min="21" max="16384" width="9.140625" style="1"/>
@@ -1105,20 +1015,14 @@
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -1130,23 +1034,23 @@
       <c r="O3" s="4"/>
       <c r="P3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," |")</f>
-        <v>| Descripción litológica | A |</v>
+        <v>| Pedegosidad superficial | Descripción |</v>
       </c>
       <c r="Q3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," |")</f>
-        <v>| Descripción litológica | A | B |</v>
+        <v>| Pedegosidad superficial | Descripción |  |</v>
       </c>
       <c r="R3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |")</f>
-        <v>| Descripción litológica | A | B | C |</v>
+        <v>| Pedegosidad superficial | Descripción |  |  |</v>
       </c>
       <c r="S3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |")</f>
-        <v>| Descripción litológica | A | B | C |D |</v>
+        <v>| Pedegosidad superficial | Descripción |  |  | |</v>
       </c>
       <c r="T3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |",G3," |",H3," |",I3," |",J3," |",K3," |",L3," |",M3," |",N3," |")</f>
-        <v>| Descripción litológica | A | B | C |D | | | | | | | | |</v>
+        <v>| Pedegosidad superficial | Descripción |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="4" spans="2:20" x14ac:dyDescent="0.55000000000000004">
@@ -1213,10 +1117,10 @@
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -1232,33 +1136,29 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B5," | ",C5," |")</f>
-        <v>| Aluviones y coluviones actuales | ✓ |</v>
+        <v>| p | Abundante |</v>
       </c>
       <c r="Q5" s="5" t="str">
         <f t="shared" ref="Q5:Q24" si="0">_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," |")</f>
-        <v>| Aluviones y coluviones actuales | ✓ |  |</v>
+        <v>| p | Abundante |  |</v>
       </c>
       <c r="R5" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," | ",E5," |")</f>
-        <v>| Aluviones y coluviones actuales | ✓ |  |  |</v>
+        <v>| p | Abundante |  |  |</v>
       </c>
       <c r="S5" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," | ",E5," |",F5," |")</f>
-        <v>| Aluviones y coluviones actuales | ✓ |  |  | |</v>
+        <v>| p | Abundante |  |  | |</v>
       </c>
       <c r="T5" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," | ",E5," |",F5," |",G5," |",H5," |",I5," |",J5," |",K5," |",L5," |",M5," |",N5," |")</f>
-        <v>| Aluviones y coluviones actuales | ✓ |  |  | | | | | | | | | |</v>
+        <v>| p | Abundante |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-      <c r="D6" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -1272,34 +1172,30 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5" t="str">
         <f t="shared" ref="P6:P24" si="1">_xlfn.CONCAT("| ",B6," | ",C6," |")</f>
-        <v>| Arenas y margas |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q6" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| Arenas y margas |  | ✓ |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R6" s="5" t="str">
         <f t="shared" ref="R6:R67" si="2">_xlfn.CONCAT("| ",B6," | ",C6," | ",D6," | ",E6," |")</f>
-        <v>| Arenas y margas |  | ✓ |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S6" s="5" t="str">
         <f t="shared" ref="S6:S69" si="3">_xlfn.CONCAT("| ",B6," | ",C6," | ",D6," | ",E6," |",F6," |")</f>
-        <v>| Arenas y margas |  | ✓ |  | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T6" s="5" t="str">
         <f t="shared" ref="T6:T69" si="4">_xlfn.CONCAT("| ",B6," | ",C6," | ",D6," | ",E6," |",F6," |",G6," |",H6," |",I6," |",J6," |",K6," |",L6," |",M6," |",N6," |")</f>
-        <v>| Arenas y margas |  | ✓ |  | | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -1312,35 +1208,31 @@
       <c r="O7" s="5"/>
       <c r="P7" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| Areniscas rojas, filitas, cuarcitas y pizarras |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q7" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| Areniscas rojas, filitas, cuarcitas y pizarras |  |  |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R7" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Areniscas rojas, filitas, cuarcitas y pizarras |  |  | ✓ |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S7" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Areniscas rojas, filitas, cuarcitas y pizarras |  |  | ✓ | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T7" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Areniscas rojas, filitas, cuarcitas y pizarras |  |  | ✓ | | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -1352,33 +1244,29 @@
       <c r="O8" s="5"/>
       <c r="P8" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| Basaltos |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q8" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| Basaltos |  |  |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R8" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Basaltos |  |  |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S8" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Basaltos |  |  |  |✓ |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T8" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Basaltos |  |  |  |✓ | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="5" t="s">
-        <v>16</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="5"/>
       <c r="C9" s="5"/>
-      <c r="D9" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
@@ -1392,33 +1280,29 @@
       <c r="O9" s="5"/>
       <c r="P9" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| Calizas recristalizadas cremas |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q9" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| Calizas recristalizadas cremas |  | ✓ |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R9" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Calizas recristalizadas cremas |  | ✓ |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S9" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Calizas recristalizadas cremas |  | ✓ |  | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T9" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Calizas recristalizadas cremas |  | ✓ |  | | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="5" t="s">
-        <v>17</v>
-      </c>
+      <c r="B10" s="5"/>
       <c r="C10" s="5"/>
-      <c r="D10" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -1432,32 +1316,28 @@
       <c r="O10" s="5"/>
       <c r="P10" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| Calizas tableadas azules |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q10" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| Calizas tableadas azules |  | ✓ |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R10" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Calizas tableadas azules |  | ✓ |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S10" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Calizas tableadas azules |  | ✓ |  | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T10" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Calizas tableadas azules |  | ✓ |  | | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -1472,32 +1352,28 @@
       <c r="O11" s="5"/>
       <c r="P11" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| Coluvial | ✓ |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q11" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| Coluvial | ✓ |  |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R11" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Coluvial | ✓ |  |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S11" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Coluvial | ✓ |  |  | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T11" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Coluvial | ✓ |  |  | | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -1512,33 +1388,29 @@
       <c r="O12" s="5"/>
       <c r="P12" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| Conos de deyección | ✓ |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q12" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| Conos de deyección | ✓ |  |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R12" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Conos de deyección | ✓ |  |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S12" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Conos de deyección | ✓ |  |  | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T12" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Conos de deyección | ✓ |  |  | | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="13" spans="2:20" ht="30.75" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="5" t="s">
-        <v>20</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="5"/>
       <c r="C13" s="5"/>
-      <c r="D13" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -1552,35 +1424,31 @@
       <c r="O13" s="5"/>
       <c r="P13" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| Cuarcitas blancas, micaesquistos plateados y gneises albíticos |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q13" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| Cuarcitas blancas, micaesquistos plateados y gneises albíticos |  | ✓ |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R13" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Cuarcitas blancas, micaesquistos plateados y gneises albíticos |  | ✓ |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S13" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Cuarcitas blancas, micaesquistos plateados y gneises albíticos |  | ✓ |  | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T13" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Cuarcitas blancas, micaesquistos plateados y gneises albíticos |  | ✓ |  | | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
-      <c r="F14" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
@@ -1592,35 +1460,31 @@
       <c r="O14" s="5"/>
       <c r="P14" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| Cuarcitas micaceas |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q14" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| Cuarcitas micaceas |  |  |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R14" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Cuarcitas micaceas |  |  |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S14" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Cuarcitas micaceas |  |  |  |✓ |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T14" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Cuarcitas micaceas |  |  |  |✓ | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
@@ -1632,33 +1496,29 @@
       <c r="O15" s="5"/>
       <c r="P15" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| Diabasas |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q15" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| Diabasas |  |  |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R15" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Diabasas |  |  |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S15" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Diabasas |  |  |  |✓ |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T15" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Diabasas |  |  |  |✓ | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="B16" s="5"/>
       <c r="C16" s="5"/>
-      <c r="D16" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -1672,35 +1532,31 @@
       <c r="O16" s="5"/>
       <c r="P16" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| Dolomitas negras y calizas |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q16" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| Dolomitas negras y calizas |  | ✓ |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R16" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Dolomitas negras y calizas |  | ✓ |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S16" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Dolomitas negras y calizas |  | ✓ |  | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T16" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Dolomitas negras y calizas |  | ✓ |  | | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="5" t="s">
-        <v>24</v>
-      </c>
+      <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
-      <c r="F17" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
@@ -1712,34 +1568,30 @@
       <c r="O17" s="5"/>
       <c r="P17" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| Filitas, cuarcitas y calcoesquistos |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q17" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| Filitas, cuarcitas y calcoesquistos |  |  |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R17" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Filitas, cuarcitas y calcoesquistos |  |  |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S17" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Filitas, cuarcitas y calcoesquistos |  |  |  |✓ |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T17" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Filitas, cuarcitas y calcoesquistos |  |  |  |✓ | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="5" t="s">
-        <v>25</v>
-      </c>
+      <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
-      <c r="E18" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
@@ -1752,34 +1604,30 @@
       <c r="O18" s="5"/>
       <c r="P18" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| Glacis. Limos negros y rojos y cantos encostrados |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q18" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| Glacis. Limos negros y rojos y cantos encostrados |  |  |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R18" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Glacis. Limos negros y rojos y cantos encostrados |  |  | ✓ |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S18" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Glacis. Limos negros y rojos y cantos encostrados |  |  | ✓ | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T18" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Glacis. Limos negros y rojos y cantos encostrados |  |  | ✓ | | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="5" t="s">
-        <v>26</v>
-      </c>
+      <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
-      <c r="E19" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -1792,34 +1640,30 @@
       <c r="O19" s="5"/>
       <c r="P19" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| Indiferenciado*** |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q19" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| Indiferenciado*** |  |  |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R19" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Indiferenciado*** |  |  | ✓ |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S19" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Indiferenciado*** |  |  | ✓ | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T19" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Indiferenciado*** |  |  | ✓ | | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="5" t="s">
-        <v>27</v>
-      </c>
+      <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
-      <c r="E20" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -1832,34 +1676,30 @@
       <c r="O20" s="5"/>
       <c r="P20" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| Limos y arcillas rojas con episodios de caliche |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q20" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| Limos y arcillas rojas con episodios de caliche |  |  |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R20" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Limos y arcillas rojas con episodios de caliche |  |  | ✓ |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S20" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Limos y arcillas rojas con episodios de caliche |  |  | ✓ | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T20" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Limos y arcillas rojas con episodios de caliche |  |  | ✓ | | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
-      <c r="E21" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
@@ -1872,35 +1712,31 @@
       <c r="O21" s="5"/>
       <c r="P21" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| Margas arenosas y margas |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q21" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| Margas arenosas y margas |  |  |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R21" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Margas arenosas y margas |  |  | ✓ |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S21" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Margas arenosas y margas |  |  | ✓ | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T21" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Margas arenosas y margas |  |  | ✓ | | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
-      <c r="F22" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -1912,35 +1748,31 @@
       <c r="O22" s="5"/>
       <c r="P22" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| Margas blancas |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q22" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| Margas blancas |  |  |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R22" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Margas blancas |  |  |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S22" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Margas blancas |  |  |  |✓ |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T22" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Margas blancas |  |  |  |✓ | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="5" t="s">
-        <v>30</v>
-      </c>
+      <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
-      <c r="F23" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
@@ -1952,33 +1784,29 @@
       <c r="O23" s="5"/>
       <c r="P23" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| Margas grises |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q23" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| Margas grises |  |  |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Margas grises |  |  |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S23" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Margas grises |  |  |  |✓ |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T23" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Margas grises |  |  |  |✓ | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -1992,34 +1820,30 @@
       <c r="O24" s="5"/>
       <c r="P24" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| Margas y areníscas |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q24" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| Margas y areníscas |  | ✓ |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R24" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Margas y areníscas |  | ✓ |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S24" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Margas y areníscas |  | ✓ |  | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T24" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Margas y areníscas |  | ✓ |  | | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="5" t="s">
-        <v>32</v>
-      </c>
+      <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
-      <c r="E25" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
@@ -2032,34 +1856,30 @@
       <c r="O25" s="4"/>
       <c r="P25" s="5" t="str">
         <f t="shared" ref="P25:P88" si="5">_xlfn.CONCAT("| ",B25," | ",C25," |")</f>
-        <v>| Mármoles calizos y dolomíticos |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q25" s="5" t="str">
         <f t="shared" ref="Q25:Q88" si="6">_xlfn.CONCAT("| ",B25," | ",C25," | ",D25," |")</f>
-        <v>| Mármoles calizos y dolomíticos |  |  |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R25" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Mármoles calizos y dolomíticos |  |  | ✓ |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S25" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Mármoles calizos y dolomíticos |  |  | ✓ | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T25" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Mármoles calizos y dolomíticos |  |  | ✓ | | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="4" t="s">
-        <v>33</v>
-      </c>
+      <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
@@ -2072,34 +1892,30 @@
       <c r="O26" s="4"/>
       <c r="P26" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| Mármoles fajeados y mármoles blancos y crema |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q26" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| Mármoles fajeados y mármoles blancos y crema |  |  |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R26" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Mármoles fajeados y mármoles blancos y crema |  |  | ✓ |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S26" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Mármoles fajeados y mármoles blancos y crema |  |  | ✓ | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T26" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Mármoles fajeados y mármoles blancos y crema |  |  | ✓ | | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
-      <c r="E27" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
@@ -2112,34 +1928,30 @@
       <c r="O27" s="4"/>
       <c r="P27" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| Micacitas con granates |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q27" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| Micacitas con granates |  |  |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R27" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Micacitas con granates |  |  | ✓ |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S27" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Micacitas con granates |  |  | ✓ | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T27" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Micacitas con granates |  |  | ✓ | | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="4" t="s">
-        <v>35</v>
-      </c>
+      <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
-      <c r="E28" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
@@ -2152,35 +1964,31 @@
       <c r="O28" s="4"/>
       <c r="P28" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| Micaesquistos y cuarcitas |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q28" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| Micaesquistos y cuarcitas |  |  |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R28" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Micaesquistos y cuarcitas |  |  | ✓ |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S28" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Micaesquistos y cuarcitas |  |  | ✓ | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T28" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Micaesquistos y cuarcitas |  |  | ✓ | | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
-      <c r="F29" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
@@ -2192,33 +2000,29 @@
       <c r="O29" s="4"/>
       <c r="P29" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| Pizarras micaceas y micacitas |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q29" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| Pizarras micaceas y micacitas |  |  |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R29" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Pizarras micaceas y micacitas |  |  |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S29" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Pizarras micaceas y micacitas |  |  |  |✓ |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T29" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Pizarras micaceas y micacitas |  |  |  |✓ | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="B30" s="4"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
@@ -2232,34 +2036,30 @@
       <c r="O30" s="4"/>
       <c r="P30" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| Terrazas |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q30" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| Terrazas |  | ✓ |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R30" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Terrazas |  | ✓ |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S30" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Terrazas |  | ✓ |  | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T30" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Terrazas |  | ✓ |  | | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="4" t="s">
-        <v>38</v>
-      </c>
+      <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
-      <c r="E31" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
@@ -2272,41 +2072,31 @@
       <c r="O31" s="4"/>
       <c r="P31" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| Yesos |  |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q31" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| Yesos |  |  |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R31" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Yesos |  |  | ✓ |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S31" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Yesos |  |  | ✓ | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T31" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Yesos |  |  | ✓ | | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="4">
-        <v>3</v>
-      </c>
-      <c r="D32" s="4">
-        <v>7</v>
-      </c>
-      <c r="E32" s="4">
-        <v>10</v>
-      </c>
-      <c r="F32" s="4">
-        <v>7</v>
-      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -2318,23 +2108,23 @@
       <c r="O32" s="4"/>
       <c r="P32" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| Conteo | 3 |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q32" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| Conteo | 3 | 7 |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R32" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| Conteo | 3 | 7 | 10 |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S32" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Conteo | 3 | 7 | 10 |7 |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T32" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| Conteo | 3 | 7 | 10 |7 | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.55000000000000004">

--- a/file/temp/ExcelTableToMarkDownSample2.xlsx
+++ b/file/temp/ExcelTableToMarkDownSample2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.HydroTools\file\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87420776-12CE-4D45-BAAB-5BDBB8F828A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEE199C-2A22-45F4-9BFB-9B831CF28A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{D94F812B-BC61-4A22-9692-634766FE0D40}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="96">
   <si>
     <t>Creación de tablas en formato .md</t>
   </si>
@@ -103,9 +103,6 @@
     <t>Unique</t>
   </si>
   <si>
-    <t>CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type.</t>
-  </si>
-  <si>
     <t>Fair condition (grass cover 50% to 75%)</t>
   </si>
   <si>
@@ -139,9 +136,6 @@
     <t>Natural desert landscaping (pervious areas only)</t>
   </si>
   <si>
-    <t>Composite CN's for natural desert landscaping should be computed using figures 2-3 or 2-4 based on the impervious area percentage (CN = 98) and the pervious area CN. The pervious area CN's are assumed equivalent to desert shrub in poor hydrologic condition.</t>
-  </si>
-  <si>
     <t>Artificial desert landscaping (impervious weed barrier, desert shrub with 1- to 2-inch sand or gravel mulch and basin borders)</t>
   </si>
   <si>
@@ -151,9 +145,6 @@
     <t>Commercial and business. Average percent impervious area: 85</t>
   </si>
   <si>
-    <t>The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.</t>
-  </si>
-  <si>
     <t>Industrial. Average percent impervious area: 72</t>
   </si>
   <si>
@@ -184,9 +175,6 @@
     <t>Newly graded areas (pervious areas only, no vegetation)</t>
   </si>
   <si>
-    <t>Composite CN's to use for the design of temporary measures during grading and construction should be computed using figure 2-3 or 2-4, based on the degree of development (imperviousness area percentage) and the CN's for the newly graded pervious areas.</t>
-  </si>
-  <si>
     <t>Cultivated agricultural lands</t>
   </si>
   <si>
@@ -202,15 +190,9 @@
     <t>Poor</t>
   </si>
   <si>
-    <t>Factors impair infiltration and tend to increase runoff.</t>
-  </si>
-  <si>
     <t>Good</t>
   </si>
   <si>
-    <t>Factors encourage average and better than average infiltration and tend to decrease runoff.</t>
-  </si>
-  <si>
     <t>Row crops</t>
   </si>
   <si>
@@ -247,42 +229,18 @@
     <t>Fair</t>
   </si>
   <si>
-    <t>50 to 75% ground cover and not heavily grazed.</t>
-  </si>
-  <si>
-    <t>&gt;75% ground cover and lightly or only occasionally grazed.</t>
-  </si>
-  <si>
     <t>Meadow – continuous grass, protected from grazing and generally mowed for hay</t>
   </si>
   <si>
     <t>Brush – brush-weed mixture with brush the major element</t>
   </si>
   <si>
-    <t>50 to 75% ground cover.</t>
-  </si>
-  <si>
-    <t>&gt;75% ground cover. Actual curve number is less than 30; use CN=30 for runoff computations.</t>
-  </si>
-  <si>
     <t>Woods – grass combination (orchard or tree farm)</t>
   </si>
   <si>
-    <t>CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture.</t>
-  </si>
-  <si>
     <t>Woods</t>
   </si>
   <si>
-    <t>Forest litter, small trees, and brush are destroyed by heavy grazing or regular burning.</t>
-  </si>
-  <si>
-    <t>Woods are grazed but not burned, and some forest litter covers the soil.</t>
-  </si>
-  <si>
-    <t>Woods are protected from grazing, and litter and brush adequately cover the soil. Actual curve number is less than 30; use CN=30 for runoff computations.</t>
-  </si>
-  <si>
     <t>Farmsteads – buildings, lanes, driveways, surrounding lots</t>
   </si>
   <si>
@@ -292,18 +250,9 @@
     <t>Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element</t>
   </si>
   <si>
-    <t>30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.</t>
-  </si>
-  <si>
-    <t>&gt;70% ground cover.</t>
-  </si>
-  <si>
     <t>Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush</t>
   </si>
   <si>
-    <t>&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub.</t>
-  </si>
-  <si>
     <t>Pinyon-juniper – pinyon, juniper, or both; grass understory</t>
   </si>
   <si>
@@ -319,10 +268,64 @@
     <t>Water body</t>
   </si>
   <si>
-    <t>rcfdtools</t>
-  </si>
-  <si>
     <t>Texto para 10 columnas</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type.&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;Composite CN's for natural desert landscaping should be computed using figures 2-3 or 2-4 based on the impervious area percentage (CN = 98) and the pervious area CN. The pervious area CN's are assumed equivalent to desert shrub in poor hydrologic condition.&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;Composite CN's to use for the design of temporary measures during grading and construction should be computed using figure 2-3 or 2-4, based on the degree of development (imperviousness area percentage) and the CN's for the newly graded pervious areas.&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;50 to 75% ground cover and not heavily grazed.&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;&gt;75% ground cover and lightly or only occasionally grazed.&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;50 to 75% ground cover.&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;&gt;75% ground cover. Actual curve number is less than 30; use CN=30 for runoff computations.&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture.&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;Forest litter, small trees, and brush are destroyed by heavy grazing or regular burning.&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;Woods are grazed but not burned, and some forest litter covers the soil.&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;Woods are protected from grazing, and litter and brush adequately cover the soil. Actual curve number is less than 30; use CN=30 for runoff computations.&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;&gt;70% ground cover.&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt;</t>
+  </si>
+  <si>
+    <t>&lt;sub&gt;rcfdtools&lt;/sub&gt;</t>
   </si>
 </sst>
 </file>
@@ -1221,7 +1224,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B2E19A4-40DE-42A8-B3E2-A2516218588C}">
   <dimension ref="B2:U103"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.640625" style="1" customWidth="1"/>
@@ -1238,7 +1241,7 @@
     <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1268,13 +1271,13 @@
         <v>5</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="U2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
@@ -1334,7 +1337,7 @@
         <v>| CNCode | Zone | CoverType | Treatment |HydroCond |HydroDesc |CNA |CNB |CNC |CND | | | |</v>
       </c>
     </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
@@ -1400,7 +1403,7 @@
         <v>| --- | --- | --- | --- |--- |--- |--- |--- |--- |--- |--- |--- |--- |</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="123" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -1417,7 +1420,7 @@
         <v>20</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="H5" s="5">
         <v>68</v>
@@ -1453,14 +1456,14 @@
       </c>
       <c r="T5" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 1 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Poor condition (grass cover &lt; 50%) |Unique |CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type. |68 |79 |86 |89 |</v>
+        <v>| 1 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Poor condition (grass cover &lt; 50%) |Unique |&lt;sub&gt;CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type.&lt;/sub&gt; |68 |79 |86 |89 |</v>
       </c>
       <c r="U5" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," | ",E5," |",F5," |",G5," |",H5," |",I5," |",J5," |",K5," |",L5," |",M5," |",N5," |")</f>
-        <v>| 1 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Poor condition (grass cover &lt; 50%) |Unique |CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type. |68 |79 |86 |89 | | | |</v>
-      </c>
-    </row>
-    <row r="6" spans="2:21" ht="123" x14ac:dyDescent="0.55000000000000004">
+        <v>| 1 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Poor condition (grass cover &lt; 50%) |Unique |&lt;sub&gt;CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type.&lt;/sub&gt; |68 |79 |86 |89 | | | |</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="5">
         <v>2</v>
       </c>
@@ -1471,13 +1474,13 @@
         <v>18</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="H6" s="5">
         <v>49</v>
@@ -1513,14 +1516,14 @@
       </c>
       <c r="T6" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 2 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Fair condition (grass cover 50% to 75%) |Unique |CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type. |49 |69 |79 |84 |</v>
+        <v>| 2 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Fair condition (grass cover 50% to 75%) |Unique |&lt;sub&gt;CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type.&lt;/sub&gt; |49 |69 |79 |84 |</v>
       </c>
       <c r="U6" s="5" t="str">
-        <f t="shared" ref="T6:U69" si="5">_xlfn.CONCAT("| ",B6," | ",C6," | ",D6," | ",E6," |",F6," |",G6," |",H6," |",I6," |",J6," |",K6," |",L6," |",M6," |",N6," |")</f>
-        <v>| 2 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Fair condition (grass cover 50% to 75%) |Unique |CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type. |49 |69 |79 |84 | | | |</v>
-      </c>
-    </row>
-    <row r="7" spans="2:21" ht="123" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" ref="U6:U69" si="5">_xlfn.CONCAT("| ",B6," | ",C6," | ",D6," | ",E6," |",F6," |",G6," |",H6," |",I6," |",J6," |",K6," |",L6," |",M6," |",N6," |")</f>
+        <v>| 2 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Fair condition (grass cover 50% to 75%) |Unique |&lt;sub&gt;CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type.&lt;/sub&gt; |49 |69 |79 |84 | | | |</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -1531,13 +1534,13 @@
         <v>18</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="H7" s="5">
         <v>39</v>
@@ -1573,14 +1576,14 @@
       </c>
       <c r="T7" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 3 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Good condition (grass cover &gt; 75%) |Unique |CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type. |39 |61 |74 |80 |</v>
+        <v>| 3 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Good condition (grass cover &gt; 75%) |Unique |&lt;sub&gt;CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type.&lt;/sub&gt; |39 |61 |74 |80 |</v>
       </c>
       <c r="U7" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 3 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Good condition (grass cover &gt; 75%) |Unique |CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type. |39 |61 |74 |80 | | | |</v>
-      </c>
-    </row>
-    <row r="8" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+        <v>| 3 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Good condition (grass cover &gt; 75%) |Unique |&lt;sub&gt;CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type.&lt;/sub&gt; |39 |61 |74 |80 | | | |</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="5">
         <v>4</v>
       </c>
@@ -1588,15 +1591,17 @@
         <v>17</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="5"/>
+      <c r="G8" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H8" s="5">
         <v>98</v>
       </c>
@@ -1631,14 +1636,14 @@
       </c>
       <c r="T8" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 4 | Urban area | Fully developed urban areas - Impervious areas | Paved parking lots, roofs, driveways, etc |Unique | |98 |98 |98 |98 |</v>
+        <v>| 4 | Urban area | Fully developed urban areas - Impervious areas | Paved parking lots, roofs, driveways, etc |Unique |&lt;sub&gt;&lt;/sub&gt; |98 |98 |98 |98 |</v>
       </c>
       <c r="U8" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 4 | Urban area | Fully developed urban areas - Impervious areas | Paved parking lots, roofs, driveways, etc |Unique | |98 |98 |98 |98 | | | |</v>
-      </c>
-    </row>
-    <row r="9" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+        <v>| 4 | Urban area | Fully developed urban areas - Impervious areas | Paved parking lots, roofs, driveways, etc |Unique |&lt;sub&gt;&lt;/sub&gt; |98 |98 |98 |98 | | | |</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -1646,15 +1651,17 @@
         <v>17</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>27</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H9" s="5">
         <v>98</v>
       </c>
@@ -1689,14 +1696,14 @@
       </c>
       <c r="T9" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 5 | Urban area | Fully developed urban areas - Streets and roads | Paved; curbs and storm sewers |Unique | |98 |98 |98 |98 |</v>
+        <v>| 5 | Urban area | Fully developed urban areas - Streets and roads | Paved; curbs and storm sewers |Unique |&lt;sub&gt;&lt;/sub&gt; |98 |98 |98 |98 |</v>
       </c>
       <c r="U9" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 5 | Urban area | Fully developed urban areas - Streets and roads | Paved; curbs and storm sewers |Unique | |98 |98 |98 |98 | | | |</v>
-      </c>
-    </row>
-    <row r="10" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+        <v>| 5 | Urban area | Fully developed urban areas - Streets and roads | Paved; curbs and storm sewers |Unique |&lt;sub&gt;&lt;/sub&gt; |98 |98 |98 |98 | | | |</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="5">
         <v>6</v>
       </c>
@@ -1704,15 +1711,17 @@
         <v>17</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="5"/>
+      <c r="G10" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H10" s="5">
         <v>83</v>
       </c>
@@ -1747,14 +1756,14 @@
       </c>
       <c r="T10" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 6 | Urban area | Fully developed urban areas - Streets and roads | Paved; open ditches (including right-of-way) |Unique | |83 |89 |92 |93 |</v>
+        <v>| 6 | Urban area | Fully developed urban areas - Streets and roads | Paved; open ditches (including right-of-way) |Unique |&lt;sub&gt;&lt;/sub&gt; |83 |89 |92 |93 |</v>
       </c>
       <c r="U10" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 6 | Urban area | Fully developed urban areas - Streets and roads | Paved; open ditches (including right-of-way) |Unique | |83 |89 |92 |93 | | | |</v>
-      </c>
-    </row>
-    <row r="11" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+        <v>| 6 | Urban area | Fully developed urban areas - Streets and roads | Paved; open ditches (including right-of-way) |Unique |&lt;sub&gt;&lt;/sub&gt; |83 |89 |92 |93 | | | |</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="5">
         <v>7</v>
       </c>
@@ -1762,15 +1771,17 @@
         <v>17</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="5"/>
+      <c r="G11" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H11" s="5">
         <v>76</v>
       </c>
@@ -1805,14 +1816,14 @@
       </c>
       <c r="T11" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 7 | Urban area | Fully developed urban areas - Streets and roads | Gravel (including right-of-way) |Unique | |76 |85 |89 |91 |</v>
+        <v>| 7 | Urban area | Fully developed urban areas - Streets and roads | Gravel (including right-of-way) |Unique |&lt;sub&gt;&lt;/sub&gt; |76 |85 |89 |91 |</v>
       </c>
       <c r="U11" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 7 | Urban area | Fully developed urban areas - Streets and roads | Gravel (including right-of-way) |Unique | |76 |85 |89 |91 | | | |</v>
-      </c>
-    </row>
-    <row r="12" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+        <v>| 7 | Urban area | Fully developed urban areas - Streets and roads | Gravel (including right-of-way) |Unique |&lt;sub&gt;&lt;/sub&gt; |76 |85 |89 |91 | | | |</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="5">
         <v>8</v>
       </c>
@@ -1820,15 +1831,17 @@
         <v>17</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="5"/>
+      <c r="G12" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H12" s="5">
         <v>72</v>
       </c>
@@ -1863,14 +1876,14 @@
       </c>
       <c r="T12" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 8 | Urban area | Fully developed urban areas - Streets and roads | Dirt (including right-of-way) |Unique | |72 |82 |87 |89 |</v>
+        <v>| 8 | Urban area | Fully developed urban areas - Streets and roads | Dirt (including right-of-way) |Unique |&lt;sub&gt;&lt;/sub&gt; |72 |82 |87 |89 |</v>
       </c>
       <c r="U12" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 8 | Urban area | Fully developed urban areas - Streets and roads | Dirt (including right-of-way) |Unique | |72 |82 |87 |89 | | | |</v>
-      </c>
-    </row>
-    <row r="13" spans="2:21" ht="230.65" x14ac:dyDescent="0.55000000000000004">
+        <v>| 8 | Urban area | Fully developed urban areas - Streets and roads | Dirt (including right-of-way) |Unique |&lt;sub&gt;&lt;/sub&gt; |72 |82 |87 |89 | | | |</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="5">
         <v>9</v>
       </c>
@@ -1878,16 +1891,16 @@
         <v>17</v>
       </c>
       <c r="D13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="H13" s="5">
         <v>63</v>
@@ -1923,14 +1936,14 @@
       </c>
       <c r="T13" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 9 | Urban area | Fully developed urban areas - Western desert urban areas | Natural desert landscaping (pervious areas only) |Unique |Composite CN's for natural desert landscaping should be computed using figures 2-3 or 2-4 based on the impervious area percentage (CN = 98) and the pervious area CN. The pervious area CN's are assumed equivalent to desert shrub in poor hydrologic condition. |63 |77 |85 |88 |</v>
+        <v>| 9 | Urban area | Fully developed urban areas - Western desert urban areas | Natural desert landscaping (pervious areas only) |Unique |&lt;sub&gt;Composite CN's for natural desert landscaping should be computed using figures 2-3 or 2-4 based on the impervious area percentage (CN = 98) and the pervious area CN. The pervious area CN's are assumed equivalent to desert shrub in poor hydrologic condition.&lt;/sub&gt; |63 |77 |85 |88 |</v>
       </c>
       <c r="U13" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 9 | Urban area | Fully developed urban areas - Western desert urban areas | Natural desert landscaping (pervious areas only) |Unique |Composite CN's for natural desert landscaping should be computed using figures 2-3 or 2-4 based on the impervious area percentage (CN = 98) and the pervious area CN. The pervious area CN's are assumed equivalent to desert shrub in poor hydrologic condition. |63 |77 |85 |88 | | | |</v>
-      </c>
-    </row>
-    <row r="14" spans="2:21" ht="107.65" x14ac:dyDescent="0.55000000000000004">
+        <v>| 9 | Urban area | Fully developed urban areas - Western desert urban areas | Natural desert landscaping (pervious areas only) |Unique |&lt;sub&gt;Composite CN's for natural desert landscaping should be computed using figures 2-3 or 2-4 based on the impervious area percentage (CN = 98) and the pervious area CN. The pervious area CN's are assumed equivalent to desert shrub in poor hydrologic condition.&lt;/sub&gt; |63 |77 |85 |88 | | | |</v>
+      </c>
+    </row>
+    <row r="14" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="5">
         <v>10</v>
       </c>
@@ -1938,15 +1951,17 @@
         <v>17</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H14" s="5">
         <v>96</v>
       </c>
@@ -1981,14 +1996,14 @@
       </c>
       <c r="T14" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 10 | Urban area | Fully developed urban areas - Western desert urban areas | Artificial desert landscaping (impervious weed barrier, desert shrub with 1- to 2-inch sand or gravel mulch and basin borders) |Unique | |96 |96 |96 |96 |</v>
+        <v>| 10 | Urban area | Fully developed urban areas - Western desert urban areas | Artificial desert landscaping (impervious weed barrier, desert shrub with 1- to 2-inch sand or gravel mulch and basin borders) |Unique |&lt;sub&gt;&lt;/sub&gt; |96 |96 |96 |96 |</v>
       </c>
       <c r="U14" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 10 | Urban area | Fully developed urban areas - Western desert urban areas | Artificial desert landscaping (impervious weed barrier, desert shrub with 1- to 2-inch sand or gravel mulch and basin borders) |Unique | |96 |96 |96 |96 | | | |</v>
-      </c>
-    </row>
-    <row r="15" spans="2:21" ht="338.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 10 | Urban area | Fully developed urban areas - Western desert urban areas | Artificial desert landscaping (impervious weed barrier, desert shrub with 1- to 2-inch sand or gravel mulch and basin borders) |Unique |&lt;sub&gt;&lt;/sub&gt; |96 |96 |96 |96 | | | |</v>
+      </c>
+    </row>
+    <row r="15" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="5">
         <v>11</v>
       </c>
@@ -1996,16 +2011,16 @@
         <v>17</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="H15" s="5">
         <v>89</v>
@@ -2041,14 +2056,14 @@
       </c>
       <c r="T15" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 11 | Urban area | Fully developed urban areas - Urban districts | Commercial and business. Average percent impervious area: 85 |Unique |The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4. |89 |92 |94 |95 |</v>
+        <v>| 11 | Urban area | Fully developed urban areas - Urban districts | Commercial and business. Average percent impervious area: 85 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |89 |92 |94 |95 |</v>
       </c>
       <c r="U15" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 11 | Urban area | Fully developed urban areas - Urban districts | Commercial and business. Average percent impervious area: 85 |Unique |The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4. |89 |92 |94 |95 | | | |</v>
-      </c>
-    </row>
-    <row r="16" spans="2:21" ht="338.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 11 | Urban area | Fully developed urban areas - Urban districts | Commercial and business. Average percent impervious area: 85 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |89 |92 |94 |95 | | | |</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="5">
         <v>12</v>
       </c>
@@ -2056,16 +2071,16 @@
         <v>17</v>
       </c>
       <c r="D16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>38</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="H16" s="5">
         <v>81</v>
@@ -2101,14 +2116,14 @@
       </c>
       <c r="T16" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 12 | Urban area | Fully developed urban areas - Urban districts | Industrial. Average percent impervious area: 72 |Unique |The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4. |81 |88 |91 |93 |</v>
+        <v>| 12 | Urban area | Fully developed urban areas - Urban districts | Industrial. Average percent impervious area: 72 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |81 |88 |91 |93 |</v>
       </c>
       <c r="U16" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 12 | Urban area | Fully developed urban areas - Urban districts | Industrial. Average percent impervious area: 72 |Unique |The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4. |81 |88 |91 |93 | | | |</v>
-      </c>
-    </row>
-    <row r="17" spans="2:21" ht="338.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 12 | Urban area | Fully developed urban areas - Urban districts | Industrial. Average percent impervious area: 72 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |81 |88 |91 |93 | | | |</v>
+      </c>
+    </row>
+    <row r="17" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="5">
         <v>13</v>
       </c>
@@ -2116,16 +2131,16 @@
         <v>17</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="H17" s="5">
         <v>77</v>
@@ -2161,14 +2176,14 @@
       </c>
       <c r="T17" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 13 | Urban area | Fully developed urban areas - Residential districts by average lot size | 1/8 acre or less (town houses). Average percent impervious area: 65 |Unique |The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4. |77 |85 |90 |92 |</v>
+        <v>| 13 | Urban area | Fully developed urban areas - Residential districts by average lot size | 1/8 acre or less (town houses). Average percent impervious area: 65 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |77 |85 |90 |92 |</v>
       </c>
       <c r="U17" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 13 | Urban area | Fully developed urban areas - Residential districts by average lot size | 1/8 acre or less (town houses). Average percent impervious area: 65 |Unique |The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4. |77 |85 |90 |92 | | | |</v>
-      </c>
-    </row>
-    <row r="18" spans="2:21" ht="338.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 13 | Urban area | Fully developed urban areas - Residential districts by average lot size | 1/8 acre or less (town houses). Average percent impervious area: 65 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |77 |85 |90 |92 | | | |</v>
+      </c>
+    </row>
+    <row r="18" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="5">
         <v>14</v>
       </c>
@@ -2176,16 +2191,16 @@
         <v>17</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="H18" s="5">
         <v>61</v>
@@ -2221,14 +2236,14 @@
       </c>
       <c r="T18" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 14 | Urban area | Fully developed urban areas - Urban districts | 1/4 acre. Average percent impervious area: 38 |Unique |The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4. |61 |75 |83 |87 |</v>
+        <v>| 14 | Urban area | Fully developed urban areas - Urban districts | 1/4 acre. Average percent impervious area: 38 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |61 |75 |83 |87 |</v>
       </c>
       <c r="U18" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 14 | Urban area | Fully developed urban areas - Urban districts | 1/4 acre. Average percent impervious area: 38 |Unique |The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4. |61 |75 |83 |87 | | | |</v>
-      </c>
-    </row>
-    <row r="19" spans="2:21" ht="338.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 14 | Urban area | Fully developed urban areas - Urban districts | 1/4 acre. Average percent impervious area: 38 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |61 |75 |83 |87 | | | |</v>
+      </c>
+    </row>
+    <row r="19" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="5">
         <v>15</v>
       </c>
@@ -2236,16 +2251,16 @@
         <v>17</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="H19" s="5">
         <v>57</v>
@@ -2281,14 +2296,14 @@
       </c>
       <c r="T19" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 15 | Urban area | Fully developed urban areas - Urban districts | 1/3 acre. Average percent impervious area: 30 |Unique |The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4. |57 |72 |81 |86 |</v>
+        <v>| 15 | Urban area | Fully developed urban areas - Urban districts | 1/3 acre. Average percent impervious area: 30 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |57 |72 |81 |86 |</v>
       </c>
       <c r="U19" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 15 | Urban area | Fully developed urban areas - Urban districts | 1/3 acre. Average percent impervious area: 30 |Unique |The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4. |57 |72 |81 |86 | | | |</v>
-      </c>
-    </row>
-    <row r="20" spans="2:21" ht="338.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 15 | Urban area | Fully developed urban areas - Urban districts | 1/3 acre. Average percent impervious area: 30 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |57 |72 |81 |86 | | | |</v>
+      </c>
+    </row>
+    <row r="20" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="5">
         <v>16</v>
       </c>
@@ -2296,16 +2311,16 @@
         <v>17</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="H20" s="5">
         <v>54</v>
@@ -2341,14 +2356,14 @@
       </c>
       <c r="T20" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 16 | Urban area | Fully developed urban areas - Urban districts | 1/2 acre. Average percent impervious area: 25 |Unique |The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4. |54 |70 |80 |85 |</v>
+        <v>| 16 | Urban area | Fully developed urban areas - Urban districts | 1/2 acre. Average percent impervious area: 25 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |54 |70 |80 |85 |</v>
       </c>
       <c r="U20" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 16 | Urban area | Fully developed urban areas - Urban districts | 1/2 acre. Average percent impervious area: 25 |Unique |The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4. |54 |70 |80 |85 | | | |</v>
-      </c>
-    </row>
-    <row r="21" spans="2:21" ht="338.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 16 | Urban area | Fully developed urban areas - Urban districts | 1/2 acre. Average percent impervious area: 25 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |54 |70 |80 |85 | | | |</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="5">
         <v>17</v>
       </c>
@@ -2356,16 +2371,16 @@
         <v>17</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="H21" s="5">
         <v>51</v>
@@ -2401,14 +2416,14 @@
       </c>
       <c r="T21" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 17 | Urban area | Fully developed urban areas - Urban districts | 1 acre. Average percent impervious area: 20 |Unique |The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4. |51 |68 |79 |84 |</v>
+        <v>| 17 | Urban area | Fully developed urban areas - Urban districts | 1 acre. Average percent impervious area: 20 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |51 |68 |79 |84 |</v>
       </c>
       <c r="U21" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 17 | Urban area | Fully developed urban areas - Urban districts | 1 acre. Average percent impervious area: 20 |Unique |The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4. |51 |68 |79 |84 | | | |</v>
-      </c>
-    </row>
-    <row r="22" spans="2:21" ht="338.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 17 | Urban area | Fully developed urban areas - Urban districts | 1 acre. Average percent impervious area: 20 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |51 |68 |79 |84 | | | |</v>
+      </c>
+    </row>
+    <row r="22" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="5">
         <v>18</v>
       </c>
@@ -2416,16 +2431,16 @@
         <v>17</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="H22" s="5">
         <v>46</v>
@@ -2461,14 +2476,14 @@
       </c>
       <c r="T22" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 18 | Urban area | Fully developed urban areas - Urban districts | 2 acre. Average percent impervious area: 12 |Unique |The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4. |46 |65 |77 |82 |</v>
+        <v>| 18 | Urban area | Fully developed urban areas - Urban districts | 2 acre. Average percent impervious area: 12 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |46 |65 |77 |82 |</v>
       </c>
       <c r="U22" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 18 | Urban area | Fully developed urban areas - Urban districts | 2 acre. Average percent impervious area: 12 |Unique |The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4. |46 |65 |77 |82 | | | |</v>
-      </c>
-    </row>
-    <row r="23" spans="2:21" ht="215.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 18 | Urban area | Fully developed urban areas - Urban districts | 2 acre. Average percent impervious area: 12 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |46 |65 |77 |82 | | | |</v>
+      </c>
+    </row>
+    <row r="23" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="5">
         <v>19</v>
       </c>
@@ -2476,16 +2491,16 @@
         <v>17</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="H23" s="5">
         <v>77</v>
@@ -2521,30 +2536,32 @@
       </c>
       <c r="T23" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 19 | Urban area | Developing urban areas | Newly graded areas (pervious areas only, no vegetation) |Unique |Composite CN's to use for the design of temporary measures during grading and construction should be computed using figure 2-3 or 2-4, based on the degree of development (imperviousness area percentage) and the CN's for the newly graded pervious areas. |77 |86 |91 |94 |</v>
+        <v>| 19 | Urban area | Developing urban areas | Newly graded areas (pervious areas only, no vegetation) |Unique |&lt;sub&gt;Composite CN's to use for the design of temporary measures during grading and construction should be computed using figure 2-3 or 2-4, based on the degree of development (imperviousness area percentage) and the CN's for the newly graded pervious areas.&lt;/sub&gt; |77 |86 |91 |94 |</v>
       </c>
       <c r="U23" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 19 | Urban area | Developing urban areas | Newly graded areas (pervious areas only, no vegetation) |Unique |Composite CN's to use for the design of temporary measures during grading and construction should be computed using figure 2-3 or 2-4, based on the degree of development (imperviousness area percentage) and the CN's for the newly graded pervious areas. |77 |86 |91 |94 | | | |</v>
-      </c>
-    </row>
-    <row r="24" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 19 | Urban area | Developing urban areas | Newly graded areas (pervious areas only, no vegetation) |Unique |&lt;sub&gt;Composite CN's to use for the design of temporary measures during grading and construction should be computed using figure 2-3 or 2-4, based on the degree of development (imperviousness area percentage) and the CN's for the newly graded pervious areas.&lt;/sub&gt; |77 |86 |91 |94 | | | |</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="5">
         <v>20</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G24" s="5"/>
+      <c r="G24" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="H24" s="5">
         <v>77</v>
       </c>
@@ -2579,31 +2596,31 @@
       </c>
       <c r="T24" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 20 | Cultivated agricultural lands | Fallow | Bare soil |Unique | |77 |86 |91 |94 |</v>
+        <v>| 20 | Cultivated agricultural lands | Fallow | Bare soil |Unique |&lt;sub&gt;&lt;/sub&gt; |77 |86 |91 |94 |</v>
       </c>
       <c r="U24" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 20 | Cultivated agricultural lands | Fallow | Bare soil |Unique | |77 |86 |91 |94 | | | |</v>
-      </c>
-    </row>
-    <row r="25" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 20 | Cultivated agricultural lands | Fallow | Bare soil |Unique |&lt;sub&gt;&lt;/sub&gt; |77 |86 |91 |94 | | | |</v>
+      </c>
+    </row>
+    <row r="25" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="5">
         <v>21</v>
       </c>
       <c r="C25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="G25" s="5" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H25" s="5">
         <v>76</v>
@@ -2639,31 +2656,31 @@
       </c>
       <c r="T25" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 21 | Cultivated agricultural lands | Fallow | Crop residue cover (CR) |Poor |Factors impair infiltration and tend to increase runoff. |76 |85 |90 |93 |</v>
+        <v>| 21 | Cultivated agricultural lands | Fallow | Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |76 |85 |90 |93 |</v>
       </c>
       <c r="U25" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 21 | Cultivated agricultural lands | Fallow | Crop residue cover (CR) |Poor |Factors impair infiltration and tend to increase runoff. |76 |85 |90 |93 | | | |</v>
-      </c>
-    </row>
-    <row r="26" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 21 | Cultivated agricultural lands | Fallow | Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |76 |85 |90 |93 | | | |</v>
+      </c>
+    </row>
+    <row r="26" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="4">
         <v>22</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D26" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="G26" s="4" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="H26" s="4">
         <v>74</v>
@@ -2699,31 +2716,31 @@
       </c>
       <c r="T26" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 22 | Cultivated agricultural lands | Fallow | Crop residue cover (CR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |74 |83 |88 |90 |</v>
+        <v>| 22 | Cultivated agricultural lands | Fallow | Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |74 |83 |88 |90 |</v>
       </c>
       <c r="U26" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 22 | Cultivated agricultural lands | Fallow | Crop residue cover (CR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |74 |83 |88 |90 | | | |</v>
-      </c>
-    </row>
-    <row r="27" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 22 | Cultivated agricultural lands | Fallow | Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |74 |83 |88 |90 | | | |</v>
+      </c>
+    </row>
+    <row r="27" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="4">
         <v>23</v>
       </c>
       <c r="C27" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="G27" s="4" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H27" s="4">
         <v>72</v>
@@ -2759,31 +2776,31 @@
       </c>
       <c r="T27" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 23 | Cultivated agricultural lands | Row crops | Straight row (SR) |Poor |Factors impair infiltration and tend to increase runoff. |72 |81 |88 |91 |</v>
+        <v>| 23 | Cultivated agricultural lands | Row crops | Straight row (SR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |72 |81 |88 |91 |</v>
       </c>
       <c r="U27" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 23 | Cultivated agricultural lands | Row crops | Straight row (SR) |Poor |Factors impair infiltration and tend to increase runoff. |72 |81 |88 |91 | | | |</v>
-      </c>
-    </row>
-    <row r="28" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 23 | Cultivated agricultural lands | Row crops | Straight row (SR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |72 |81 |88 |91 | | | |</v>
+      </c>
+    </row>
+    <row r="28" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="4">
         <v>24</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="H28" s="4">
         <v>67</v>
@@ -2819,31 +2836,31 @@
       </c>
       <c r="T28" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 24 | Cultivated agricultural lands | Row crops | Straight row (SR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |67 |78 |85 |89 |</v>
+        <v>| 24 | Cultivated agricultural lands | Row crops | Straight row (SR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |67 |78 |85 |89 |</v>
       </c>
       <c r="U28" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 24 | Cultivated agricultural lands | Row crops | Straight row (SR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |67 |78 |85 |89 | | | |</v>
-      </c>
-    </row>
-    <row r="29" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 24 | Cultivated agricultural lands | Row crops | Straight row (SR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |67 |78 |85 |89 | | | |</v>
+      </c>
+    </row>
+    <row r="29" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="4">
         <v>25</v>
       </c>
       <c r="C29" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="G29" s="4" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H29" s="4">
         <v>71</v>
@@ -2879,31 +2896,31 @@
       </c>
       <c r="T29" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 25 | Cultivated agricultural lands | Row crops | Straight row (SR) + Crop residue cover (CR) |Poor |Factors impair infiltration and tend to increase runoff. |71 |80 |87 |90 |</v>
+        <v>| 25 | Cultivated agricultural lands | Row crops | Straight row (SR) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |71 |80 |87 |90 |</v>
       </c>
       <c r="U29" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 25 | Cultivated agricultural lands | Row crops | Straight row (SR) + Crop residue cover (CR) |Poor |Factors impair infiltration and tend to increase runoff. |71 |80 |87 |90 | | | |</v>
-      </c>
-    </row>
-    <row r="30" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 25 | Cultivated agricultural lands | Row crops | Straight row (SR) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |71 |80 |87 |90 | | | |</v>
+      </c>
+    </row>
+    <row r="30" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="4">
         <v>26</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="H30" s="4">
         <v>64</v>
@@ -2939,31 +2956,31 @@
       </c>
       <c r="T30" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 26 | Cultivated agricultural lands | Row crops | Straight row (SR) + Crop residue cover (CR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |64 |75 |82 |85 |</v>
+        <v>| 26 | Cultivated agricultural lands | Row crops | Straight row (SR) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |64 |75 |82 |85 |</v>
       </c>
       <c r="U30" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 26 | Cultivated agricultural lands | Row crops | Straight row (SR) + Crop residue cover (CR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |64 |75 |82 |85 | | | |</v>
-      </c>
-    </row>
-    <row r="31" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 26 | Cultivated agricultural lands | Row crops | Straight row (SR) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |64 |75 |82 |85 | | | |</v>
+      </c>
+    </row>
+    <row r="31" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="4">
         <v>27</v>
       </c>
       <c r="C31" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="G31" s="4" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H31" s="4">
         <v>70</v>
@@ -2999,31 +3016,31 @@
       </c>
       <c r="T31" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 27 | Cultivated agricultural lands | Row crops | Contoured (C) |Poor |Factors impair infiltration and tend to increase runoff. |70 |79 |84 |88 |</v>
+        <v>| 27 | Cultivated agricultural lands | Row crops | Contoured (C) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |70 |79 |84 |88 |</v>
       </c>
       <c r="U31" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 27 | Cultivated agricultural lands | Row crops | Contoured (C) |Poor |Factors impair infiltration and tend to increase runoff. |70 |79 |84 |88 | | | |</v>
-      </c>
-    </row>
-    <row r="32" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 27 | Cultivated agricultural lands | Row crops | Contoured (C) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |70 |79 |84 |88 | | | |</v>
+      </c>
+    </row>
+    <row r="32" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="5">
         <v>28</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="H32" s="4">
         <v>65</v>
@@ -3059,31 +3076,31 @@
       </c>
       <c r="T32" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 28 | Cultivated agricultural lands | Row crops | Contoured (C) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |65 |75 |82 |86 |</v>
+        <v>| 28 | Cultivated agricultural lands | Row crops | Contoured (C) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |65 |75 |82 |86 |</v>
       </c>
       <c r="U32" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 28 | Cultivated agricultural lands | Row crops | Contoured (C) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |65 |75 |82 |86 | | | |</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 28 | Cultivated agricultural lands | Row crops | Contoured (C) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |65 |75 |82 |86 | | | |</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="5">
         <v>29</v>
       </c>
       <c r="C33" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="G33" s="4" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H33" s="4">
         <v>69</v>
@@ -3119,31 +3136,31 @@
       </c>
       <c r="T33" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 29 | Cultivated agricultural lands | Row crops | Contoured (C) + Crop residue cover (CR) |Poor |Factors impair infiltration and tend to increase runoff. |69 |78 |83 |87 |</v>
+        <v>| 29 | Cultivated agricultural lands | Row crops | Contoured (C) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |69 |78 |83 |87 |</v>
       </c>
       <c r="U33" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 29 | Cultivated agricultural lands | Row crops | Contoured (C) + Crop residue cover (CR) |Poor |Factors impair infiltration and tend to increase runoff. |69 |78 |83 |87 | | | |</v>
-      </c>
-    </row>
-    <row r="34" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 29 | Cultivated agricultural lands | Row crops | Contoured (C) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |69 |78 |83 |87 | | | |</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="4">
         <v>30</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="H34" s="4">
         <v>64</v>
@@ -3179,31 +3196,31 @@
       </c>
       <c r="T34" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 30 | Cultivated agricultural lands | Row crops | Contoured (C) + Crop residue cover (CR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |64 |74 |81 |85 |</v>
+        <v>| 30 | Cultivated agricultural lands | Row crops | Contoured (C) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |64 |74 |81 |85 |</v>
       </c>
       <c r="U34" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 30 | Cultivated agricultural lands | Row crops | Contoured (C) + Crop residue cover (CR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |64 |74 |81 |85 | | | |</v>
-      </c>
-    </row>
-    <row r="35" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 30 | Cultivated agricultural lands | Row crops | Contoured (C) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |64 |74 |81 |85 | | | |</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="4">
         <v>31</v>
       </c>
       <c r="C35" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="G35" s="4" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H35" s="4">
         <v>66</v>
@@ -3239,31 +3256,31 @@
       </c>
       <c r="T35" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 31 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) |Poor |Factors impair infiltration and tend to increase runoff. |66 |74 |80 |82 |</v>
+        <v>| 31 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |66 |74 |80 |82 |</v>
       </c>
       <c r="U35" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 31 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) |Poor |Factors impair infiltration and tend to increase runoff. |66 |74 |80 |82 | | | |</v>
-      </c>
-    </row>
-    <row r="36" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 31 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |66 |74 |80 |82 | | | |</v>
+      </c>
+    </row>
+    <row r="36" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" s="4">
         <v>32</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="H36" s="4">
         <v>62</v>
@@ -3299,31 +3316,31 @@
       </c>
       <c r="T36" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 32 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |62 |71 |78 |81 |</v>
+        <v>| 32 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |62 |71 |78 |81 |</v>
       </c>
       <c r="U36" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 32 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |62 |71 |78 |81 | | | |</v>
-      </c>
-    </row>
-    <row r="37" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 32 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |62 |71 |78 |81 | | | |</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="5">
         <v>33</v>
       </c>
       <c r="C37" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="G37" s="4" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H37" s="4">
         <v>65</v>
@@ -3359,31 +3376,31 @@
       </c>
       <c r="T37" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 33 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Poor |Factors impair infiltration and tend to increase runoff. |65 |73 |79 |81 |</v>
+        <v>| 33 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |65 |73 |79 |81 |</v>
       </c>
       <c r="U37" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 33 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Poor |Factors impair infiltration and tend to increase runoff. |65 |73 |79 |81 | | | |</v>
-      </c>
-    </row>
-    <row r="38" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 33 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |65 |73 |79 |81 | | | |</v>
+      </c>
+    </row>
+    <row r="38" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" s="5">
         <v>34</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D38" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>63</v>
-      </c>
       <c r="F38" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="H38" s="4">
         <v>61</v>
@@ -3419,31 +3436,31 @@
       </c>
       <c r="T38" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 34 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |61 |70 |77 |80 |</v>
+        <v>| 34 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |61 |70 |77 |80 |</v>
       </c>
       <c r="U38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 34 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |61 |70 |77 |80 | | | |</v>
-      </c>
-    </row>
-    <row r="39" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 34 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |61 |70 |77 |80 | | | |</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" s="4">
         <v>35</v>
       </c>
       <c r="C39" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F39" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D39" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="G39" s="4" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H39" s="4">
         <v>65</v>
@@ -3479,31 +3496,31 @@
       </c>
       <c r="T39" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 35 | Cultivated agricultural lands | Small grain | Straight row (SR) |Poor |Factors impair infiltration and tend to increase runoff. |65 |76 |84 |88 |</v>
+        <v>| 35 | Cultivated agricultural lands | Small grain | Straight row (SR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |65 |76 |84 |88 |</v>
       </c>
       <c r="U39" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 35 | Cultivated agricultural lands | Small grain | Straight row (SR) |Poor |Factors impair infiltration and tend to increase runoff. |65 |76 |84 |88 | | | |</v>
-      </c>
-    </row>
-    <row r="40" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 35 | Cultivated agricultural lands | Small grain | Straight row (SR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |65 |76 |84 |88 | | | |</v>
+      </c>
+    </row>
+    <row r="40" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" s="4">
         <v>36</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="H40" s="4">
         <v>63</v>
@@ -3539,31 +3556,31 @@
       </c>
       <c r="T40" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 36 | Cultivated agricultural lands | Small grain | Straight row (SR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |63 |75 |83 |87 |</v>
+        <v>| 36 | Cultivated agricultural lands | Small grain | Straight row (SR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |63 |75 |83 |87 |</v>
       </c>
       <c r="U40" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 36 | Cultivated agricultural lands | Small grain | Straight row (SR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |63 |75 |83 |87 | | | |</v>
-      </c>
-    </row>
-    <row r="41" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 36 | Cultivated agricultural lands | Small grain | Straight row (SR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |63 |75 |83 |87 | | | |</v>
+      </c>
+    </row>
+    <row r="41" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="4">
         <v>37</v>
       </c>
       <c r="C41" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F41" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="G41" s="4" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H41" s="4">
         <v>64</v>
@@ -3599,31 +3616,31 @@
       </c>
       <c r="T41" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 37 | Cultivated agricultural lands | Small grain | Straight row (SR) + Crop residue cover (CR) |Poor |Factors impair infiltration and tend to increase runoff. |64 |75 |83 |86 |</v>
+        <v>| 37 | Cultivated agricultural lands | Small grain | Straight row (SR) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |64 |75 |83 |86 |</v>
       </c>
       <c r="U41" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 37 | Cultivated agricultural lands | Small grain | Straight row (SR) + Crop residue cover (CR) |Poor |Factors impair infiltration and tend to increase runoff. |64 |75 |83 |86 | | | |</v>
-      </c>
-    </row>
-    <row r="42" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 37 | Cultivated agricultural lands | Small grain | Straight row (SR) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |64 |75 |83 |86 | | | |</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="4">
         <v>38</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="H42" s="4">
         <v>60</v>
@@ -3659,31 +3676,31 @@
       </c>
       <c r="T42" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 38 | Cultivated agricultural lands | Small grain | Straight row (SR) + Crop residue cover (CR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |60 |72 |80 |84 |</v>
+        <v>| 38 | Cultivated agricultural lands | Small grain | Straight row (SR) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |60 |72 |80 |84 |</v>
       </c>
       <c r="U42" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 38 | Cultivated agricultural lands | Small grain | Straight row (SR) + Crop residue cover (CR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |60 |72 |80 |84 | | | |</v>
-      </c>
-    </row>
-    <row r="43" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 38 | Cultivated agricultural lands | Small grain | Straight row (SR) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |60 |72 |80 |84 | | | |</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="4">
         <v>39</v>
       </c>
       <c r="C43" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D43" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="G43" s="4" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H43" s="4">
         <v>63</v>
@@ -3719,31 +3736,31 @@
       </c>
       <c r="T43" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 39 | Cultivated agricultural lands | Small grain | Contoured (C) |Poor |Factors impair infiltration and tend to increase runoff. |63 |74 |82 |85 |</v>
+        <v>| 39 | Cultivated agricultural lands | Small grain | Contoured (C) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |63 |74 |82 |85 |</v>
       </c>
       <c r="U43" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 39 | Cultivated agricultural lands | Small grain | Contoured (C) |Poor |Factors impair infiltration and tend to increase runoff. |63 |74 |82 |85 | | | |</v>
-      </c>
-    </row>
-    <row r="44" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 39 | Cultivated agricultural lands | Small grain | Contoured (C) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |63 |74 |82 |85 | | | |</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="4">
         <v>40</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="H44" s="4">
         <v>61</v>
@@ -3779,31 +3796,31 @@
       </c>
       <c r="T44" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 40 | Cultivated agricultural lands | Small grain | Contoured (C) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |61 |73 |81 |84 |</v>
+        <v>| 40 | Cultivated agricultural lands | Small grain | Contoured (C) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |61 |73 |81 |84 |</v>
       </c>
       <c r="U44" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 40 | Cultivated agricultural lands | Small grain | Contoured (C) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |61 |73 |81 |84 | | | |</v>
-      </c>
-    </row>
-    <row r="45" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 40 | Cultivated agricultural lands | Small grain | Contoured (C) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |61 |73 |81 |84 | | | |</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="4">
         <v>41</v>
       </c>
       <c r="C45" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D45" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="G45" s="4" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H45" s="4">
         <v>62</v>
@@ -3839,31 +3856,31 @@
       </c>
       <c r="T45" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 41 | Cultivated agricultural lands | Small grain | Contoured (C) + Crop residue cover (CR) |Poor |Factors impair infiltration and tend to increase runoff. |62 |73 |81 |84 |</v>
+        <v>| 41 | Cultivated agricultural lands | Small grain | Contoured (C) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |62 |73 |81 |84 |</v>
       </c>
       <c r="U45" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 41 | Cultivated agricultural lands | Small grain | Contoured (C) + Crop residue cover (CR) |Poor |Factors impair infiltration and tend to increase runoff. |62 |73 |81 |84 | | | |</v>
-      </c>
-    </row>
-    <row r="46" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 41 | Cultivated agricultural lands | Small grain | Contoured (C) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |62 |73 |81 |84 | | | |</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" s="4">
         <v>42</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="H46" s="4">
         <v>60</v>
@@ -3899,31 +3916,31 @@
       </c>
       <c r="T46" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 42 | Cultivated agricultural lands | Small grain | Contoured (C) + Crop residue cover (CR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |60 |72 |80 |83 |</v>
+        <v>| 42 | Cultivated agricultural lands | Small grain | Contoured (C) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |60 |72 |80 |83 |</v>
       </c>
       <c r="U46" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 42 | Cultivated agricultural lands | Small grain | Contoured (C) + Crop residue cover (CR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |60 |72 |80 |83 | | | |</v>
-      </c>
-    </row>
-    <row r="47" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 42 | Cultivated agricultural lands | Small grain | Contoured (C) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |60 |72 |80 |83 | | | |</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="4">
         <v>43</v>
       </c>
       <c r="C47" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D47" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="G47" s="4" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H47" s="4">
         <v>61</v>
@@ -3959,31 +3976,31 @@
       </c>
       <c r="T47" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 43 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) |Poor |Factors impair infiltration and tend to increase runoff. |61 |72 |79 |82 |</v>
+        <v>| 43 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |61 |72 |79 |82 |</v>
       </c>
       <c r="U47" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 43 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) |Poor |Factors impair infiltration and tend to increase runoff. |61 |72 |79 |82 | | | |</v>
-      </c>
-    </row>
-    <row r="48" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 43 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |61 |72 |79 |82 | | | |</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="4">
         <v>44</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="H48" s="4">
         <v>59</v>
@@ -4019,31 +4036,31 @@
       </c>
       <c r="T48" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 44 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |59 |70 |78 |81 |</v>
+        <v>| 44 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |59 |70 |78 |81 |</v>
       </c>
       <c r="U48" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 44 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |59 |70 |78 |81 | | | |</v>
-      </c>
-    </row>
-    <row r="49" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 44 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |59 |70 |78 |81 | | | |</v>
+      </c>
+    </row>
+    <row r="49" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="4">
         <v>45</v>
       </c>
       <c r="C49" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F49" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D49" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="G49" s="4" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H49" s="4">
         <v>60</v>
@@ -4079,31 +4096,31 @@
       </c>
       <c r="T49" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 45 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Poor |Factors impair infiltration and tend to increase runoff. |60 |71 |78 |81 |</v>
+        <v>| 45 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |60 |71 |78 |81 |</v>
       </c>
       <c r="U49" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 45 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Poor |Factors impair infiltration and tend to increase runoff. |60 |71 |78 |81 | | | |</v>
-      </c>
-    </row>
-    <row r="50" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 45 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |60 |71 |78 |81 | | | |</v>
+      </c>
+    </row>
+    <row r="50" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="4">
         <v>46</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="H50" s="4">
         <v>58</v>
@@ -4139,31 +4156,31 @@
       </c>
       <c r="T50" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 46 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |58 |69 |77 |80 |</v>
+        <v>| 46 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |58 |69 |77 |80 |</v>
       </c>
       <c r="U50" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 46 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |58 |69 |77 |80 | | | |</v>
-      </c>
-    </row>
-    <row r="51" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 46 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |58 |69 |77 |80 | | | |</v>
+      </c>
+    </row>
+    <row r="51" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" s="4">
         <v>47</v>
       </c>
       <c r="C51" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F51" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D51" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="G51" s="4" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H51" s="4">
         <v>66</v>
@@ -4199,31 +4216,31 @@
       </c>
       <c r="T51" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 47 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Straight row (SR) |Poor |Factors impair infiltration and tend to increase runoff. |66 |77 |85 |89 |</v>
+        <v>| 47 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Straight row (SR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |66 |77 |85 |89 |</v>
       </c>
       <c r="U51" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 47 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Straight row (SR) |Poor |Factors impair infiltration and tend to increase runoff. |66 |77 |85 |89 | | | |</v>
-      </c>
-    </row>
-    <row r="52" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 47 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Straight row (SR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |66 |77 |85 |89 | | | |</v>
+      </c>
+    </row>
+    <row r="52" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" s="4">
         <v>48</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="H52" s="4">
         <v>58</v>
@@ -4259,31 +4276,31 @@
       </c>
       <c r="T52" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 48 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Straight row (SR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |58 |72 |81 |85 |</v>
+        <v>| 48 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Straight row (SR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |58 |72 |81 |85 |</v>
       </c>
       <c r="U52" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 48 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Straight row (SR) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |58 |72 |81 |85 | | | |</v>
-      </c>
-    </row>
-    <row r="53" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 48 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Straight row (SR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |58 |72 |81 |85 | | | |</v>
+      </c>
+    </row>
+    <row r="53" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="4">
         <v>49</v>
       </c>
       <c r="C53" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D53" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="G53" s="4" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H53" s="4">
         <v>64</v>
@@ -4319,31 +4336,31 @@
       </c>
       <c r="T53" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 49 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured (C) |Poor |Factors impair infiltration and tend to increase runoff. |64 |75 |83 |85 |</v>
+        <v>| 49 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured (C) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |64 |75 |83 |85 |</v>
       </c>
       <c r="U53" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 49 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured (C) |Poor |Factors impair infiltration and tend to increase runoff. |64 |75 |83 |85 | | | |</v>
-      </c>
-    </row>
-    <row r="54" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 49 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured (C) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |64 |75 |83 |85 | | | |</v>
+      </c>
+    </row>
+    <row r="54" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="4">
         <v>50</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="H54" s="4">
         <v>55</v>
@@ -4379,31 +4396,31 @@
       </c>
       <c r="T54" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 50 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured (C) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |55 |69 |78 |83 |</v>
+        <v>| 50 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured (C) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |55 |69 |78 |83 |</v>
       </c>
       <c r="U54" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 50 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured (C) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |55 |69 |78 |83 | | | |</v>
-      </c>
-    </row>
-    <row r="55" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 50 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured (C) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |55 |69 |78 |83 | | | |</v>
+      </c>
+    </row>
+    <row r="55" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="4">
         <v>51</v>
       </c>
       <c r="C55" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F55" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="G55" s="4" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="H55" s="4">
         <v>63</v>
@@ -4439,31 +4456,31 @@
       </c>
       <c r="T55" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 51 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured &amp; terraced (C &amp; T) |Poor |Factors impair infiltration and tend to increase runoff. |63 |73 |80 |83 |</v>
+        <v>| 51 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured &amp; terraced (C &amp; T) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |63 |73 |80 |83 |</v>
       </c>
       <c r="U55" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 51 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured &amp; terraced (C &amp; T) |Poor |Factors impair infiltration and tend to increase runoff. |63 |73 |80 |83 | | | |</v>
-      </c>
-    </row>
-    <row r="56" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 51 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured &amp; terraced (C &amp; T) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |63 |73 |80 |83 | | | |</v>
+      </c>
+    </row>
+    <row r="56" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="4">
         <v>52</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="H56" s="4">
         <v>51</v>
@@ -4499,28 +4516,30 @@
       </c>
       <c r="T56" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 52 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured &amp; terraced (C &amp; T) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |51 |67 |76 |80 |</v>
+        <v>| 52 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured &amp; terraced (C &amp; T) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |51 |67 |76 |80 |</v>
       </c>
       <c r="U56" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 52 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured &amp; terraced (C &amp; T) |Good |Factors encourage average and better than average infiltration and tend to decrease runoff. |51 |67 |76 |80 | | | |</v>
-      </c>
-    </row>
-    <row r="57" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 52 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured &amp; terraced (C &amp; T) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |51 |67 |76 |80 | | | |</v>
+      </c>
+    </row>
+    <row r="57" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="4">
         <v>53</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E57" s="4"/>
       <c r="F57" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G57" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="H57" s="4">
         <v>68</v>
       </c>
@@ -4555,29 +4574,29 @@
       </c>
       <c r="T57" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 53 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Poor | |68 |79 |86 |89 |</v>
+        <v>| 53 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Poor |&lt;sub&gt;&lt;/sub&gt; |68 |79 |86 |89 |</v>
       </c>
       <c r="U57" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 53 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Poor | |68 |79 |86 |89 | | | |</v>
-      </c>
-    </row>
-    <row r="58" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 53 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Poor |&lt;sub&gt;&lt;/sub&gt; |68 |79 |86 |89 | | | |</v>
+      </c>
+    </row>
+    <row r="58" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="4">
         <v>54</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E58" s="4"/>
       <c r="F58" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="H58" s="4">
         <v>49</v>
@@ -4613,29 +4632,29 @@
       </c>
       <c r="T58" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 54 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Fair |50 to 75% ground cover and not heavily grazed. |49 |69 |79 |84 |</v>
+        <v>| 54 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Fair |&lt;sub&gt;50 to 75% ground cover and not heavily grazed.&lt;/sub&gt; |49 |69 |79 |84 |</v>
       </c>
       <c r="U58" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 54 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Fair |50 to 75% ground cover and not heavily grazed. |49 |69 |79 |84 | | | |</v>
-      </c>
-    </row>
-    <row r="59" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 54 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Fair |&lt;sub&gt;50 to 75% ground cover and not heavily grazed.&lt;/sub&gt; |49 |69 |79 |84 | | | |</v>
+      </c>
+    </row>
+    <row r="59" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="4">
         <v>55</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E59" s="4"/>
       <c r="F59" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="H59" s="4">
         <v>39</v>
@@ -4671,28 +4690,30 @@
       </c>
       <c r="T59" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 55 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Good |&gt;75% ground cover and lightly or only occasionally grazed. |39 |61 |74 |80 |</v>
+        <v>| 55 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Good |&lt;sub&gt;&gt;75% ground cover and lightly or only occasionally grazed.&lt;/sub&gt; |39 |61 |74 |80 |</v>
       </c>
       <c r="U59" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 55 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Good |&gt;75% ground cover and lightly or only occasionally grazed. |39 |61 |74 |80 | | | |</v>
-      </c>
-    </row>
-    <row r="60" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 55 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Good |&lt;sub&gt;&gt;75% ground cover and lightly or only occasionally grazed.&lt;/sub&gt; |39 |61 |74 |80 | | | |</v>
+      </c>
+    </row>
+    <row r="60" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="4">
         <v>56</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G60" s="4"/>
+      <c r="G60" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="H60" s="4">
         <v>30</v>
       </c>
@@ -4727,28 +4748,30 @@
       </c>
       <c r="T60" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 56 | Other agricultural lands | Meadow – continuous grass, protected from grazing and generally mowed for hay |  |Unique | |30 |58 |71 |78 |</v>
+        <v>| 56 | Other agricultural lands | Meadow – continuous grass, protected from grazing and generally mowed for hay |  |Unique |&lt;sub&gt;&lt;/sub&gt; |30 |58 |71 |78 |</v>
       </c>
       <c r="U60" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 56 | Other agricultural lands | Meadow – continuous grass, protected from grazing and generally mowed for hay |  |Unique | |30 |58 |71 |78 | | | |</v>
-      </c>
-    </row>
-    <row r="61" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 56 | Other agricultural lands | Meadow – continuous grass, protected from grazing and generally mowed for hay |  |Unique |&lt;sub&gt;&lt;/sub&gt; |30 |58 |71 |78 | | | |</v>
+      </c>
+    </row>
+    <row r="61" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="4">
         <v>57</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G61" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="H61" s="4">
         <v>48</v>
       </c>
@@ -4783,29 +4806,29 @@
       </c>
       <c r="T61" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 57 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Poor | |48 |67 |77 |83 |</v>
+        <v>| 57 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Poor |&lt;sub&gt;&lt;/sub&gt; |48 |67 |77 |83 |</v>
       </c>
       <c r="U61" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 57 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Poor | |48 |67 |77 |83 | | | |</v>
-      </c>
-    </row>
-    <row r="62" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 57 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Poor |&lt;sub&gt;&lt;/sub&gt; |48 |67 |77 |83 | | | |</v>
+      </c>
+    </row>
+    <row r="62" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="4">
         <v>58</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E62" s="4"/>
       <c r="F62" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="H62" s="4">
         <v>35</v>
@@ -4841,29 +4864,29 @@
       </c>
       <c r="T62" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 58 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Fair |50 to 75% ground cover. |35 |56 |70 |77 |</v>
+        <v>| 58 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Fair |&lt;sub&gt;50 to 75% ground cover.&lt;/sub&gt; |35 |56 |70 |77 |</v>
       </c>
       <c r="U62" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 58 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Fair |50 to 75% ground cover. |35 |56 |70 |77 | | | |</v>
-      </c>
-    </row>
-    <row r="63" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 58 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Fair |&lt;sub&gt;50 to 75% ground cover.&lt;/sub&gt; |35 |56 |70 |77 | | | |</v>
+      </c>
+    </row>
+    <row r="63" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="4">
         <v>59</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E63" s="4"/>
       <c r="F63" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="H63" s="4"/>
       <c r="I63" s="4">
@@ -4897,29 +4920,29 @@
       </c>
       <c r="T63" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 59 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Good |&gt;75% ground cover. Actual curve number is less than 30; use CN=30 for runoff computations. | |48 |65 |73 |</v>
+        <v>| 59 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Good |&lt;sub&gt;&gt;75% ground cover. Actual curve number is less than 30; use CN=30 for runoff computations.&lt;/sub&gt; | |48 |65 |73 |</v>
       </c>
       <c r="U63" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 59 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Good |&gt;75% ground cover. Actual curve number is less than 30; use CN=30 for runoff computations. | |48 |65 |73 | | | |</v>
-      </c>
-    </row>
-    <row r="64" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 59 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Good |&lt;sub&gt;&gt;75% ground cover. Actual curve number is less than 30; use CN=30 for runoff computations.&lt;/sub&gt; | |48 |65 |73 | | | |</v>
+      </c>
+    </row>
+    <row r="64" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="4">
         <v>60</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E64" s="4"/>
       <c r="F64" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="H64" s="4">
         <v>57</v>
@@ -4955,29 +4978,29 @@
       </c>
       <c r="T64" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 60 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Poor |CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture. |57 |73 |82 |86 |</v>
+        <v>| 60 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Poor |&lt;sub&gt;CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture.&lt;/sub&gt; |57 |73 |82 |86 |</v>
       </c>
       <c r="U64" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 60 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Poor |CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture. |57 |73 |82 |86 | | | |</v>
-      </c>
-    </row>
-    <row r="65" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 60 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Poor |&lt;sub&gt;CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture.&lt;/sub&gt; |57 |73 |82 |86 | | | |</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="4">
         <v>61</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="H65" s="4">
         <v>43</v>
@@ -5013,29 +5036,29 @@
       </c>
       <c r="T65" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 61 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Fair |CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture. |43 |65 |76 |82 |</v>
+        <v>| 61 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Fair |&lt;sub&gt;CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture.&lt;/sub&gt; |43 |65 |76 |82 |</v>
       </c>
       <c r="U65" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 61 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Fair |CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture. |43 |65 |76 |82 | | | |</v>
-      </c>
-    </row>
-    <row r="66" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 61 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Fair |&lt;sub&gt;CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture.&lt;/sub&gt; |43 |65 |76 |82 | | | |</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="4">
         <v>62</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E66" s="4"/>
       <c r="F66" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="H66" s="4">
         <v>32</v>
@@ -5071,29 +5094,29 @@
       </c>
       <c r="T66" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 62 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Good |CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture. |32 |58 |72 |79 |</v>
+        <v>| 62 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Good |&lt;sub&gt;CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture.&lt;/sub&gt; |32 |58 |72 |79 |</v>
       </c>
       <c r="U66" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 62 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Good |CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture. |32 |58 |72 |79 | | | |</v>
-      </c>
-    </row>
-    <row r="67" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 62 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Good |&lt;sub&gt;CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture.&lt;/sub&gt; |32 |58 |72 |79 | | | |</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="4">
         <v>63</v>
       </c>
       <c r="C67" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="E67" s="4"/>
       <c r="F67" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H67" s="4">
         <v>45</v>
@@ -5129,29 +5152,29 @@
       </c>
       <c r="T67" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 63 | Other agricultural lands | Woods |  |Poor |Forest litter, small trees, and brush are destroyed by heavy grazing or regular burning. |45 |66 |77 |83 |</v>
+        <v>| 63 | Other agricultural lands | Woods |  |Poor |&lt;sub&gt;Forest litter, small trees, and brush are destroyed by heavy grazing or regular burning.&lt;/sub&gt; |45 |66 |77 |83 |</v>
       </c>
       <c r="U67" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 63 | Other agricultural lands | Woods |  |Poor |Forest litter, small trees, and brush are destroyed by heavy grazing or regular burning. |45 |66 |77 |83 | | | |</v>
-      </c>
-    </row>
-    <row r="68" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 63 | Other agricultural lands | Woods |  |Poor |&lt;sub&gt;Forest litter, small trees, and brush are destroyed by heavy grazing or regular burning.&lt;/sub&gt; |45 |66 |77 |83 | | | |</v>
+      </c>
+    </row>
+    <row r="68" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="4">
         <v>64</v>
       </c>
       <c r="C68" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="E68" s="4"/>
       <c r="F68" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H68" s="4">
         <v>36</v>
@@ -5187,29 +5210,29 @@
       </c>
       <c r="T68" s="5" t="str">
         <f t="shared" ref="T68:T103" si="9">_xlfn.CONCAT("| ",B68," | ",C68," | ",D68," | ",E68," |",F68," |",G68," |",H68," |",I68," |",J68," |",K68," |")</f>
-        <v>| 64 | Other agricultural lands | Woods |  |Fair |Woods are grazed but not burned, and some forest litter covers the soil. |36 |60 |73 |79 |</v>
+        <v>| 64 | Other agricultural lands | Woods |  |Fair |&lt;sub&gt;Woods are grazed but not burned, and some forest litter covers the soil.&lt;/sub&gt; |36 |60 |73 |79 |</v>
       </c>
       <c r="U68" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 64 | Other agricultural lands | Woods |  |Fair |Woods are grazed but not burned, and some forest litter covers the soil. |36 |60 |73 |79 | | | |</v>
-      </c>
-    </row>
-    <row r="69" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 64 | Other agricultural lands | Woods |  |Fair |&lt;sub&gt;Woods are grazed but not burned, and some forest litter covers the soil.&lt;/sub&gt; |36 |60 |73 |79 | | | |</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" s="4">
         <v>65</v>
       </c>
       <c r="C69" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="E69" s="4"/>
       <c r="F69" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H69" s="4"/>
       <c r="I69" s="4">
@@ -5243,28 +5266,30 @@
       </c>
       <c r="T69" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 65 | Other agricultural lands | Woods |  |Good |Woods are protected from grazing, and litter and brush adequately cover the soil. Actual curve number is less than 30; use CN=30 for runoff computations. | |55 |70 |77 |</v>
+        <v>| 65 | Other agricultural lands | Woods |  |Good |&lt;sub&gt;Woods are protected from grazing, and litter and brush adequately cover the soil. Actual curve number is less than 30; use CN=30 for runoff computations.&lt;/sub&gt; | |55 |70 |77 |</v>
       </c>
       <c r="U69" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 65 | Other agricultural lands | Woods |  |Good |Woods are protected from grazing, and litter and brush adequately cover the soil. Actual curve number is less than 30; use CN=30 for runoff computations. | |55 |70 |77 | | | |</v>
-      </c>
-    </row>
-    <row r="70" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 65 | Other agricultural lands | Woods |  |Good |&lt;sub&gt;Woods are protected from grazing, and litter and brush adequately cover the soil. Actual curve number is less than 30; use CN=30 for runoff computations.&lt;/sub&gt; | |55 |70 |77 | | | |</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" s="4">
         <v>66</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E70" s="4"/>
       <c r="F70" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G70" s="4"/>
+      <c r="G70" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="H70" s="4">
         <v>59</v>
       </c>
@@ -5299,28 +5324,30 @@
       </c>
       <c r="T70" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 66 | Other agricultural lands | Farmsteads – buildings, lanes, driveways, surrounding lots |  |Unique | |59 |74 |82 |86 |</v>
+        <v>| 66 | Other agricultural lands | Farmsteads – buildings, lanes, driveways, surrounding lots |  |Unique |&lt;sub&gt;&lt;/sub&gt; |59 |74 |82 |86 |</v>
       </c>
       <c r="U70" s="5" t="str">
-        <f t="shared" ref="T70:U103" si="11">_xlfn.CONCAT("| ",B70," | ",C70," | ",D70," | ",E70," |",F70," |",G70," |",H70," |",I70," |",J70," |",K70," |",L70," |",M70," |",N70," |")</f>
-        <v>| 66 | Other agricultural lands | Farmsteads – buildings, lanes, driveways, surrounding lots |  |Unique | |59 |74 |82 |86 | | | |</v>
-      </c>
-    </row>
-    <row r="71" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" ref="U70:U103" si="11">_xlfn.CONCAT("| ",B70," | ",C70," | ",D70," | ",E70," |",F70," |",G70," |",H70," |",I70," |",J70," |",K70," |",L70," |",M70," |",N70," |")</f>
+        <v>| 66 | Other agricultural lands | Farmsteads – buildings, lanes, driveways, surrounding lots |  |Unique |&lt;sub&gt;&lt;/sub&gt; |59 |74 |82 |86 | | | |</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="4">
         <v>67</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="E71" s="4"/>
       <c r="F71" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G71" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="H71" s="4"/>
       <c r="I71" s="4">
         <v>80</v>
@@ -5353,29 +5380,29 @@
       </c>
       <c r="T71" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 67 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Poor | | |80 |87 |93 |</v>
+        <v>| 67 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Poor |&lt;sub&gt;&lt;/sub&gt; | |80 |87 |93 |</v>
       </c>
       <c r="U71" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 67 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Poor | | |80 |87 |93 | | | |</v>
-      </c>
-    </row>
-    <row r="72" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 67 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Poor |&lt;sub&gt;&lt;/sub&gt; | |80 |87 |93 | | | |</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="4">
         <v>68</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="E72" s="4"/>
       <c r="F72" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H72" s="4"/>
       <c r="I72" s="4">
@@ -5409,29 +5436,29 @@
       </c>
       <c r="T72" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 68 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Fair |30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub. | |71 |81 |89 |</v>
+        <v>| 68 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |71 |81 |89 |</v>
       </c>
       <c r="U72" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 68 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Fair |30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub. | |71 |81 |89 | | | |</v>
-      </c>
-    </row>
-    <row r="73" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 68 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |71 |81 |89 | | | |</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" s="4">
         <v>69</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="E73" s="4"/>
       <c r="F73" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="H73" s="4"/>
       <c r="I73" s="4">
@@ -5465,28 +5492,30 @@
       </c>
       <c r="T73" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 69 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Good |&gt;70% ground cover. | |62 |74 |85 |</v>
+        <v>| 69 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Good |&lt;sub&gt;&gt;70% ground cover.&lt;/sub&gt; | |62 |74 |85 |</v>
       </c>
       <c r="U73" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 69 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Good |&gt;70% ground cover. | |62 |74 |85 | | | |</v>
-      </c>
-    </row>
-    <row r="74" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 69 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Good |&lt;sub&gt;&gt;70% ground cover.&lt;/sub&gt; | |62 |74 |85 | | | |</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" s="4">
         <v>70</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="E74" s="4"/>
       <c r="F74" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G74" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="H74" s="4"/>
       <c r="I74" s="4">
         <v>66</v>
@@ -5519,29 +5548,29 @@
       </c>
       <c r="T74" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 70 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Poor | | |66 |74 |79 |</v>
+        <v>| 70 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Poor |&lt;sub&gt;&lt;/sub&gt; | |66 |74 |79 |</v>
       </c>
       <c r="U74" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 70 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Poor | | |66 |74 |79 | | | |</v>
-      </c>
-    </row>
-    <row r="75" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 70 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Poor |&lt;sub&gt;&lt;/sub&gt; | |66 |74 |79 | | | |</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" s="4">
         <v>71</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="E75" s="4"/>
       <c r="F75" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H75" s="4"/>
       <c r="I75" s="4">
@@ -5575,29 +5604,29 @@
       </c>
       <c r="T75" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 71 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Fair |30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub. | |48 |57 |63 |</v>
+        <v>| 71 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |48 |57 |63 |</v>
       </c>
       <c r="U75" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 71 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Fair |30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub. | |48 |57 |63 | | | |</v>
-      </c>
-    </row>
-    <row r="76" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 71 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |48 |57 |63 | | | |</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" s="4">
         <v>72</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="E76" s="4"/>
       <c r="F76" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H76" s="4"/>
       <c r="I76" s="4">
@@ -5631,28 +5660,30 @@
       </c>
       <c r="T76" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 72 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Good |&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub. | |30 |41 |48 |</v>
+        <v>| 72 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Good |&lt;sub&gt;&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |30 |41 |48 |</v>
       </c>
       <c r="U76" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 72 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Good |&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub. | |30 |41 |48 | | | |</v>
-      </c>
-    </row>
-    <row r="77" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 72 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Good |&lt;sub&gt;&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |30 |41 |48 | | | |</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" s="4">
         <v>73</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="E77" s="4"/>
       <c r="F77" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G77" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="H77" s="4"/>
       <c r="I77" s="4">
         <v>75</v>
@@ -5685,29 +5716,29 @@
       </c>
       <c r="T77" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 73 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Poor | | |75 |85 |89 |</v>
+        <v>| 73 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Poor |&lt;sub&gt;&lt;/sub&gt; | |75 |85 |89 |</v>
       </c>
       <c r="U77" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 73 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Poor | | |75 |85 |89 | | | |</v>
-      </c>
-    </row>
-    <row r="78" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 73 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Poor |&lt;sub&gt;&lt;/sub&gt; | |75 |85 |89 | | | |</v>
+      </c>
+    </row>
+    <row r="78" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" s="4">
         <v>74</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="E78" s="4"/>
       <c r="F78" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="4">
@@ -5741,29 +5772,29 @@
       </c>
       <c r="T78" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 74 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Fair |30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub. | |58 |73 |80 |</v>
+        <v>| 74 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |58 |73 |80 |</v>
       </c>
       <c r="U78" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 74 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Fair |30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub. | |58 |73 |80 | | | |</v>
-      </c>
-    </row>
-    <row r="79" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 74 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |58 |73 |80 | | | |</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" s="4">
         <v>75</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="E79" s="4"/>
       <c r="F79" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H79" s="4"/>
       <c r="I79" s="4">
@@ -5797,28 +5828,30 @@
       </c>
       <c r="T79" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 75 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Good |&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub. | |41 |61 |71 |</v>
+        <v>| 75 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Good |&lt;sub&gt;&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |41 |61 |71 |</v>
       </c>
       <c r="U79" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 75 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Good |&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub. | |41 |61 |71 | | | |</v>
-      </c>
-    </row>
-    <row r="80" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 75 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Good |&lt;sub&gt;&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |41 |61 |71 | | | |</v>
+      </c>
+    </row>
+    <row r="80" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" s="4">
         <v>76</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E80" s="4"/>
       <c r="F80" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G80" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="H80" s="4"/>
       <c r="I80" s="4">
         <v>67</v>
@@ -5851,29 +5884,29 @@
       </c>
       <c r="T80" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 76 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Poor | | |67 |80 |85 |</v>
+        <v>| 76 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Poor |&lt;sub&gt;&lt;/sub&gt; | |67 |80 |85 |</v>
       </c>
       <c r="U80" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 76 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Poor | | |67 |80 |85 | | | |</v>
-      </c>
-    </row>
-    <row r="81" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 76 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Poor |&lt;sub&gt;&lt;/sub&gt; | |67 |80 |85 | | | |</v>
+      </c>
+    </row>
+    <row r="81" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B81" s="4">
         <v>77</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E81" s="4"/>
       <c r="F81" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H81" s="4"/>
       <c r="I81" s="4">
@@ -5907,29 +5940,29 @@
       </c>
       <c r="T81" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 77 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Fair |30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub. | |51 |63 |70 |</v>
+        <v>| 77 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |51 |63 |70 |</v>
       </c>
       <c r="U81" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 77 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Fair |30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub. | |51 |63 |70 | | | |</v>
-      </c>
-    </row>
-    <row r="82" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 77 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |51 |63 |70 | | | |</v>
+      </c>
+    </row>
+    <row r="82" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" s="4">
         <v>78</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E82" s="4"/>
       <c r="F82" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H82" s="4"/>
       <c r="I82" s="4">
@@ -5963,28 +5996,30 @@
       </c>
       <c r="T82" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 78 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Good |&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub. | |35 |47 |55 |</v>
+        <v>| 78 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Good |&lt;sub&gt;&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |35 |47 |55 |</v>
       </c>
       <c r="U82" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 78 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Good |&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub. | |35 |47 |55 | | | |</v>
-      </c>
-    </row>
-    <row r="83" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 78 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Good |&lt;sub&gt;&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |35 |47 |55 | | | |</v>
+      </c>
+    </row>
+    <row r="83" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" s="4">
         <v>79</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="E83" s="4"/>
       <c r="F83" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G83" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="H83" s="4">
         <v>63</v>
       </c>
@@ -6019,29 +6054,29 @@
       </c>
       <c r="T83" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 79 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Poor | |63 |77 |85 |88 |</v>
+        <v>| 79 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Poor |&lt;sub&gt;&lt;/sub&gt; |63 |77 |85 |88 |</v>
       </c>
       <c r="U83" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 79 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Poor | |63 |77 |85 |88 | | | |</v>
-      </c>
-    </row>
-    <row r="84" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 79 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Poor |&lt;sub&gt;&lt;/sub&gt; |63 |77 |85 |88 | | | |</v>
+      </c>
+    </row>
+    <row r="84" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" s="4">
         <v>80</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="E84" s="4"/>
       <c r="F84" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H84" s="4">
         <v>55</v>
@@ -6077,29 +6112,29 @@
       </c>
       <c r="T84" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 80 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Fair |30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub. |55 |72 |81 |86 |</v>
+        <v>| 80 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; |55 |72 |81 |86 |</v>
       </c>
       <c r="U84" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 80 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Fair |30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub. |55 |72 |81 |86 | | | |</v>
-      </c>
-    </row>
-    <row r="85" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 80 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; |55 |72 |81 |86 | | | |</v>
+      </c>
+    </row>
+    <row r="85" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" s="4">
         <v>81</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="E85" s="4"/>
       <c r="F85" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H85" s="4">
         <v>49</v>
@@ -6135,31 +6170,31 @@
       </c>
       <c r="T85" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 81 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Good |&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub. |49 |68 |79 |84 |</v>
+        <v>| 81 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Good |&lt;sub&gt;&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; |49 |68 |79 |84 |</v>
       </c>
       <c r="U85" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 81 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Good |&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub. |49 |68 |79 |84 | | | |</v>
-      </c>
-    </row>
-    <row r="86" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 81 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Good |&lt;sub&gt;&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; |49 |68 |79 |84 | | | |</v>
+      </c>
+    </row>
+    <row r="86" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" s="4">
         <v>82</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H86" s="4">
         <v>96</v>
@@ -6195,14 +6230,14 @@
       </c>
       <c r="T86" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 82 | Unclassified | Water body | Water body |Unique |rcfdtools |96 |96 |96 |96 |</v>
+        <v>| 82 | Unclassified | Water body | Water body |Unique |&lt;sub&gt;rcfdtools&lt;/sub&gt; |96 |96 |96 |96 |</v>
       </c>
       <c r="U86" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 82 | Unclassified | Water body | Water body |Unique |rcfdtools |96 |96 |96 |96 | | | |</v>
-      </c>
-    </row>
-    <row r="87" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| 82 | Unclassified | Water body | Water body |Unique |&lt;sub&gt;rcfdtools&lt;/sub&gt; |96 |96 |96 |96 | | | |</v>
+      </c>
+    </row>
+    <row r="87" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
@@ -6242,7 +6277,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="88" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
@@ -6282,7 +6317,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="89" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
@@ -6322,7 +6357,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="90" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -6362,7 +6397,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="91" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -6402,7 +6437,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="92" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -6442,7 +6477,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="93" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
@@ -6482,7 +6517,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="94" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
@@ -6522,7 +6557,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="95" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
@@ -6562,7 +6597,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="96" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
@@ -6602,7 +6637,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="97" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
@@ -6642,7 +6677,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="98" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
@@ -6682,7 +6717,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="99" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
@@ -6722,7 +6757,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="100" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
@@ -6762,7 +6797,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="101" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
@@ -6802,7 +6837,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="102" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
@@ -6842,7 +6877,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="103" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>

--- a/file/temp/ExcelTableToMarkDownSample2.xlsx
+++ b/file/temp/ExcelTableToMarkDownSample2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.HydroTools\file\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEE199C-2A22-45F4-9BFB-9B831CF28A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89E8000-A028-4283-BA8B-0BBC7853F13A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{D94F812B-BC61-4A22-9692-634766FE0D40}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="131">
   <si>
     <t>Creación de tablas en formato .md</t>
   </si>
@@ -61,278 +61,384 @@
     <t>Texto para 13 columnas</t>
   </si>
   <si>
-    <t>CNCode</t>
-  </si>
-  <si>
-    <t>Zone</t>
-  </si>
-  <si>
-    <t>CoverType</t>
-  </si>
-  <si>
-    <t>Treatment</t>
-  </si>
-  <si>
-    <t>HydroCond</t>
-  </si>
-  <si>
-    <t>HydroDesc</t>
-  </si>
-  <si>
-    <t>CNA</t>
-  </si>
-  <si>
-    <t>CNB</t>
-  </si>
-  <si>
-    <t>CNC</t>
-  </si>
-  <si>
-    <t>CND</t>
-  </si>
-  <si>
-    <t>Urban area</t>
-  </si>
-  <si>
-    <t>Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.)</t>
-  </si>
-  <si>
-    <t>Poor condition (grass cover &lt; 50%)</t>
-  </si>
-  <si>
-    <t>Unique</t>
-  </si>
-  <si>
-    <t>Fair condition (grass cover 50% to 75%)</t>
-  </si>
-  <si>
-    <t>Good condition (grass cover &gt; 75%)</t>
-  </si>
-  <si>
-    <t>Fully developed urban areas - Impervious areas</t>
-  </si>
-  <si>
-    <t>Paved parking lots, roofs, driveways, etc</t>
-  </si>
-  <si>
-    <t>Fully developed urban areas - Streets and roads</t>
-  </si>
-  <si>
-    <t>Paved; curbs and storm sewers</t>
-  </si>
-  <si>
-    <t>Paved; open ditches (including right-of-way)</t>
-  </si>
-  <si>
-    <t>Gravel (including right-of-way)</t>
-  </si>
-  <si>
-    <t>Dirt (including right-of-way)</t>
-  </si>
-  <si>
-    <t>Fully developed urban areas - Western desert urban areas</t>
-  </si>
-  <si>
-    <t>Natural desert landscaping (pervious areas only)</t>
-  </si>
-  <si>
-    <t>Artificial desert landscaping (impervious weed barrier, desert shrub with 1- to 2-inch sand or gravel mulch and basin borders)</t>
-  </si>
-  <si>
-    <t>Fully developed urban areas - Urban districts</t>
-  </si>
-  <si>
-    <t>Commercial and business. Average percent impervious area: 85</t>
-  </si>
-  <si>
-    <t>Industrial. Average percent impervious area: 72</t>
-  </si>
-  <si>
-    <t>Fully developed urban areas - Residential districts by average lot size</t>
-  </si>
-  <si>
-    <t>1/8 acre or less (town houses). Average percent impervious area: 65</t>
-  </si>
-  <si>
-    <t>1/4 acre. Average percent impervious area: 38</t>
-  </si>
-  <si>
-    <t>1/3 acre. Average percent impervious area: 30</t>
-  </si>
-  <si>
-    <t>1/2 acre. Average percent impervious area: 25</t>
-  </si>
-  <si>
-    <t>1 acre. Average percent impervious area: 20</t>
-  </si>
-  <si>
-    <t>2 acre. Average percent impervious area: 12</t>
-  </si>
-  <si>
-    <t>Developing urban areas</t>
-  </si>
-  <si>
-    <t>Newly graded areas (pervious areas only, no vegetation)</t>
-  </si>
-  <si>
-    <t>Cultivated agricultural lands</t>
-  </si>
-  <si>
-    <t>Fallow</t>
-  </si>
-  <si>
-    <t>Bare soil</t>
-  </si>
-  <si>
-    <t>Crop residue cover (CR)</t>
-  </si>
-  <si>
-    <t>Poor</t>
-  </si>
-  <si>
-    <t>Good</t>
-  </si>
-  <si>
-    <t>Row crops</t>
-  </si>
-  <si>
-    <t>Straight row (SR)</t>
-  </si>
-  <si>
-    <t>Straight row (SR) + Crop residue cover (CR)</t>
-  </si>
-  <si>
-    <t>Contoured (C)</t>
-  </si>
-  <si>
-    <t>Contoured (C) + Crop residue cover (CR)</t>
-  </si>
-  <si>
-    <t>Contoured &amp; terraced (C &amp; T)</t>
-  </si>
-  <si>
-    <t>Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR)</t>
-  </si>
-  <si>
-    <t>Small grain</t>
-  </si>
-  <si>
-    <t>Close-seeded or broadcast legumes or rotation meadow</t>
-  </si>
-  <si>
-    <t>Other agricultural lands</t>
-  </si>
-  <si>
-    <t>Pasture, grassland, or range – continuous forage for graving</t>
-  </si>
-  <si>
-    <t>Fair</t>
-  </si>
-  <si>
-    <t>Meadow – continuous grass, protected from grazing and generally mowed for hay</t>
-  </si>
-  <si>
-    <t>Brush – brush-weed mixture with brush the major element</t>
-  </si>
-  <si>
-    <t>Woods – grass combination (orchard or tree farm)</t>
-  </si>
-  <si>
-    <t>Woods</t>
-  </si>
-  <si>
-    <t>Farmsteads – buildings, lanes, driveways, surrounding lots</t>
-  </si>
-  <si>
-    <t>Arid and semiarid rangelands</t>
-  </si>
-  <si>
-    <t>Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element</t>
-  </si>
-  <si>
-    <t>Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush</t>
-  </si>
-  <si>
-    <t>Pinyon-juniper – pinyon, juniper, or both; grass understory</t>
-  </si>
-  <si>
-    <t>Sagebrush with grass understory</t>
-  </si>
-  <si>
-    <t>Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus.</t>
-  </si>
-  <si>
-    <t>Unclassified</t>
-  </si>
-  <si>
-    <t>Water body</t>
-  </si>
-  <si>
     <t>Texto para 10 columnas</t>
   </si>
   <si>
-    <t>&lt;sub&gt;CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type.&lt;/sub&gt;</t>
-  </si>
-  <si>
-    <t>&lt;sub&gt;&lt;/sub&gt;</t>
-  </si>
-  <si>
-    <t>&lt;sub&gt;Composite CN's for natural desert landscaping should be computed using figures 2-3 or 2-4 based on the impervious area percentage (CN = 98) and the pervious area CN. The pervious area CN's are assumed equivalent to desert shrub in poor hydrologic condition.&lt;/sub&gt;</t>
-  </si>
-  <si>
-    <t>&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt;</t>
-  </si>
-  <si>
-    <t>&lt;sub&gt;Composite CN's to use for the design of temporary measures during grading and construction should be computed using figure 2-3 or 2-4, based on the degree of development (imperviousness area percentage) and the CN's for the newly graded pervious areas.&lt;/sub&gt;</t>
-  </si>
-  <si>
-    <t>&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt;</t>
-  </si>
-  <si>
-    <t>&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt;</t>
-  </si>
-  <si>
-    <t>&lt;sub&gt;50 to 75% ground cover and not heavily grazed.&lt;/sub&gt;</t>
-  </si>
-  <si>
-    <t>&lt;sub&gt;&gt;75% ground cover and lightly or only occasionally grazed.&lt;/sub&gt;</t>
-  </si>
-  <si>
-    <t>&lt;sub&gt;50 to 75% ground cover.&lt;/sub&gt;</t>
-  </si>
-  <si>
-    <t>&lt;sub&gt;&gt;75% ground cover. Actual curve number is less than 30; use CN=30 for runoff computations.&lt;/sub&gt;</t>
-  </si>
-  <si>
-    <t>&lt;sub&gt;CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture.&lt;/sub&gt;</t>
-  </si>
-  <si>
-    <t>&lt;sub&gt;Forest litter, small trees, and brush are destroyed by heavy grazing or regular burning.&lt;/sub&gt;</t>
-  </si>
-  <si>
-    <t>&lt;sub&gt;Woods are grazed but not burned, and some forest litter covers the soil.&lt;/sub&gt;</t>
-  </si>
-  <si>
-    <t>&lt;sub&gt;Woods are protected from grazing, and litter and brush adequately cover the soil. Actual curve number is less than 30; use CN=30 for runoff computations.&lt;/sub&gt;</t>
-  </si>
-  <si>
-    <t>&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt;</t>
-  </si>
-  <si>
-    <t>&lt;sub&gt;&gt;70% ground cover.&lt;/sub&gt;</t>
-  </si>
-  <si>
-    <t>&lt;sub&gt;&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt;</t>
-  </si>
-  <si>
-    <t>&lt;sub&gt;rcfdtools&lt;/sub&gt;</t>
+    <t>Referencia</t>
+  </si>
+  <si>
+    <t>Alcance</t>
+  </si>
+  <si>
+    <t>Versión</t>
+  </si>
+  <si>
+    <t>Portal</t>
+  </si>
+  <si>
+    <t>Archivo local</t>
+  </si>
+  <si>
+    <t>IDEAM</t>
+  </si>
+  <si>
+    <t>http://www.ideam.gov.co/</t>
+  </si>
+  <si>
+    <t>IDEAM.GuiaMonitoreoVertimiento.pdf</t>
+  </si>
+  <si>
+    <t>Protocolo para el monitoreo y seguimiento del agua</t>
+  </si>
+  <si>
+    <t>IDEAM.ProtocoloMonitoreoSeguimientoAgua.2007.pdf</t>
+  </si>
+  <si>
+    <t>IDEAM.HIMAT.ManualObservadorMeteorologico.1987.pdf</t>
+  </si>
+  <si>
+    <t>IDEAM.DocumentoMetodologicoVariableMeteorologica.20180516.pdf</t>
+  </si>
+  <si>
+    <t>IGAC - Resolución 1562 año 2018</t>
+  </si>
+  <si>
+    <t>https://www.igac.gov.co/</t>
+  </si>
+  <si>
+    <t>Resolucion1562de2018.IGAC.pdf</t>
+  </si>
+  <si>
+    <t>IGAC - Resolución 471 de 2020</t>
+  </si>
+  <si>
+    <t>Resolucion471de2020.IGAC.pdf</t>
+  </si>
+  <si>
+    <t>IGAC - Resolución 715 del 2018</t>
+  </si>
+  <si>
+    <t>Resolucion715de2018.IGAC.pdf</t>
+  </si>
+  <si>
+    <t>OMM-N°0008</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/?lvl=notice_display&amp;id=5280</t>
+  </si>
+  <si>
+    <t>WMO.0008GuiaInstrumentoMetodoObservacionMeteorologico.2019.pdf</t>
+  </si>
+  <si>
+    <t>OMM-N°0100</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=10027</t>
+  </si>
+  <si>
+    <t>WMO.0100.GuiaPracticaClimatologica.2018.pdf</t>
+  </si>
+  <si>
+    <t>OMM-N°0168</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=10456</t>
+  </si>
+  <si>
+    <t>WMO.0168.GuiaPracticaHidrologicaVol1Hidrologia.2008.pdf</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=10038</t>
+  </si>
+  <si>
+    <t>WMO.0168.GuiaPracticaHidrologicaVol2Hidrologia.2011.pdf</t>
+  </si>
+  <si>
+    <t>OMM-N°0182</t>
+  </si>
+  <si>
+    <t>Vocabulario Meteorológico Internacional</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=4712</t>
+  </si>
+  <si>
+    <t>WMO.0182.VocabularioMeteorologicoInternacional.1992.pdf</t>
+  </si>
+  <si>
+    <t>OMM-N°0386</t>
+  </si>
+  <si>
+    <t>Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=10470</t>
+  </si>
+  <si>
+    <t>WMO.0386.ManualSistemaMundialTelecomunicacion.2020.pdf</t>
+  </si>
+  <si>
+    <t>OMM-N°0488</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=5440</t>
+  </si>
+  <si>
+    <t>WMO.0488.GuiaSistemaMundialObservacion.2017.pdf</t>
+  </si>
+  <si>
+    <t>OMM-N°0544</t>
+  </si>
+  <si>
+    <t>Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico</t>
+  </si>
+  <si>
+    <t>WMO.0544.ManualSistemaMundialObservacionVolumen1.2017.pdf</t>
+  </si>
+  <si>
+    <t>OMM-N°1061</t>
+  </si>
+  <si>
+    <t>Guía del Sistema de Información de la OMM</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=10258</t>
+  </si>
+  <si>
+    <t>WMO.1061.GuiaSistemaInformacionOMM.2018.pdf</t>
+  </si>
+  <si>
+    <t>OMM-N°1091</t>
+  </si>
+  <si>
+    <t>Directrices sobre los sistemas de predicción por conjuntos y la predicción</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=7774</t>
+  </si>
+  <si>
+    <t>WMO.1091.DirectricesSistemasPrediccionConjuntos.2012.pdf</t>
+  </si>
+  <si>
+    <t>OMM-N°1100</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=5742</t>
+  </si>
+  <si>
+    <t>WMO.1100.GuiaAplicacionSistemasGestionCalidadServicioMeteorologicoHidrologico.2017.pdf</t>
+  </si>
+  <si>
+    <t>OMM-N°1160</t>
+  </si>
+  <si>
+    <t>Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=10230</t>
+  </si>
+  <si>
+    <t>WMO.1160.ManualSistemaIntegradoObservacionOMM.2019.pdf</t>
+  </si>
+  <si>
+    <t>OMM-N°1165</t>
+  </si>
+  <si>
+    <t>Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=10042</t>
+  </si>
+  <si>
+    <t>WMO.1165.GuiaSistemaMundialIntegradoSistemaObservacionOMM.2019.pdf</t>
+  </si>
+  <si>
+    <t>OMM-N°1182</t>
+  </si>
+  <si>
+    <t>Directrices sobre mejores prácticas para el rescate de datos climáticos</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=3529</t>
+  </si>
+  <si>
+    <t>WMO.1182.DirectrizRescateDatoClimatico.2016.pdf</t>
+  </si>
+  <si>
+    <t>OMM-N°1192</t>
+  </si>
+  <si>
+    <t>Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=10163</t>
+  </si>
+  <si>
+    <t>WMO.1192.NormaMetadatoSistemaMundialIntegradoObservacion.2019</t>
+  </si>
+  <si>
+    <t>OMM-N°1203</t>
+  </si>
+  <si>
+    <t>Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=4167</t>
+  </si>
+  <si>
+    <t>WMO.01203.DirectricezCalculoNormalClimatica.2017.pdf</t>
+  </si>
+  <si>
+    <t>WMO-N°0199</t>
+  </si>
+  <si>
+    <t>Some Methods of Climatological Analysis</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=1961</t>
+  </si>
+  <si>
+    <t>WMO.0199.SomeMethodsClimatologicalAnalysis.1966.pdf</t>
+  </si>
+  <si>
+    <t>WMO-N°0415</t>
+  </si>
+  <si>
+    <t>On The Statistical Analysis of Series of Observations</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=1065</t>
+  </si>
+  <si>
+    <t>WMO.0415.StatisticalAnalysisSerieObservation.1990.pdf</t>
+  </si>
+  <si>
+    <t>WMO-N°0485</t>
+  </si>
+  <si>
+    <t>Manual del Sistema Mundial de Proceso de Datos y de Predicción</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=10281</t>
+  </si>
+  <si>
+    <t>WMO.0485.ManualSistemaMundialProcesoDatosPrediccion.2019.pdf</t>
+  </si>
+  <si>
+    <t>WMO-N°1131</t>
+  </si>
+  <si>
+    <t>Climate Data Management System Specifications</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=7867</t>
+  </si>
+  <si>
+    <t>WMO.1131.ClimateDataManagementSystem.2014.pdf</t>
+  </si>
+  <si>
+    <t>WMO-N°1170</t>
+  </si>
+  <si>
+    <t>Climate Services for Supporting Climate Change Adaptation</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=7936</t>
+  </si>
+  <si>
+    <t>WMO.1170.ClimateServiceForSupportingClimateChangeAdaptation.2016.pdf</t>
+  </si>
+  <si>
+    <t>WMO-N°1221</t>
+  </si>
+  <si>
+    <t>Guidelines on Quality Management in Climate Services</t>
+  </si>
+  <si>
+    <t>https://library.wmo.int/doc_num.php?explnum_id=5174</t>
+  </si>
+  <si>
+    <t>WMO.1221.GuidelinesQualityManagementClimateServices.2018.pdf</t>
+  </si>
+  <si>
+    <t>https://public.wmo.int/</t>
+  </si>
+  <si>
+    <t>ISO-19115</t>
+  </si>
+  <si>
+    <t>https://www.iso.org/standard/26020.html</t>
+  </si>
+  <si>
+    <t>ISO-IEC-11179 Partes 1 a 7</t>
+  </si>
+  <si>
+    <t>Varias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.iso.org/standard/61932.html
+</t>
+  </si>
+  <si>
+    <t>Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes</t>
+  </si>
+  <si>
+    <t>WMO</t>
+  </si>
+  <si>
+    <t>Guía para el monitoreo de vertimientos</t>
+  </si>
+  <si>
+    <t>Normas, manuales, metodologías y procedimientos asociados a actividades hidrometeorológicas</t>
+  </si>
+  <si>
+    <t>Manual del observador meteorológico</t>
+  </si>
+  <si>
+    <t>Manual de operaciones de la red hidrometeorológica</t>
+  </si>
+  <si>
+    <t>Por medio de la cual se definen los valores que representan la calidad de los puntos medidos en redes geodésicas y levantamientos geodésicos</t>
+  </si>
+  <si>
+    <t>Por medio de la cual se establecen las especificaciones técnicas mínimas que deben tener los Productos de la cartografía básica oficial de Colombia</t>
+  </si>
+  <si>
+    <t>Por la cual se actualiza el Sistema de Referencia Geocéntrico para Las Américas (SIRGAS)</t>
+  </si>
+  <si>
+    <t>Guía de Instrumentos y Métodos de Observación Meteorológicos</t>
+  </si>
+  <si>
+    <t>Guía de prácticas climatológicas</t>
+  </si>
+  <si>
+    <t>Guía de prácticas hidrológicas. Volumen I Hidrología - De la medición a la información hidrológica. Edición 2008. Actualización 2020</t>
+  </si>
+  <si>
+    <t>Guía de prácticas hidrológicas. Volumen II Hidrología - Gestión de recursos hídricos y aplicación de prácticas hidrológicas. Sexta Edición, 2011</t>
+  </si>
+  <si>
+    <t>Guía del Sistema Mundial de Observación. Edición 2010. Actualización 2017</t>
+  </si>
+  <si>
+    <t>Normas asociadas a metodologías para actividades hidrometeorológicas</t>
+  </si>
+  <si>
+    <t>https://wmo.int/wmo-no-544-manual-global-observing-system</t>
+  </si>
+  <si>
+    <t>Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB</t>
+  </si>
+  <si>
+    <t>Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -477,6 +583,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -796,7 +909,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -840,8 +953,9 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -867,8 +981,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="43" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="18" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="22" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="26" builtinId="38" customBuiltin="1"/>
@@ -902,6 +1019,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="43" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -1224,14 +1342,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B2E19A4-40DE-42A8-B3E2-A2516218588C}">
   <dimension ref="B2:U103"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="38" style="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" style="1" customWidth="1"/>
     <col min="4" max="4" width="24.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.2109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="52.640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54.85546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.0703125" style="1" customWidth="1"/>
     <col min="8" max="14" width="3.42578125" style="1" customWidth="1"/>
     <col min="15" max="15" width="2.7109375" style="1" customWidth="1"/>
@@ -1241,7 +1359,7 @@
     <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1271,73 +1389,63 @@
         <v>5</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="U2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," |")</f>
-        <v>| CNCode | Zone |</v>
+        <v>| Referencia | Alcance |</v>
       </c>
       <c r="Q3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," |")</f>
-        <v>| CNCode | Zone | CoverType |</v>
+        <v>| Referencia | Alcance | Versión |</v>
       </c>
       <c r="R3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |")</f>
-        <v>| CNCode | Zone | CoverType | Treatment |</v>
+        <v>| Referencia | Alcance | Versión | Portal |</v>
       </c>
       <c r="S3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |")</f>
-        <v>| CNCode | Zone | CoverType | Treatment |HydroCond |</v>
+        <v>| Referencia | Alcance | Versión | Portal |Archivo local |</v>
       </c>
       <c r="T3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |",G3," |",H3," |",I3," |",J3," |",K3," |")</f>
-        <v>| CNCode | Zone | CoverType | Treatment |HydroCond |HydroDesc |CNA |CNB |CNC |CND |</v>
+        <v>| Referencia | Alcance | Versión | Portal |Archivo local | | | | | |</v>
       </c>
       <c r="U3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |",G3," |",H3," |",I3," |",J3," |",K3," |",L3," |",M3," |",N3," |")</f>
-        <v>| CNCode | Zone | CoverType | Treatment |HydroCond |HydroDesc |CNA |CNB |CNC |CND | | | |</v>
-      </c>
-    </row>
-    <row r="4" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>| Referencia | Alcance | Versión | Portal |Archivo local | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
@@ -1403,4841 +1511,3611 @@
         <v>| --- | --- | --- | --- |--- |--- |--- |--- |--- |--- |--- |--- |--- |</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="5">
-        <v>1</v>
+    <row r="5" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>18</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="H5" s="5">
-        <v>68</v>
-      </c>
-      <c r="I5" s="5">
-        <v>79</v>
-      </c>
-      <c r="J5" s="5">
-        <v>86</v>
-      </c>
-      <c r="K5" s="5">
-        <v>89</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B5," | ",C5," |")</f>
-        <v>| 1 | Urban area |</v>
+        <v>| IDEAM | Guía para el monitoreo de vertimientos |</v>
       </c>
       <c r="Q5" s="5" t="str">
         <f t="shared" ref="Q5:Q24" si="1">_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," |")</f>
-        <v>| 1 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) |</v>
+        <v>| IDEAM | Guía para el monitoreo de vertimientos |  |</v>
       </c>
       <c r="R5" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," | ",E5," |")</f>
-        <v>| 1 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Poor condition (grass cover &lt; 50%) |</v>
+        <v>| IDEAM | Guía para el monitoreo de vertimientos |  | http://www.ideam.gov.co/ |</v>
       </c>
       <c r="S5" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," | ",E5," |",F5," |")</f>
-        <v>| 1 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Poor condition (grass cover &lt; 50%) |Unique |</v>
+        <v>| IDEAM | Guía para el monitoreo de vertimientos |  | http://www.ideam.gov.co/ |IDEAM.GuiaMonitoreoVertimiento.pdf |</v>
       </c>
       <c r="T5" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 1 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Poor condition (grass cover &lt; 50%) |Unique |&lt;sub&gt;CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type.&lt;/sub&gt; |68 |79 |86 |89 |</v>
+        <v>| IDEAM | Guía para el monitoreo de vertimientos |  | http://www.ideam.gov.co/ |IDEAM.GuiaMonitoreoVertimiento.pdf | | | | | |</v>
       </c>
       <c r="U5" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," | ",E5," |",F5," |",G5," |",H5," |",I5," |",J5," |",K5," |",L5," |",M5," |",N5," |")</f>
-        <v>| 1 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Poor condition (grass cover &lt; 50%) |Unique |&lt;sub&gt;CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type.&lt;/sub&gt; |68 |79 |86 |89 | | | |</v>
-      </c>
-    </row>
-    <row r="6" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="5">
-        <v>2</v>
+        <v>| IDEAM | Guía para el monitoreo de vertimientos |  | http://www.ideam.gov.co/ |IDEAM.GuiaMonitoreoVertimiento.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2007</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="H6" s="5">
-        <v>49</v>
-      </c>
-      <c r="I6" s="5">
-        <v>69</v>
-      </c>
-      <c r="J6" s="5">
-        <v>79</v>
-      </c>
-      <c r="K6" s="5">
-        <v>84</v>
-      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5" t="str">
         <f t="shared" ref="P6:P24" si="2">_xlfn.CONCAT("| ",B6," | ",C6," |")</f>
-        <v>| 2 | Urban area |</v>
+        <v>| IDEAM | Protocolo para el monitoreo y seguimiento del agua |</v>
       </c>
       <c r="Q6" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| 2 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) |</v>
+        <v>| IDEAM | Protocolo para el monitoreo y seguimiento del agua | 2007 |</v>
       </c>
       <c r="R6" s="5" t="str">
         <f t="shared" ref="R6:R67" si="3">_xlfn.CONCAT("| ",B6," | ",C6," | ",D6," | ",E6," |")</f>
-        <v>| 2 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Fair condition (grass cover 50% to 75%) |</v>
+        <v>| IDEAM | Protocolo para el monitoreo y seguimiento del agua | 2007 | http://www.ideam.gov.co/ |</v>
       </c>
       <c r="S6" s="5" t="str">
         <f t="shared" ref="S6:S69" si="4">_xlfn.CONCAT("| ",B6," | ",C6," | ",D6," | ",E6," |",F6," |")</f>
-        <v>| 2 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Fair condition (grass cover 50% to 75%) |Unique |</v>
+        <v>| IDEAM | Protocolo para el monitoreo y seguimiento del agua | 2007 | http://www.ideam.gov.co/ |IDEAM.ProtocoloMonitoreoSeguimientoAgua.2007.pdf |</v>
       </c>
       <c r="T6" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 2 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Fair condition (grass cover 50% to 75%) |Unique |&lt;sub&gt;CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type.&lt;/sub&gt; |49 |69 |79 |84 |</v>
+        <v>| IDEAM | Protocolo para el monitoreo y seguimiento del agua | 2007 | http://www.ideam.gov.co/ |IDEAM.ProtocoloMonitoreoSeguimientoAgua.2007.pdf | | | | | |</v>
       </c>
       <c r="U6" s="5" t="str">
         <f t="shared" ref="U6:U69" si="5">_xlfn.CONCAT("| ",B6," | ",C6," | ",D6," | ",E6," |",F6," |",G6," |",H6," |",I6," |",J6," |",K6," |",L6," |",M6," |",N6," |")</f>
-        <v>| 2 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Fair condition (grass cover 50% to 75%) |Unique |&lt;sub&gt;CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type.&lt;/sub&gt; |49 |69 |79 |84 | | | |</v>
-      </c>
-    </row>
-    <row r="7" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="5">
-        <v>3</v>
+        <v>| IDEAM | Protocolo para el monitoreo y seguimiento del agua | 2007 | http://www.ideam.gov.co/ |IDEAM.ProtocoloMonitoreoSeguimientoAgua.2007.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>18</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="H7" s="5">
-        <v>39</v>
-      </c>
-      <c r="I7" s="5">
-        <v>61</v>
-      </c>
-      <c r="J7" s="5">
-        <v>74</v>
-      </c>
-      <c r="K7" s="5">
-        <v>80</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
       <c r="P7" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| 3 | Urban area |</v>
+        <v>| IDEAM | Normas, manuales, metodologías y procedimientos asociados a actividades hidrometeorológicas |</v>
       </c>
       <c r="Q7" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| 3 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) |</v>
+        <v>| IDEAM | Normas, manuales, metodologías y procedimientos asociados a actividades hidrometeorológicas |  |</v>
       </c>
       <c r="R7" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 3 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Good condition (grass cover &gt; 75%) |</v>
+        <v>| IDEAM | Normas, manuales, metodologías y procedimientos asociados a actividades hidrometeorológicas |  | http://www.ideam.gov.co/ |</v>
       </c>
       <c r="S7" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 3 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Good condition (grass cover &gt; 75%) |Unique |</v>
+        <v>| IDEAM | Normas, manuales, metodologías y procedimientos asociados a actividades hidrometeorológicas |  | http://www.ideam.gov.co/ | |</v>
       </c>
       <c r="T7" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 3 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Good condition (grass cover &gt; 75%) |Unique |&lt;sub&gt;CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type.&lt;/sub&gt; |39 |61 |74 |80 |</v>
+        <v>| IDEAM | Normas, manuales, metodologías y procedimientos asociados a actividades hidrometeorológicas |  | http://www.ideam.gov.co/ | | | | | | |</v>
       </c>
       <c r="U7" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 3 | Urban area | Fully developed urban areas - Open space (lawns, parks, golf courses, cemeteries, etc.) | Good condition (grass cover &gt; 75%) |Unique |&lt;sub&gt;CN's shown are equivalent to those of pasture. Composite CN's may be computed for other combinations of open space cover type.&lt;/sub&gt; |39 |61 |74 |80 | | | |</v>
-      </c>
-    </row>
-    <row r="8" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="5">
-        <v>4</v>
+        <v>| IDEAM | Normas, manuales, metodologías y procedimientos asociados a actividades hidrometeorológicas |  | http://www.ideam.gov.co/ | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>23</v>
+        <v>117</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1987</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H8" s="5">
-        <v>98</v>
-      </c>
-      <c r="I8" s="5">
-        <v>98</v>
-      </c>
-      <c r="J8" s="5">
-        <v>98</v>
-      </c>
-      <c r="K8" s="5">
-        <v>98</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| 4 | Urban area |</v>
+        <v>| IDEAM | Manual del observador meteorológico |</v>
       </c>
       <c r="Q8" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| 4 | Urban area | Fully developed urban areas - Impervious areas |</v>
+        <v>| IDEAM | Manual del observador meteorológico | 1987 |</v>
       </c>
       <c r="R8" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 4 | Urban area | Fully developed urban areas - Impervious areas | Paved parking lots, roofs, driveways, etc |</v>
+        <v>| IDEAM | Manual del observador meteorológico | 1987 | http://www.ideam.gov.co/ |</v>
       </c>
       <c r="S8" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 4 | Urban area | Fully developed urban areas - Impervious areas | Paved parking lots, roofs, driveways, etc |Unique |</v>
+        <v>| IDEAM | Manual del observador meteorológico | 1987 | http://www.ideam.gov.co/ |IDEAM.HIMAT.ManualObservadorMeteorologico.1987.pdf |</v>
       </c>
       <c r="T8" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 4 | Urban area | Fully developed urban areas - Impervious areas | Paved parking lots, roofs, driveways, etc |Unique |&lt;sub&gt;&lt;/sub&gt; |98 |98 |98 |98 |</v>
+        <v>| IDEAM | Manual del observador meteorológico | 1987 | http://www.ideam.gov.co/ |IDEAM.HIMAT.ManualObservadorMeteorologico.1987.pdf | | | | | |</v>
       </c>
       <c r="U8" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 4 | Urban area | Fully developed urban areas - Impervious areas | Paved parking lots, roofs, driveways, etc |Unique |&lt;sub&gt;&lt;/sub&gt; |98 |98 |98 |98 | | | |</v>
-      </c>
-    </row>
-    <row r="9" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="5">
-        <v>5</v>
+        <v>| IDEAM | Manual del observador meteorológico | 1987 | http://www.ideam.gov.co/ |IDEAM.HIMAT.ManualObservadorMeteorologico.1987.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>25</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H9" s="5">
-        <v>98</v>
-      </c>
-      <c r="I9" s="5">
-        <v>98</v>
-      </c>
-      <c r="J9" s="5">
-        <v>98</v>
-      </c>
-      <c r="K9" s="5">
-        <v>98</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
       <c r="P9" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| 5 | Urban area |</v>
+        <v>| IDEAM | Manual de operaciones de la red hidrometeorológica |</v>
       </c>
       <c r="Q9" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| 5 | Urban area | Fully developed urban areas - Streets and roads |</v>
+        <v>| IDEAM | Manual de operaciones de la red hidrometeorológica |  |</v>
       </c>
       <c r="R9" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 5 | Urban area | Fully developed urban areas - Streets and roads | Paved; curbs and storm sewers |</v>
+        <v>| IDEAM | Manual de operaciones de la red hidrometeorológica |  | http://www.ideam.gov.co/ |</v>
       </c>
       <c r="S9" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 5 | Urban area | Fully developed urban areas - Streets and roads | Paved; curbs and storm sewers |Unique |</v>
+        <v>| IDEAM | Manual de operaciones de la red hidrometeorológica |  | http://www.ideam.gov.co/ | |</v>
       </c>
       <c r="T9" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 5 | Urban area | Fully developed urban areas - Streets and roads | Paved; curbs and storm sewers |Unique |&lt;sub&gt;&lt;/sub&gt; |98 |98 |98 |98 |</v>
+        <v>| IDEAM | Manual de operaciones de la red hidrometeorológica |  | http://www.ideam.gov.co/ | | | | | | |</v>
       </c>
       <c r="U9" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 5 | Urban area | Fully developed urban areas - Streets and roads | Paved; curbs and storm sewers |Unique |&lt;sub&gt;&lt;/sub&gt; |98 |98 |98 |98 | | | |</v>
-      </c>
-    </row>
-    <row r="10" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="5">
-        <v>6</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>27</v>
+        <v>| IDEAM | Manual de operaciones de la red hidrometeorológica |  | http://www.ideam.gov.co/ | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5">
+        <v>2018</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>14</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H10" s="5">
-        <v>83</v>
-      </c>
-      <c r="I10" s="5">
-        <v>89</v>
-      </c>
-      <c r="J10" s="5">
-        <v>92</v>
-      </c>
-      <c r="K10" s="5">
-        <v>93</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
       <c r="P10" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| 6 | Urban area |</v>
+        <v>| IDEAM |  |</v>
       </c>
       <c r="Q10" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| 6 | Urban area | Fully developed urban areas - Streets and roads |</v>
+        <v>| IDEAM |  | 2018 |</v>
       </c>
       <c r="R10" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 6 | Urban area | Fully developed urban areas - Streets and roads | Paved; open ditches (including right-of-way) |</v>
+        <v>| IDEAM |  | 2018 | http://www.ideam.gov.co/ |</v>
       </c>
       <c r="S10" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 6 | Urban area | Fully developed urban areas - Streets and roads | Paved; open ditches (including right-of-way) |Unique |</v>
+        <v>| IDEAM |  | 2018 | http://www.ideam.gov.co/ |IDEAM.DocumentoMetodologicoVariableMeteorologica.20180516.pdf |</v>
       </c>
       <c r="T10" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 6 | Urban area | Fully developed urban areas - Streets and roads | Paved; open ditches (including right-of-way) |Unique |&lt;sub&gt;&lt;/sub&gt; |83 |89 |92 |93 |</v>
+        <v>| IDEAM |  | 2018 | http://www.ideam.gov.co/ |IDEAM.DocumentoMetodologicoVariableMeteorologica.20180516.pdf | | | | | |</v>
       </c>
       <c r="U10" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 6 | Urban area | Fully developed urban areas - Streets and roads | Paved; open ditches (including right-of-way) |Unique |&lt;sub&gt;&lt;/sub&gt; |83 |89 |92 |93 | | | |</v>
-      </c>
-    </row>
-    <row r="11" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="5">
-        <v>7</v>
+        <v>| IDEAM |  | 2018 | http://www.ideam.gov.co/ |IDEAM.DocumentoMetodologicoVariableMeteorologica.20180516.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>25</v>
+        <v>119</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2018</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H11" s="5">
-        <v>76</v>
-      </c>
-      <c r="I11" s="5">
-        <v>85</v>
-      </c>
-      <c r="J11" s="5">
-        <v>89</v>
-      </c>
-      <c r="K11" s="5">
-        <v>91</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
       <c r="P11" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| 7 | Urban area |</v>
+        <v>| IGAC - Resolución 1562 año 2018 | Por medio de la cual se definen los valores que representan la calidad de los puntos medidos en redes geodésicas y levantamientos geodésicos |</v>
       </c>
       <c r="Q11" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| 7 | Urban area | Fully developed urban areas - Streets and roads |</v>
+        <v>| IGAC - Resolución 1562 año 2018 | Por medio de la cual se definen los valores que representan la calidad de los puntos medidos en redes geodésicas y levantamientos geodésicos | 2018 |</v>
       </c>
       <c r="R11" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 7 | Urban area | Fully developed urban areas - Streets and roads | Gravel (including right-of-way) |</v>
+        <v>| IGAC - Resolución 1562 año 2018 | Por medio de la cual se definen los valores que representan la calidad de los puntos medidos en redes geodésicas y levantamientos geodésicos | 2018 | https://www.igac.gov.co/ |</v>
       </c>
       <c r="S11" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 7 | Urban area | Fully developed urban areas - Streets and roads | Gravel (including right-of-way) |Unique |</v>
+        <v>| IGAC - Resolución 1562 año 2018 | Por medio de la cual se definen los valores que representan la calidad de los puntos medidos en redes geodésicas y levantamientos geodésicos | 2018 | https://www.igac.gov.co/ |Resolucion1562de2018.IGAC.pdf |</v>
       </c>
       <c r="T11" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 7 | Urban area | Fully developed urban areas - Streets and roads | Gravel (including right-of-way) |Unique |&lt;sub&gt;&lt;/sub&gt; |76 |85 |89 |91 |</v>
+        <v>| IGAC - Resolución 1562 año 2018 | Por medio de la cual se definen los valores que representan la calidad de los puntos medidos en redes geodésicas y levantamientos geodésicos | 2018 | https://www.igac.gov.co/ |Resolucion1562de2018.IGAC.pdf | | | | | |</v>
       </c>
       <c r="U11" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 7 | Urban area | Fully developed urban areas - Streets and roads | Gravel (including right-of-way) |Unique |&lt;sub&gt;&lt;/sub&gt; |76 |85 |89 |91 | | | |</v>
-      </c>
-    </row>
-    <row r="12" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="5">
-        <v>8</v>
+        <v>| IGAC - Resolución 1562 año 2018 | Por medio de la cual se definen los valores que representan la calidad de los puntos medidos en redes geodésicas y levantamientos geodésicos | 2018 | https://www.igac.gov.co/ |Resolucion1562de2018.IGAC.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>25</v>
+        <v>120</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2020</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H12" s="5">
-        <v>72</v>
-      </c>
-      <c r="I12" s="5">
-        <v>82</v>
-      </c>
-      <c r="J12" s="5">
-        <v>87</v>
-      </c>
-      <c r="K12" s="5">
-        <v>89</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
       <c r="P12" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| 8 | Urban area |</v>
+        <v>| IGAC - Resolución 471 de 2020 | Por medio de la cual se establecen las especificaciones técnicas mínimas que deben tener los Productos de la cartografía básica oficial de Colombia |</v>
       </c>
       <c r="Q12" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| 8 | Urban area | Fully developed urban areas - Streets and roads |</v>
+        <v>| IGAC - Resolución 471 de 2020 | Por medio de la cual se establecen las especificaciones técnicas mínimas que deben tener los Productos de la cartografía básica oficial de Colombia | 2020 |</v>
       </c>
       <c r="R12" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 8 | Urban area | Fully developed urban areas - Streets and roads | Dirt (including right-of-way) |</v>
+        <v>| IGAC - Resolución 471 de 2020 | Por medio de la cual se establecen las especificaciones técnicas mínimas que deben tener los Productos de la cartografía básica oficial de Colombia | 2020 | https://www.igac.gov.co/ |</v>
       </c>
       <c r="S12" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 8 | Urban area | Fully developed urban areas - Streets and roads | Dirt (including right-of-way) |Unique |</v>
+        <v>| IGAC - Resolución 471 de 2020 | Por medio de la cual se establecen las especificaciones técnicas mínimas que deben tener los Productos de la cartografía básica oficial de Colombia | 2020 | https://www.igac.gov.co/ |Resolucion471de2020.IGAC.pdf |</v>
       </c>
       <c r="T12" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 8 | Urban area | Fully developed urban areas - Streets and roads | Dirt (including right-of-way) |Unique |&lt;sub&gt;&lt;/sub&gt; |72 |82 |87 |89 |</v>
+        <v>| IGAC - Resolución 471 de 2020 | Por medio de la cual se establecen las especificaciones técnicas mínimas que deben tener los Productos de la cartografía básica oficial de Colombia | 2020 | https://www.igac.gov.co/ |Resolucion471de2020.IGAC.pdf | | | | | |</v>
       </c>
       <c r="U12" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 8 | Urban area | Fully developed urban areas - Streets and roads | Dirt (including right-of-way) |Unique |&lt;sub&gt;&lt;/sub&gt; |72 |82 |87 |89 | | | |</v>
-      </c>
-    </row>
-    <row r="13" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="5">
-        <v>9</v>
+        <v>| IGAC - Resolución 471 de 2020 | Por medio de la cual se establecen las especificaciones técnicas mínimas que deben tener los Productos de la cartografía básica oficial de Colombia | 2020 | https://www.igac.gov.co/ |Resolucion471de2020.IGAC.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>30</v>
+        <v>121</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2018</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H13" s="5">
-        <v>63</v>
-      </c>
-      <c r="I13" s="5">
-        <v>77</v>
-      </c>
-      <c r="J13" s="5">
-        <v>85</v>
-      </c>
-      <c r="K13" s="5">
-        <v>88</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
       <c r="P13" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| 9 | Urban area |</v>
+        <v>| IGAC - Resolución 715 del 2018 | Por la cual se actualiza el Sistema de Referencia Geocéntrico para Las Américas (SIRGAS) |</v>
       </c>
       <c r="Q13" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| 9 | Urban area | Fully developed urban areas - Western desert urban areas |</v>
+        <v>| IGAC - Resolución 715 del 2018 | Por la cual se actualiza el Sistema de Referencia Geocéntrico para Las Américas (SIRGAS) | 2018 |</v>
       </c>
       <c r="R13" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 9 | Urban area | Fully developed urban areas - Western desert urban areas | Natural desert landscaping (pervious areas only) |</v>
+        <v>| IGAC - Resolución 715 del 2018 | Por la cual se actualiza el Sistema de Referencia Geocéntrico para Las Américas (SIRGAS) | 2018 | https://www.igac.gov.co/ |</v>
       </c>
       <c r="S13" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 9 | Urban area | Fully developed urban areas - Western desert urban areas | Natural desert landscaping (pervious areas only) |Unique |</v>
+        <v>| IGAC - Resolución 715 del 2018 | Por la cual se actualiza el Sistema de Referencia Geocéntrico para Las Américas (SIRGAS) | 2018 | https://www.igac.gov.co/ |Resolucion715de2018.IGAC.pdf |</v>
       </c>
       <c r="T13" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 9 | Urban area | Fully developed urban areas - Western desert urban areas | Natural desert landscaping (pervious areas only) |Unique |&lt;sub&gt;Composite CN's for natural desert landscaping should be computed using figures 2-3 or 2-4 based on the impervious area percentage (CN = 98) and the pervious area CN. The pervious area CN's are assumed equivalent to desert shrub in poor hydrologic condition.&lt;/sub&gt; |63 |77 |85 |88 |</v>
+        <v>| IGAC - Resolución 715 del 2018 | Por la cual se actualiza el Sistema de Referencia Geocéntrico para Las Américas (SIRGAS) | 2018 | https://www.igac.gov.co/ |Resolucion715de2018.IGAC.pdf | | | | | |</v>
       </c>
       <c r="U13" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 9 | Urban area | Fully developed urban areas - Western desert urban areas | Natural desert landscaping (pervious areas only) |Unique |&lt;sub&gt;Composite CN's for natural desert landscaping should be computed using figures 2-3 or 2-4 based on the impervious area percentage (CN = 98) and the pervious area CN. The pervious area CN's are assumed equivalent to desert shrub in poor hydrologic condition.&lt;/sub&gt; |63 |77 |85 |88 | | | |</v>
-      </c>
-    </row>
-    <row r="14" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="5">
-        <v>10</v>
+        <v>| IGAC - Resolución 715 del 2018 | Por la cual se actualiza el Sistema de Referencia Geocéntrico para Las Américas (SIRGAS) | 2018 | https://www.igac.gov.co/ |Resolucion715de2018.IGAC.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="14" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>30</v>
+        <v>122</v>
+      </c>
+      <c r="D14" s="5">
+        <v>2019</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H14" s="5">
-        <v>96</v>
-      </c>
-      <c r="I14" s="5">
-        <v>96</v>
-      </c>
-      <c r="J14" s="5">
-        <v>96</v>
-      </c>
-      <c r="K14" s="5">
-        <v>96</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
       <c r="P14" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| 10 | Urban area |</v>
+        <v>| OMM-N°0008 | Guía de Instrumentos y Métodos de Observación Meteorológicos |</v>
       </c>
       <c r="Q14" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| 10 | Urban area | Fully developed urban areas - Western desert urban areas |</v>
+        <v>| OMM-N°0008 | Guía de Instrumentos y Métodos de Observación Meteorológicos | 2019 |</v>
       </c>
       <c r="R14" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 10 | Urban area | Fully developed urban areas - Western desert urban areas | Artificial desert landscaping (impervious weed barrier, desert shrub with 1- to 2-inch sand or gravel mulch and basin borders) |</v>
+        <v>| OMM-N°0008 | Guía de Instrumentos y Métodos de Observación Meteorológicos | 2019 | https://library.wmo.int/?lvl=notice_display&amp;id=5280 |</v>
       </c>
       <c r="S14" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 10 | Urban area | Fully developed urban areas - Western desert urban areas | Artificial desert landscaping (impervious weed barrier, desert shrub with 1- to 2-inch sand or gravel mulch and basin borders) |Unique |</v>
+        <v>| OMM-N°0008 | Guía de Instrumentos y Métodos de Observación Meteorológicos | 2019 | https://library.wmo.int/?lvl=notice_display&amp;id=5280 |WMO.0008GuiaInstrumentoMetodoObservacionMeteorologico.2019.pdf |</v>
       </c>
       <c r="T14" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 10 | Urban area | Fully developed urban areas - Western desert urban areas | Artificial desert landscaping (impervious weed barrier, desert shrub with 1- to 2-inch sand or gravel mulch and basin borders) |Unique |&lt;sub&gt;&lt;/sub&gt; |96 |96 |96 |96 |</v>
+        <v>| OMM-N°0008 | Guía de Instrumentos y Métodos de Observación Meteorológicos | 2019 | https://library.wmo.int/?lvl=notice_display&amp;id=5280 |WMO.0008GuiaInstrumentoMetodoObservacionMeteorologico.2019.pdf | | | | | |</v>
       </c>
       <c r="U14" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 10 | Urban area | Fully developed urban areas - Western desert urban areas | Artificial desert landscaping (impervious weed barrier, desert shrub with 1- to 2-inch sand or gravel mulch and basin borders) |Unique |&lt;sub&gt;&lt;/sub&gt; |96 |96 |96 |96 | | | |</v>
-      </c>
-    </row>
-    <row r="15" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="5">
-        <v>11</v>
+        <v>| OMM-N°0008 | Guía de Instrumentos y Métodos de Observación Meteorológicos | 2019 | https://library.wmo.int/?lvl=notice_display&amp;id=5280 |WMO.0008GuiaInstrumentoMetodoObservacionMeteorologico.2019.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="15" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>33</v>
+        <v>123</v>
+      </c>
+      <c r="D15" s="5">
+        <v>2018</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H15" s="5">
-        <v>89</v>
-      </c>
-      <c r="I15" s="5">
-        <v>92</v>
-      </c>
-      <c r="J15" s="5">
-        <v>94</v>
-      </c>
-      <c r="K15" s="5">
-        <v>95</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
       <c r="P15" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| 11 | Urban area |</v>
+        <v>| OMM-N°0100 | Guía de prácticas climatológicas |</v>
       </c>
       <c r="Q15" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| 11 | Urban area | Fully developed urban areas - Urban districts |</v>
+        <v>| OMM-N°0100 | Guía de prácticas climatológicas | 2018 |</v>
       </c>
       <c r="R15" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 11 | Urban area | Fully developed urban areas - Urban districts | Commercial and business. Average percent impervious area: 85 |</v>
+        <v>| OMM-N°0100 | Guía de prácticas climatológicas | 2018 | https://library.wmo.int/doc_num.php?explnum_id=10027 |</v>
       </c>
       <c r="S15" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 11 | Urban area | Fully developed urban areas - Urban districts | Commercial and business. Average percent impervious area: 85 |Unique |</v>
+        <v>| OMM-N°0100 | Guía de prácticas climatológicas | 2018 | https://library.wmo.int/doc_num.php?explnum_id=10027 |WMO.0100.GuiaPracticaClimatologica.2018.pdf |</v>
       </c>
       <c r="T15" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 11 | Urban area | Fully developed urban areas - Urban districts | Commercial and business. Average percent impervious area: 85 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |89 |92 |94 |95 |</v>
+        <v>| OMM-N°0100 | Guía de prácticas climatológicas | 2018 | https://library.wmo.int/doc_num.php?explnum_id=10027 |WMO.0100.GuiaPracticaClimatologica.2018.pdf | | | | | |</v>
       </c>
       <c r="U15" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 11 | Urban area | Fully developed urban areas - Urban districts | Commercial and business. Average percent impervious area: 85 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |89 |92 |94 |95 | | | |</v>
-      </c>
-    </row>
-    <row r="16" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="5">
-        <v>12</v>
+        <v>| OMM-N°0100 | Guía de prácticas climatológicas | 2018 | https://library.wmo.int/doc_num.php?explnum_id=10027 |WMO.0100.GuiaPracticaClimatologica.2018.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21" ht="61.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>33</v>
+        <v>124</v>
+      </c>
+      <c r="D16" s="5">
+        <v>2008</v>
       </c>
       <c r="E16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H16" s="5">
-        <v>81</v>
-      </c>
-      <c r="I16" s="5">
-        <v>88</v>
-      </c>
-      <c r="J16" s="5">
-        <v>91</v>
-      </c>
-      <c r="K16" s="5">
-        <v>93</v>
-      </c>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
       <c r="P16" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| 12 | Urban area |</v>
+        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen I Hidrología - De la medición a la información hidrológica. Edición 2008. Actualización 2020 |</v>
       </c>
       <c r="Q16" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| 12 | Urban area | Fully developed urban areas - Urban districts |</v>
+        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen I Hidrología - De la medición a la información hidrológica. Edición 2008. Actualización 2020 | 2008 |</v>
       </c>
       <c r="R16" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 12 | Urban area | Fully developed urban areas - Urban districts | Industrial. Average percent impervious area: 72 |</v>
+        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen I Hidrología - De la medición a la información hidrológica. Edición 2008. Actualización 2020 | 2008 | https://library.wmo.int/doc_num.php?explnum_id=10456 |</v>
       </c>
       <c r="S16" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 12 | Urban area | Fully developed urban areas - Urban districts | Industrial. Average percent impervious area: 72 |Unique |</v>
+        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen I Hidrología - De la medición a la información hidrológica. Edición 2008. Actualización 2020 | 2008 | https://library.wmo.int/doc_num.php?explnum_id=10456 |WMO.0168.GuiaPracticaHidrologicaVol1Hidrologia.2008.pdf |</v>
       </c>
       <c r="T16" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 12 | Urban area | Fully developed urban areas - Urban districts | Industrial. Average percent impervious area: 72 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |81 |88 |91 |93 |</v>
+        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen I Hidrología - De la medición a la información hidrológica. Edición 2008. Actualización 2020 | 2008 | https://library.wmo.int/doc_num.php?explnum_id=10456 |WMO.0168.GuiaPracticaHidrologicaVol1Hidrologia.2008.pdf | | | | | |</v>
       </c>
       <c r="U16" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 12 | Urban area | Fully developed urban areas - Urban districts | Industrial. Average percent impervious area: 72 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |81 |88 |91 |93 | | | |</v>
-      </c>
-    </row>
-    <row r="17" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="5">
-        <v>13</v>
+        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen I Hidrología - De la medición a la información hidrológica. Edición 2008. Actualización 2020 | 2008 | https://library.wmo.int/doc_num.php?explnum_id=10456 |WMO.0168.GuiaPracticaHidrologicaVol1Hidrologia.2008.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="17" spans="2:21" ht="61.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17" s="5">
+        <v>2011</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" s="5">
-        <v>77</v>
-      </c>
-      <c r="I17" s="5">
-        <v>85</v>
-      </c>
-      <c r="J17" s="5">
-        <v>90</v>
-      </c>
-      <c r="K17" s="5">
-        <v>92</v>
-      </c>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
       <c r="P17" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| 13 | Urban area |</v>
+        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen II Hidrología - Gestión de recursos hídricos y aplicación de prácticas hidrológicas. Sexta Edición, 2011 |</v>
       </c>
       <c r="Q17" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| 13 | Urban area | Fully developed urban areas - Residential districts by average lot size |</v>
+        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen II Hidrología - Gestión de recursos hídricos y aplicación de prácticas hidrológicas. Sexta Edición, 2011 | 2011 |</v>
       </c>
       <c r="R17" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 13 | Urban area | Fully developed urban areas - Residential districts by average lot size | 1/8 acre or less (town houses). Average percent impervious area: 65 |</v>
+        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen II Hidrología - Gestión de recursos hídricos y aplicación de prácticas hidrológicas. Sexta Edición, 2011 | 2011 | https://library.wmo.int/doc_num.php?explnum_id=10038 |</v>
       </c>
       <c r="S17" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 13 | Urban area | Fully developed urban areas - Residential districts by average lot size | 1/8 acre or less (town houses). Average percent impervious area: 65 |Unique |</v>
+        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen II Hidrología - Gestión de recursos hídricos y aplicación de prácticas hidrológicas. Sexta Edición, 2011 | 2011 | https://library.wmo.int/doc_num.php?explnum_id=10038 |WMO.0168.GuiaPracticaHidrologicaVol2Hidrologia.2011.pdf |</v>
       </c>
       <c r="T17" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 13 | Urban area | Fully developed urban areas - Residential districts by average lot size | 1/8 acre or less (town houses). Average percent impervious area: 65 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |77 |85 |90 |92 |</v>
+        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen II Hidrología - Gestión de recursos hídricos y aplicación de prácticas hidrológicas. Sexta Edición, 2011 | 2011 | https://library.wmo.int/doc_num.php?explnum_id=10038 |WMO.0168.GuiaPracticaHidrologicaVol2Hidrologia.2011.pdf | | | | | |</v>
       </c>
       <c r="U17" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 13 | Urban area | Fully developed urban areas - Residential districts by average lot size | 1/8 acre or less (town houses). Average percent impervious area: 65 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |77 |85 |90 |92 | | | |</v>
-      </c>
-    </row>
-    <row r="18" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="5">
-        <v>14</v>
+        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen II Hidrología - Gestión de recursos hídricos y aplicación de prácticas hidrológicas. Sexta Edición, 2011 | 2011 | https://library.wmo.int/doc_num.php?explnum_id=10038 |WMO.0168.GuiaPracticaHidrologicaVol2Hidrologia.2011.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="18" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>33</v>
+        <v>39</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1992</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H18" s="5">
-        <v>61</v>
-      </c>
-      <c r="I18" s="5">
-        <v>75</v>
-      </c>
-      <c r="J18" s="5">
-        <v>83</v>
-      </c>
-      <c r="K18" s="5">
-        <v>87</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
       <c r="P18" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| 14 | Urban area |</v>
+        <v>| OMM-N°0182 | Vocabulario Meteorológico Internacional |</v>
       </c>
       <c r="Q18" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| 14 | Urban area | Fully developed urban areas - Urban districts |</v>
+        <v>| OMM-N°0182 | Vocabulario Meteorológico Internacional | 1992 |</v>
       </c>
       <c r="R18" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 14 | Urban area | Fully developed urban areas - Urban districts | 1/4 acre. Average percent impervious area: 38 |</v>
+        <v>| OMM-N°0182 | Vocabulario Meteorológico Internacional | 1992 | https://library.wmo.int/doc_num.php?explnum_id=4712 |</v>
       </c>
       <c r="S18" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 14 | Urban area | Fully developed urban areas - Urban districts | 1/4 acre. Average percent impervious area: 38 |Unique |</v>
+        <v>| OMM-N°0182 | Vocabulario Meteorológico Internacional | 1992 | https://library.wmo.int/doc_num.php?explnum_id=4712 |WMO.0182.VocabularioMeteorologicoInternacional.1992.pdf |</v>
       </c>
       <c r="T18" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 14 | Urban area | Fully developed urban areas - Urban districts | 1/4 acre. Average percent impervious area: 38 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |61 |75 |83 |87 |</v>
+        <v>| OMM-N°0182 | Vocabulario Meteorológico Internacional | 1992 | https://library.wmo.int/doc_num.php?explnum_id=4712 |WMO.0182.VocabularioMeteorologicoInternacional.1992.pdf | | | | | |</v>
       </c>
       <c r="U18" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 14 | Urban area | Fully developed urban areas - Urban districts | 1/4 acre. Average percent impervious area: 38 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |61 |75 |83 |87 | | | |</v>
-      </c>
-    </row>
-    <row r="19" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="5">
-        <v>15</v>
+        <v>| OMM-N°0182 | Vocabulario Meteorológico Internacional | 1992 | https://library.wmo.int/doc_num.php?explnum_id=4712 |WMO.0182.VocabularioMeteorologicoInternacional.1992.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="19" spans="2:21" ht="61.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>33</v>
+        <v>43</v>
+      </c>
+      <c r="D19" s="5">
+        <v>2020</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H19" s="5">
-        <v>57</v>
-      </c>
-      <c r="I19" s="5">
-        <v>72</v>
-      </c>
-      <c r="J19" s="5">
-        <v>81</v>
-      </c>
-      <c r="K19" s="5">
-        <v>86</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
       <c r="P19" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| 15 | Urban area |</v>
+        <v>| OMM-N°0386 | Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM |</v>
       </c>
       <c r="Q19" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| 15 | Urban area | Fully developed urban areas - Urban districts |</v>
+        <v>| OMM-N°0386 | Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM | 2020 |</v>
       </c>
       <c r="R19" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 15 | Urban area | Fully developed urban areas - Urban districts | 1/3 acre. Average percent impervious area: 30 |</v>
+        <v>| OMM-N°0386 | Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM | 2020 | https://library.wmo.int/doc_num.php?explnum_id=10470 |</v>
       </c>
       <c r="S19" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 15 | Urban area | Fully developed urban areas - Urban districts | 1/3 acre. Average percent impervious area: 30 |Unique |</v>
+        <v>| OMM-N°0386 | Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM | 2020 | https://library.wmo.int/doc_num.php?explnum_id=10470 |WMO.0386.ManualSistemaMundialTelecomunicacion.2020.pdf |</v>
       </c>
       <c r="T19" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 15 | Urban area | Fully developed urban areas - Urban districts | 1/3 acre. Average percent impervious area: 30 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |57 |72 |81 |86 |</v>
+        <v>| OMM-N°0386 | Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM | 2020 | https://library.wmo.int/doc_num.php?explnum_id=10470 |WMO.0386.ManualSistemaMundialTelecomunicacion.2020.pdf | | | | | |</v>
       </c>
       <c r="U19" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 15 | Urban area | Fully developed urban areas - Urban districts | 1/3 acre. Average percent impervious area: 30 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |57 |72 |81 |86 | | | |</v>
-      </c>
-    </row>
-    <row r="20" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="5">
-        <v>16</v>
+        <v>| OMM-N°0386 | Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM | 2020 | https://library.wmo.int/doc_num.php?explnum_id=10470 |WMO.0386.ManualSistemaMundialTelecomunicacion.2020.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="20" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>33</v>
+        <v>126</v>
+      </c>
+      <c r="D20" s="5">
+        <v>2017</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H20" s="5">
-        <v>54</v>
-      </c>
-      <c r="I20" s="5">
-        <v>70</v>
-      </c>
-      <c r="J20" s="5">
-        <v>80</v>
-      </c>
-      <c r="K20" s="5">
-        <v>85</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
       <c r="P20" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| 16 | Urban area |</v>
+        <v>| OMM-N°0488 | Guía del Sistema Mundial de Observación. Edición 2010. Actualización 2017 |</v>
       </c>
       <c r="Q20" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| 16 | Urban area | Fully developed urban areas - Urban districts |</v>
+        <v>| OMM-N°0488 | Guía del Sistema Mundial de Observación. Edición 2010. Actualización 2017 | 2017 |</v>
       </c>
       <c r="R20" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 16 | Urban area | Fully developed urban areas - Urban districts | 1/2 acre. Average percent impervious area: 25 |</v>
+        <v>| OMM-N°0488 | Guía del Sistema Mundial de Observación. Edición 2010. Actualización 2017 | 2017 | https://library.wmo.int/doc_num.php?explnum_id=5440 |</v>
       </c>
       <c r="S20" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 16 | Urban area | Fully developed urban areas - Urban districts | 1/2 acre. Average percent impervious area: 25 |Unique |</v>
+        <v>| OMM-N°0488 | Guía del Sistema Mundial de Observación. Edición 2010. Actualización 2017 | 2017 | https://library.wmo.int/doc_num.php?explnum_id=5440 |WMO.0488.GuiaSistemaMundialObservacion.2017.pdf |</v>
       </c>
       <c r="T20" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 16 | Urban area | Fully developed urban areas - Urban districts | 1/2 acre. Average percent impervious area: 25 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |54 |70 |80 |85 |</v>
+        <v>| OMM-N°0488 | Guía del Sistema Mundial de Observación. Edición 2010. Actualización 2017 | 2017 | https://library.wmo.int/doc_num.php?explnum_id=5440 |WMO.0488.GuiaSistemaMundialObservacion.2017.pdf | | | | | |</v>
       </c>
       <c r="U20" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 16 | Urban area | Fully developed urban areas - Urban districts | 1/2 acre. Average percent impervious area: 25 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |54 |70 |80 |85 | | | |</v>
-      </c>
-    </row>
-    <row r="21" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="5">
-        <v>17</v>
+        <v>| OMM-N°0488 | Guía del Sistema Mundial de Observación. Edición 2010. Actualización 2017 | 2017 | https://library.wmo.int/doc_num.php?explnum_id=5440 |WMO.0488.GuiaSistemaMundialObservacion.2017.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21" ht="61.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>41</v>
+        <v>50</v>
+      </c>
+      <c r="D21" s="5">
+        <v>2017</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>128</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H21" s="5">
         <v>51</v>
       </c>
-      <c r="I21" s="5">
-        <v>68</v>
-      </c>
-      <c r="J21" s="5">
-        <v>79</v>
-      </c>
-      <c r="K21" s="5">
-        <v>84</v>
-      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
       <c r="P21" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| 17 | Urban area |</v>
+        <v>| OMM-N°0544 | Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico |</v>
       </c>
       <c r="Q21" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| 17 | Urban area | Fully developed urban areas - Urban districts |</v>
+        <v>| OMM-N°0544 | Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico | 2017 |</v>
       </c>
       <c r="R21" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 17 | Urban area | Fully developed urban areas - Urban districts | 1 acre. Average percent impervious area: 20 |</v>
+        <v>| OMM-N°0544 | Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico | 2017 | https://wmo.int/wmo-no-544-manual-global-observing-system |</v>
       </c>
       <c r="S21" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 17 | Urban area | Fully developed urban areas - Urban districts | 1 acre. Average percent impervious area: 20 |Unique |</v>
+        <v>| OMM-N°0544 | Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico | 2017 | https://wmo.int/wmo-no-544-manual-global-observing-system |WMO.0544.ManualSistemaMundialObservacionVolumen1.2017.pdf |</v>
       </c>
       <c r="T21" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 17 | Urban area | Fully developed urban areas - Urban districts | 1 acre. Average percent impervious area: 20 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |51 |68 |79 |84 |</v>
+        <v>| OMM-N°0544 | Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico | 2017 | https://wmo.int/wmo-no-544-manual-global-observing-system |WMO.0544.ManualSistemaMundialObservacionVolumen1.2017.pdf | | | | | |</v>
       </c>
       <c r="U21" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 17 | Urban area | Fully developed urban areas - Urban districts | 1 acre. Average percent impervious area: 20 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |51 |68 |79 |84 | | | |</v>
-      </c>
-    </row>
-    <row r="22" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="5">
-        <v>18</v>
+        <v>| OMM-N°0544 | Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico | 2017 | https://wmo.int/wmo-no-544-manual-global-observing-system |WMO.0544.ManualSistemaMundialObservacionVolumen1.2017.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="22" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>33</v>
+        <v>53</v>
+      </c>
+      <c r="D22" s="5">
+        <v>2018</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H22" s="5">
-        <v>46</v>
-      </c>
-      <c r="I22" s="5">
-        <v>65</v>
-      </c>
-      <c r="J22" s="5">
-        <v>77</v>
-      </c>
-      <c r="K22" s="5">
-        <v>82</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| 18 | Urban area |</v>
+        <v>| OMM-N°1061 | Guía del Sistema de Información de la OMM |</v>
       </c>
       <c r="Q22" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| 18 | Urban area | Fully developed urban areas - Urban districts |</v>
+        <v>| OMM-N°1061 | Guía del Sistema de Información de la OMM | 2018 |</v>
       </c>
       <c r="R22" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 18 | Urban area | Fully developed urban areas - Urban districts | 2 acre. Average percent impervious area: 12 |</v>
+        <v>| OMM-N°1061 | Guía del Sistema de Información de la OMM | 2018 | https://library.wmo.int/doc_num.php?explnum_id=10258 |</v>
       </c>
       <c r="S22" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 18 | Urban area | Fully developed urban areas - Urban districts | 2 acre. Average percent impervious area: 12 |Unique |</v>
+        <v>| OMM-N°1061 | Guía del Sistema de Información de la OMM | 2018 | https://library.wmo.int/doc_num.php?explnum_id=10258 |WMO.1061.GuiaSistemaInformacionOMM.2018.pdf |</v>
       </c>
       <c r="T22" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 18 | Urban area | Fully developed urban areas - Urban districts | 2 acre. Average percent impervious area: 12 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |46 |65 |77 |82 |</v>
+        <v>| OMM-N°1061 | Guía del Sistema de Información de la OMM | 2018 | https://library.wmo.int/doc_num.php?explnum_id=10258 |WMO.1061.GuiaSistemaInformacionOMM.2018.pdf | | | | | |</v>
       </c>
       <c r="U22" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 18 | Urban area | Fully developed urban areas - Urban districts | 2 acre. Average percent impervious area: 12 |Unique |&lt;sub&gt;The average percent impervious area shown was used to develop the composite CN's. Other assumptions are as follows: impervious areas are directly connected to the drainage system, impervious areas have a CN of 98, and pervious areas are considered equivalent to open space in good hydrologic condition. CN's for other combinations of conditions may be computed using figure 2-3 or 2-4.&lt;/sub&gt; |46 |65 |77 |82 | | | |</v>
-      </c>
-    </row>
-    <row r="23" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="5">
-        <v>19</v>
+        <v>| OMM-N°1061 | Guía del Sistema de Información de la OMM | 2018 | https://library.wmo.int/doc_num.php?explnum_id=10258 |WMO.1061.GuiaSistemaInformacionOMM.2018.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="23" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>43</v>
+        <v>57</v>
+      </c>
+      <c r="D23" s="5">
+        <v>2012</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="H23" s="5">
-        <v>77</v>
-      </c>
-      <c r="I23" s="5">
-        <v>86</v>
-      </c>
-      <c r="J23" s="5">
-        <v>91</v>
-      </c>
-      <c r="K23" s="5">
-        <v>94</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
       <c r="P23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| 19 | Urban area |</v>
+        <v>| OMM-N°1091 | Directrices sobre los sistemas de predicción por conjuntos y la predicción |</v>
       </c>
       <c r="Q23" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| 19 | Urban area | Developing urban areas |</v>
+        <v>| OMM-N°1091 | Directrices sobre los sistemas de predicción por conjuntos y la predicción | 2012 |</v>
       </c>
       <c r="R23" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 19 | Urban area | Developing urban areas | Newly graded areas (pervious areas only, no vegetation) |</v>
+        <v>| OMM-N°1091 | Directrices sobre los sistemas de predicción por conjuntos y la predicción | 2012 | https://library.wmo.int/doc_num.php?explnum_id=7774 |</v>
       </c>
       <c r="S23" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 19 | Urban area | Developing urban areas | Newly graded areas (pervious areas only, no vegetation) |Unique |</v>
+        <v>| OMM-N°1091 | Directrices sobre los sistemas de predicción por conjuntos y la predicción | 2012 | https://library.wmo.int/doc_num.php?explnum_id=7774 |WMO.1091.DirectricesSistemasPrediccionConjuntos.2012.pdf |</v>
       </c>
       <c r="T23" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 19 | Urban area | Developing urban areas | Newly graded areas (pervious areas only, no vegetation) |Unique |&lt;sub&gt;Composite CN's to use for the design of temporary measures during grading and construction should be computed using figure 2-3 or 2-4, based on the degree of development (imperviousness area percentage) and the CN's for the newly graded pervious areas.&lt;/sub&gt; |77 |86 |91 |94 |</v>
+        <v>| OMM-N°1091 | Directrices sobre los sistemas de predicción por conjuntos y la predicción | 2012 | https://library.wmo.int/doc_num.php?explnum_id=7774 |WMO.1091.DirectricesSistemasPrediccionConjuntos.2012.pdf | | | | | |</v>
       </c>
       <c r="U23" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 19 | Urban area | Developing urban areas | Newly graded areas (pervious areas only, no vegetation) |Unique |&lt;sub&gt;Composite CN's to use for the design of temporary measures during grading and construction should be computed using figure 2-3 or 2-4, based on the degree of development (imperviousness area percentage) and the CN's for the newly graded pervious areas.&lt;/sub&gt; |77 |86 |91 |94 | | | |</v>
-      </c>
-    </row>
-    <row r="24" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="5">
-        <v>20</v>
+        <v>| OMM-N°1091 | Directrices sobre los sistemas de predicción por conjuntos y la predicción | 2012 | https://library.wmo.int/doc_num.php?explnum_id=7774 |WMO.1091.DirectricesSistemasPrediccionConjuntos.2012.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21" ht="76.900000000000006" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>46</v>
+        <v>113</v>
+      </c>
+      <c r="D24" s="5">
+        <v>2017</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H24" s="5">
-        <v>77</v>
-      </c>
-      <c r="I24" s="5">
-        <v>86</v>
-      </c>
-      <c r="J24" s="5">
-        <v>91</v>
-      </c>
-      <c r="K24" s="5">
-        <v>94</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
       <c r="P24" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| 20 | Cultivated agricultural lands |</v>
+        <v>| OMM-N°1100 | Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes |</v>
       </c>
       <c r="Q24" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| 20 | Cultivated agricultural lands | Fallow |</v>
+        <v>| OMM-N°1100 | Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes | 2017 |</v>
       </c>
       <c r="R24" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 20 | Cultivated agricultural lands | Fallow | Bare soil |</v>
+        <v>| OMM-N°1100 | Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes | 2017 | https://library.wmo.int/doc_num.php?explnum_id=5742 |</v>
       </c>
       <c r="S24" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 20 | Cultivated agricultural lands | Fallow | Bare soil |Unique |</v>
+        <v>| OMM-N°1100 | Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes | 2017 | https://library.wmo.int/doc_num.php?explnum_id=5742 |WMO.1100.GuiaAplicacionSistemasGestionCalidadServicioMeteorologicoHidrologico.2017.pdf |</v>
       </c>
       <c r="T24" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 20 | Cultivated agricultural lands | Fallow | Bare soil |Unique |&lt;sub&gt;&lt;/sub&gt; |77 |86 |91 |94 |</v>
+        <v>| OMM-N°1100 | Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes | 2017 | https://library.wmo.int/doc_num.php?explnum_id=5742 |WMO.1100.GuiaAplicacionSistemasGestionCalidadServicioMeteorologicoHidrologico.2017.pdf | | | | | |</v>
       </c>
       <c r="U24" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 20 | Cultivated agricultural lands | Fallow | Bare soil |Unique |&lt;sub&gt;&lt;/sub&gt; |77 |86 |91 |94 | | | |</v>
-      </c>
-    </row>
-    <row r="25" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="5">
-        <v>21</v>
+        <v>| OMM-N°1100 | Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes | 2017 | https://library.wmo.int/doc_num.php?explnum_id=5742 |WMO.1100.GuiaAplicacionSistemasGestionCalidadServicioMeteorologicoHidrologico.2017.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="25" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>46</v>
+        <v>64</v>
+      </c>
+      <c r="D25" s="5">
+        <v>2019</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="H25" s="5">
-        <v>76</v>
-      </c>
-      <c r="I25" s="5">
-        <v>85</v>
-      </c>
-      <c r="J25" s="5">
-        <v>90</v>
-      </c>
-      <c r="K25" s="5">
-        <v>93</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
       <c r="L25" s="5"/>
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
       <c r="O25" s="4"/>
       <c r="P25" s="5" t="str">
         <f t="shared" ref="P25:P88" si="6">_xlfn.CONCAT("| ",B25," | ",C25," |")</f>
-        <v>| 21 | Cultivated agricultural lands |</v>
+        <v>| OMM-N°1160 | Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM |</v>
       </c>
       <c r="Q25" s="5" t="str">
         <f t="shared" ref="Q25:Q88" si="7">_xlfn.CONCAT("| ",B25," | ",C25," | ",D25," |")</f>
-        <v>| 21 | Cultivated agricultural lands | Fallow |</v>
+        <v>| OMM-N°1160 | Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 |</v>
       </c>
       <c r="R25" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 21 | Cultivated agricultural lands | Fallow | Crop residue cover (CR) |</v>
+        <v>| OMM-N°1160 | Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10230 |</v>
       </c>
       <c r="S25" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 21 | Cultivated agricultural lands | Fallow | Crop residue cover (CR) |Poor |</v>
+        <v>| OMM-N°1160 | Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10230 |WMO.1160.ManualSistemaIntegradoObservacionOMM.2019.pdf |</v>
       </c>
       <c r="T25" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 21 | Cultivated agricultural lands | Fallow | Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |76 |85 |90 |93 |</v>
+        <v>| OMM-N°1160 | Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10230 |WMO.1160.ManualSistemaIntegradoObservacionOMM.2019.pdf | | | | | |</v>
       </c>
       <c r="U25" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 21 | Cultivated agricultural lands | Fallow | Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |76 |85 |90 |93 | | | |</v>
-      </c>
-    </row>
-    <row r="26" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="4">
-        <v>22</v>
+        <v>| OMM-N°1160 | Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10230 |WMO.1160.ManualSistemaIntegradoObservacionOMM.2019.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="26" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>46</v>
+        <v>68</v>
+      </c>
+      <c r="D26" s="4">
+        <v>2019</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H26" s="4">
-        <v>74</v>
-      </c>
-      <c r="I26" s="4">
-        <v>83</v>
-      </c>
-      <c r="J26" s="4">
-        <v>88</v>
-      </c>
-      <c r="K26" s="4">
-        <v>90</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
       <c r="L26" s="5"/>
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
       <c r="P26" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 22 | Cultivated agricultural lands |</v>
+        <v>| OMM-N°1165 | Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM |</v>
       </c>
       <c r="Q26" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 22 | Cultivated agricultural lands | Fallow |</v>
+        <v>| OMM-N°1165 | Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 |</v>
       </c>
       <c r="R26" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 22 | Cultivated agricultural lands | Fallow | Crop residue cover (CR) |</v>
+        <v>| OMM-N°1165 | Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10042 |</v>
       </c>
       <c r="S26" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 22 | Cultivated agricultural lands | Fallow | Crop residue cover (CR) |Good |</v>
+        <v>| OMM-N°1165 | Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10042 |WMO.1165.GuiaSistemaMundialIntegradoSistemaObservacionOMM.2019.pdf |</v>
       </c>
       <c r="T26" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 22 | Cultivated agricultural lands | Fallow | Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |74 |83 |88 |90 |</v>
+        <v>| OMM-N°1165 | Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10042 |WMO.1165.GuiaSistemaMundialIntegradoSistemaObservacionOMM.2019.pdf | | | | | |</v>
       </c>
       <c r="U26" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 22 | Cultivated agricultural lands | Fallow | Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |74 |83 |88 |90 | | | |</v>
-      </c>
-    </row>
-    <row r="27" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="4">
-        <v>23</v>
+        <v>| OMM-N°1165 | Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10042 |WMO.1165.GuiaSistemaMundialIntegradoSistemaObservacionOMM.2019.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="27" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>51</v>
+        <v>72</v>
+      </c>
+      <c r="D27" s="4">
+        <v>2016</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H27" s="4">
-        <v>72</v>
-      </c>
-      <c r="I27" s="4">
-        <v>81</v>
-      </c>
-      <c r="J27" s="4">
-        <v>88</v>
-      </c>
-      <c r="K27" s="4">
-        <v>91</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
       <c r="L27" s="5"/>
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
       <c r="O27" s="4"/>
       <c r="P27" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 23 | Cultivated agricultural lands |</v>
+        <v>| OMM-N°1182 | Directrices sobre mejores prácticas para el rescate de datos climáticos |</v>
       </c>
       <c r="Q27" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 23 | Cultivated agricultural lands | Row crops |</v>
+        <v>| OMM-N°1182 | Directrices sobre mejores prácticas para el rescate de datos climáticos | 2016 |</v>
       </c>
       <c r="R27" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 23 | Cultivated agricultural lands | Row crops | Straight row (SR) |</v>
+        <v>| OMM-N°1182 | Directrices sobre mejores prácticas para el rescate de datos climáticos | 2016 | https://library.wmo.int/doc_num.php?explnum_id=3529 |</v>
       </c>
       <c r="S27" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 23 | Cultivated agricultural lands | Row crops | Straight row (SR) |Poor |</v>
+        <v>| OMM-N°1182 | Directrices sobre mejores prácticas para el rescate de datos climáticos | 2016 | https://library.wmo.int/doc_num.php?explnum_id=3529 |WMO.1182.DirectrizRescateDatoClimatico.2016.pdf |</v>
       </c>
       <c r="T27" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 23 | Cultivated agricultural lands | Row crops | Straight row (SR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |72 |81 |88 |91 |</v>
+        <v>| OMM-N°1182 | Directrices sobre mejores prácticas para el rescate de datos climáticos | 2016 | https://library.wmo.int/doc_num.php?explnum_id=3529 |WMO.1182.DirectrizRescateDatoClimatico.2016.pdf | | | | | |</v>
       </c>
       <c r="U27" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 23 | Cultivated agricultural lands | Row crops | Straight row (SR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |72 |81 |88 |91 | | | |</v>
-      </c>
-    </row>
-    <row r="28" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="4">
-        <v>24</v>
+        <v>| OMM-N°1182 | Directrices sobre mejores prácticas para el rescate de datos climáticos | 2016 | https://library.wmo.int/doc_num.php?explnum_id=3529 |WMO.1182.DirectrizRescateDatoClimatico.2016.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="28" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>51</v>
+        <v>76</v>
+      </c>
+      <c r="D28" s="4">
+        <v>2019</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H28" s="4">
-        <v>67</v>
-      </c>
-      <c r="I28" s="4">
         <v>78</v>
       </c>
-      <c r="J28" s="4">
-        <v>85</v>
-      </c>
-      <c r="K28" s="4">
-        <v>89</v>
-      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
       <c r="L28" s="5"/>
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
       <c r="O28" s="4"/>
       <c r="P28" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 24 | Cultivated agricultural lands |</v>
+        <v>| OMM-N°1192 | Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM |</v>
       </c>
       <c r="Q28" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 24 | Cultivated agricultural lands | Row crops |</v>
+        <v>| OMM-N°1192 | Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 |</v>
       </c>
       <c r="R28" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 24 | Cultivated agricultural lands | Row crops | Straight row (SR) |</v>
+        <v>| OMM-N°1192 | Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10163 |</v>
       </c>
       <c r="S28" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 24 | Cultivated agricultural lands | Row crops | Straight row (SR) |Good |</v>
+        <v>| OMM-N°1192 | Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10163 |WMO.1192.NormaMetadatoSistemaMundialIntegradoObservacion.2019 |</v>
       </c>
       <c r="T28" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 24 | Cultivated agricultural lands | Row crops | Straight row (SR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |67 |78 |85 |89 |</v>
+        <v>| OMM-N°1192 | Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10163 |WMO.1192.NormaMetadatoSistemaMundialIntegradoObservacion.2019 | | | | | |</v>
       </c>
       <c r="U28" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 24 | Cultivated agricultural lands | Row crops | Straight row (SR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |67 |78 |85 |89 | | | |</v>
-      </c>
-    </row>
-    <row r="29" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="4">
-        <v>25</v>
+        <v>| OMM-N°1192 | Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10163 |WMO.1192.NormaMetadatoSistemaMundialIntegradoObservacion.2019 | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="29" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>51</v>
+        <v>80</v>
+      </c>
+      <c r="D29" s="4">
+        <v>2017</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G29" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="H29" s="4">
-        <v>71</v>
-      </c>
-      <c r="I29" s="4">
-        <v>80</v>
-      </c>
-      <c r="J29" s="4">
-        <v>87</v>
-      </c>
-      <c r="K29" s="4">
-        <v>90</v>
-      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
       <c r="L29" s="5"/>
       <c r="M29" s="4"/>
       <c r="N29" s="4"/>
       <c r="O29" s="4"/>
       <c r="P29" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 25 | Cultivated agricultural lands |</v>
+        <v>| OMM-N°1203 | Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas |</v>
       </c>
       <c r="Q29" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 25 | Cultivated agricultural lands | Row crops |</v>
+        <v>| OMM-N°1203 | Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas | 2017 |</v>
       </c>
       <c r="R29" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 25 | Cultivated agricultural lands | Row crops | Straight row (SR) + Crop residue cover (CR) |</v>
+        <v>| OMM-N°1203 | Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas | 2017 | https://library.wmo.int/doc_num.php?explnum_id=4167 |</v>
       </c>
       <c r="S29" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 25 | Cultivated agricultural lands | Row crops | Straight row (SR) + Crop residue cover (CR) |Poor |</v>
+        <v>| OMM-N°1203 | Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas | 2017 | https://library.wmo.int/doc_num.php?explnum_id=4167 |WMO.01203.DirectricezCalculoNormalClimatica.2017.pdf |</v>
       </c>
       <c r="T29" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 25 | Cultivated agricultural lands | Row crops | Straight row (SR) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |71 |80 |87 |90 |</v>
+        <v>| OMM-N°1203 | Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas | 2017 | https://library.wmo.int/doc_num.php?explnum_id=4167 |WMO.01203.DirectricezCalculoNormalClimatica.2017.pdf | | | | | |</v>
       </c>
       <c r="U29" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 25 | Cultivated agricultural lands | Row crops | Straight row (SR) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |71 |80 |87 |90 | | | |</v>
-      </c>
-    </row>
-    <row r="30" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="4">
-        <v>26</v>
+        <v>| OMM-N°1203 | Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas | 2017 | https://library.wmo.int/doc_num.php?explnum_id=4167 |WMO.01203.DirectricezCalculoNormalClimatica.2017.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="30" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>51</v>
+        <v>84</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1966</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H30" s="4">
-        <v>64</v>
-      </c>
-      <c r="I30" s="4">
-        <v>75</v>
-      </c>
-      <c r="J30" s="4">
-        <v>82</v>
-      </c>
-      <c r="K30" s="4">
-        <v>85</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
       <c r="L30" s="5"/>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
       <c r="O30" s="4"/>
       <c r="P30" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 26 | Cultivated agricultural lands |</v>
+        <v>| WMO-N°0199 | Some Methods of Climatological Analysis |</v>
       </c>
       <c r="Q30" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 26 | Cultivated agricultural lands | Row crops |</v>
+        <v>| WMO-N°0199 | Some Methods of Climatological Analysis | 1966 |</v>
       </c>
       <c r="R30" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 26 | Cultivated agricultural lands | Row crops | Straight row (SR) + Crop residue cover (CR) |</v>
+        <v>| WMO-N°0199 | Some Methods of Climatological Analysis | 1966 | https://library.wmo.int/doc_num.php?explnum_id=1961 |</v>
       </c>
       <c r="S30" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 26 | Cultivated agricultural lands | Row crops | Straight row (SR) + Crop residue cover (CR) |Good |</v>
+        <v>| WMO-N°0199 | Some Methods of Climatological Analysis | 1966 | https://library.wmo.int/doc_num.php?explnum_id=1961 |WMO.0199.SomeMethodsClimatologicalAnalysis.1966.pdf |</v>
       </c>
       <c r="T30" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 26 | Cultivated agricultural lands | Row crops | Straight row (SR) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |64 |75 |82 |85 |</v>
+        <v>| WMO-N°0199 | Some Methods of Climatological Analysis | 1966 | https://library.wmo.int/doc_num.php?explnum_id=1961 |WMO.0199.SomeMethodsClimatologicalAnalysis.1966.pdf | | | | | |</v>
       </c>
       <c r="U30" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 26 | Cultivated agricultural lands | Row crops | Straight row (SR) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |64 |75 |82 |85 | | | |</v>
-      </c>
-    </row>
-    <row r="31" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="4">
-        <v>27</v>
+        <v>| WMO-N°0199 | Some Methods of Climatological Analysis | 1966 | https://library.wmo.int/doc_num.php?explnum_id=1961 |WMO.0199.SomeMethodsClimatologicalAnalysis.1966.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="31" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>51</v>
+        <v>88</v>
+      </c>
+      <c r="D31" s="4">
+        <v>1990</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H31" s="4">
-        <v>70</v>
-      </c>
-      <c r="I31" s="4">
-        <v>79</v>
-      </c>
-      <c r="J31" s="4">
-        <v>84</v>
-      </c>
-      <c r="K31" s="4">
-        <v>88</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
       <c r="O31" s="4"/>
       <c r="P31" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 27 | Cultivated agricultural lands |</v>
+        <v>| WMO-N°0415 | On The Statistical Analysis of Series of Observations |</v>
       </c>
       <c r="Q31" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 27 | Cultivated agricultural lands | Row crops |</v>
+        <v>| WMO-N°0415 | On The Statistical Analysis of Series of Observations | 1990 |</v>
       </c>
       <c r="R31" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 27 | Cultivated agricultural lands | Row crops | Contoured (C) |</v>
+        <v>| WMO-N°0415 | On The Statistical Analysis of Series of Observations | 1990 | https://library.wmo.int/doc_num.php?explnum_id=1065 |</v>
       </c>
       <c r="S31" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 27 | Cultivated agricultural lands | Row crops | Contoured (C) |Poor |</v>
+        <v>| WMO-N°0415 | On The Statistical Analysis of Series of Observations | 1990 | https://library.wmo.int/doc_num.php?explnum_id=1065 |WMO.0415.StatisticalAnalysisSerieObservation.1990.pdf |</v>
       </c>
       <c r="T31" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 27 | Cultivated agricultural lands | Row crops | Contoured (C) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |70 |79 |84 |88 |</v>
+        <v>| WMO-N°0415 | On The Statistical Analysis of Series of Observations | 1990 | https://library.wmo.int/doc_num.php?explnum_id=1065 |WMO.0415.StatisticalAnalysisSerieObservation.1990.pdf | | | | | |</v>
       </c>
       <c r="U31" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 27 | Cultivated agricultural lands | Row crops | Contoured (C) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |70 |79 |84 |88 | | | |</v>
-      </c>
-    </row>
-    <row r="32" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="5">
-        <v>28</v>
+        <v>| WMO-N°0415 | On The Statistical Analysis of Series of Observations | 1990 | https://library.wmo.int/doc_num.php?explnum_id=1065 |WMO.0415.StatisticalAnalysisSerieObservation.1990.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="32" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>51</v>
+        <v>92</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2019</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H32" s="4">
-        <v>65</v>
-      </c>
-      <c r="I32" s="4">
-        <v>75</v>
-      </c>
-      <c r="J32" s="4">
-        <v>82</v>
-      </c>
-      <c r="K32" s="4">
-        <v>86</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="5"/>
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
       <c r="P32" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 28 | Cultivated agricultural lands |</v>
+        <v>| WMO-N°0485 | Manual del Sistema Mundial de Proceso de Datos y de Predicción |</v>
       </c>
       <c r="Q32" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 28 | Cultivated agricultural lands | Row crops |</v>
+        <v>| WMO-N°0485 | Manual del Sistema Mundial de Proceso de Datos y de Predicción | 2019 |</v>
       </c>
       <c r="R32" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 28 | Cultivated agricultural lands | Row crops | Contoured (C) |</v>
+        <v>| WMO-N°0485 | Manual del Sistema Mundial de Proceso de Datos y de Predicción | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10281 |</v>
       </c>
       <c r="S32" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 28 | Cultivated agricultural lands | Row crops | Contoured (C) |Good |</v>
+        <v>| WMO-N°0485 | Manual del Sistema Mundial de Proceso de Datos y de Predicción | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10281 |WMO.0485.ManualSistemaMundialProcesoDatosPrediccion.2019.pdf |</v>
       </c>
       <c r="T32" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 28 | Cultivated agricultural lands | Row crops | Contoured (C) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |65 |75 |82 |86 |</v>
+        <v>| WMO-N°0485 | Manual del Sistema Mundial de Proceso de Datos y de Predicción | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10281 |WMO.0485.ManualSistemaMundialProcesoDatosPrediccion.2019.pdf | | | | | |</v>
       </c>
       <c r="U32" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 28 | Cultivated agricultural lands | Row crops | Contoured (C) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |65 |75 |82 |86 | | | |</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="5">
-        <v>29</v>
+        <v>| WMO-N°0485 | Manual del Sistema Mundial de Proceso de Datos y de Predicción | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10281 |WMO.0485.ManualSistemaMundialProcesoDatosPrediccion.2019.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>51</v>
+        <v>96</v>
+      </c>
+      <c r="D33" s="4">
+        <v>2014</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H33" s="4">
-        <v>69</v>
-      </c>
-      <c r="I33" s="4">
-        <v>78</v>
-      </c>
-      <c r="J33" s="4">
-        <v>83</v>
-      </c>
-      <c r="K33" s="4">
-        <v>87</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="5"/>
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
       <c r="P33" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 29 | Cultivated agricultural lands |</v>
+        <v>| WMO-N°1131 | Climate Data Management System Specifications |</v>
       </c>
       <c r="Q33" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 29 | Cultivated agricultural lands | Row crops |</v>
+        <v>| WMO-N°1131 | Climate Data Management System Specifications | 2014 |</v>
       </c>
       <c r="R33" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 29 | Cultivated agricultural lands | Row crops | Contoured (C) + Crop residue cover (CR) |</v>
+        <v>| WMO-N°1131 | Climate Data Management System Specifications | 2014 | https://library.wmo.int/doc_num.php?explnum_id=7867 |</v>
       </c>
       <c r="S33" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 29 | Cultivated agricultural lands | Row crops | Contoured (C) + Crop residue cover (CR) |Poor |</v>
+        <v>| WMO-N°1131 | Climate Data Management System Specifications | 2014 | https://library.wmo.int/doc_num.php?explnum_id=7867 |WMO.1131.ClimateDataManagementSystem.2014.pdf |</v>
       </c>
       <c r="T33" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 29 | Cultivated agricultural lands | Row crops | Contoured (C) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |69 |78 |83 |87 |</v>
+        <v>| WMO-N°1131 | Climate Data Management System Specifications | 2014 | https://library.wmo.int/doc_num.php?explnum_id=7867 |WMO.1131.ClimateDataManagementSystem.2014.pdf | | | | | |</v>
       </c>
       <c r="U33" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 29 | Cultivated agricultural lands | Row crops | Contoured (C) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |69 |78 |83 |87 | | | |</v>
-      </c>
-    </row>
-    <row r="34" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="4">
-        <v>30</v>
+        <v>| WMO-N°1131 | Climate Data Management System Specifications | 2014 | https://library.wmo.int/doc_num.php?explnum_id=7867 |WMO.1131.ClimateDataManagementSystem.2014.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>51</v>
+        <v>100</v>
+      </c>
+      <c r="D34" s="4">
+        <v>2016</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H34" s="4">
-        <v>64</v>
-      </c>
-      <c r="I34" s="4">
-        <v>74</v>
-      </c>
-      <c r="J34" s="4">
-        <v>81</v>
-      </c>
-      <c r="K34" s="4">
-        <v>85</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
       <c r="O34" s="4"/>
       <c r="P34" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 30 | Cultivated agricultural lands |</v>
+        <v>| WMO-N°1170 | Climate Services for Supporting Climate Change Adaptation |</v>
       </c>
       <c r="Q34" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 30 | Cultivated agricultural lands | Row crops |</v>
+        <v>| WMO-N°1170 | Climate Services for Supporting Climate Change Adaptation | 2016 |</v>
       </c>
       <c r="R34" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 30 | Cultivated agricultural lands | Row crops | Contoured (C) + Crop residue cover (CR) |</v>
+        <v>| WMO-N°1170 | Climate Services for Supporting Climate Change Adaptation | 2016 | https://library.wmo.int/doc_num.php?explnum_id=7936 |</v>
       </c>
       <c r="S34" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 30 | Cultivated agricultural lands | Row crops | Contoured (C) + Crop residue cover (CR) |Good |</v>
+        <v>| WMO-N°1170 | Climate Services for Supporting Climate Change Adaptation | 2016 | https://library.wmo.int/doc_num.php?explnum_id=7936 |WMO.1170.ClimateServiceForSupportingClimateChangeAdaptation.2016.pdf |</v>
       </c>
       <c r="T34" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 30 | Cultivated agricultural lands | Row crops | Contoured (C) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |64 |74 |81 |85 |</v>
+        <v>| WMO-N°1170 | Climate Services for Supporting Climate Change Adaptation | 2016 | https://library.wmo.int/doc_num.php?explnum_id=7936 |WMO.1170.ClimateServiceForSupportingClimateChangeAdaptation.2016.pdf | | | | | |</v>
       </c>
       <c r="U34" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 30 | Cultivated agricultural lands | Row crops | Contoured (C) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |64 |74 |81 |85 | | | |</v>
-      </c>
-    </row>
-    <row r="35" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="4">
-        <v>31</v>
+        <v>| WMO-N°1170 | Climate Services for Supporting Climate Change Adaptation | 2016 | https://library.wmo.int/doc_num.php?explnum_id=7936 |WMO.1170.ClimateServiceForSupportingClimateChangeAdaptation.2016.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>51</v>
+        <v>104</v>
+      </c>
+      <c r="D35" s="4">
+        <v>2018</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H35" s="4">
-        <v>66</v>
-      </c>
-      <c r="I35" s="4">
-        <v>74</v>
-      </c>
-      <c r="J35" s="4">
-        <v>80</v>
-      </c>
-      <c r="K35" s="4">
-        <v>82</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
       <c r="L35" s="4"/>
       <c r="M35" s="5"/>
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
       <c r="P35" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 31 | Cultivated agricultural lands |</v>
+        <v>| WMO-N°1221 | Guidelines on Quality Management in Climate Services |</v>
       </c>
       <c r="Q35" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 31 | Cultivated agricultural lands | Row crops |</v>
+        <v>| WMO-N°1221 | Guidelines on Quality Management in Climate Services | 2018 |</v>
       </c>
       <c r="R35" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 31 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) |</v>
+        <v>| WMO-N°1221 | Guidelines on Quality Management in Climate Services | 2018 | https://library.wmo.int/doc_num.php?explnum_id=5174 |</v>
       </c>
       <c r="S35" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 31 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) |Poor |</v>
+        <v>| WMO-N°1221 | Guidelines on Quality Management in Climate Services | 2018 | https://library.wmo.int/doc_num.php?explnum_id=5174 |WMO.1221.GuidelinesQualityManagementClimateServices.2018.pdf |</v>
       </c>
       <c r="T35" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 31 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |66 |74 |80 |82 |</v>
+        <v>| WMO-N°1221 | Guidelines on Quality Management in Climate Services | 2018 | https://library.wmo.int/doc_num.php?explnum_id=5174 |WMO.1221.GuidelinesQualityManagementClimateServices.2018.pdf | | | | | |</v>
       </c>
       <c r="U35" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 31 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |66 |74 |80 |82 | | | |</v>
-      </c>
-    </row>
-    <row r="36" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="4">
-        <v>32</v>
+        <v>| WMO-N°1221 | Guidelines on Quality Management in Climate Services | 2018 | https://library.wmo.int/doc_num.php?explnum_id=5174 |WMO.1221.GuidelinesQualityManagementClimateServices.2018.pdf | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="36" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>51</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="D36" s="4"/>
       <c r="E36" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H36" s="4">
-        <v>62</v>
-      </c>
-      <c r="I36" s="4">
-        <v>71</v>
-      </c>
-      <c r="J36" s="4">
-        <v>78</v>
-      </c>
-      <c r="K36" s="4">
-        <v>81</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
       <c r="L36" s="4"/>
       <c r="M36" s="5"/>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
       <c r="P36" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 32 | Cultivated agricultural lands |</v>
+        <v>| WMO | Normas asociadas a metodologías para actividades hidrometeorológicas |</v>
       </c>
       <c r="Q36" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 32 | Cultivated agricultural lands | Row crops |</v>
+        <v>| WMO | Normas asociadas a metodologías para actividades hidrometeorológicas |  |</v>
       </c>
       <c r="R36" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 32 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) |</v>
+        <v>| WMO | Normas asociadas a metodologías para actividades hidrometeorológicas |  | https://public.wmo.int/ |</v>
       </c>
       <c r="S36" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 32 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) |Good |</v>
+        <v>| WMO | Normas asociadas a metodologías para actividades hidrometeorológicas |  | https://public.wmo.int/ | |</v>
       </c>
       <c r="T36" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 32 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |62 |71 |78 |81 |</v>
+        <v>| WMO | Normas asociadas a metodologías para actividades hidrometeorológicas |  | https://public.wmo.int/ | | | | | | |</v>
       </c>
       <c r="U36" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 32 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |62 |71 |78 |81 | | | |</v>
-      </c>
-    </row>
-    <row r="37" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="5">
-        <v>33</v>
+        <v>| WMO | Normas asociadas a metodologías para actividades hidrometeorológicas |  | https://public.wmo.int/ | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>51</v>
+        <v>129</v>
+      </c>
+      <c r="D37" s="4">
+        <v>2014</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H37" s="4">
-        <v>65</v>
-      </c>
-      <c r="I37" s="4">
-        <v>73</v>
-      </c>
-      <c r="J37" s="4">
-        <v>79</v>
-      </c>
-      <c r="K37" s="4">
-        <v>81</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
       <c r="L37" s="4"/>
       <c r="M37" s="5"/>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
       <c r="P37" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 33 | Cultivated agricultural lands |</v>
+        <v>| ISO-19115 | Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB |</v>
       </c>
       <c r="Q37" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 33 | Cultivated agricultural lands | Row crops |</v>
+        <v>| ISO-19115 | Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB | 2014 |</v>
       </c>
       <c r="R37" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 33 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |</v>
+        <v>| ISO-19115 | Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB | 2014 | https://www.iso.org/standard/26020.html |</v>
       </c>
       <c r="S37" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 33 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Poor |</v>
+        <v>| ISO-19115 | Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB | 2014 | https://www.iso.org/standard/26020.html | |</v>
       </c>
       <c r="T37" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 33 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |65 |73 |79 |81 |</v>
+        <v>| ISO-19115 | Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB | 2014 | https://www.iso.org/standard/26020.html | | | | | | |</v>
       </c>
       <c r="U37" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 33 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |65 |73 |79 |81 | | | |</v>
-      </c>
-    </row>
-    <row r="38" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="5">
-        <v>34</v>
+        <v>| ISO-19115 | Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB | 2014 | https://www.iso.org/standard/26020.html | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="38" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H38" s="4">
-        <v>61</v>
-      </c>
-      <c r="I38" s="4">
-        <v>70</v>
-      </c>
-      <c r="J38" s="4">
-        <v>77</v>
-      </c>
-      <c r="K38" s="4">
-        <v>80</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
       <c r="L38" s="4"/>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
       <c r="O38" s="4"/>
       <c r="P38" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 34 | Cultivated agricultural lands |</v>
+        <v>| ISO-IEC-11179 Partes 1 a 7 | Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos. |</v>
       </c>
       <c r="Q38" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 34 | Cultivated agricultural lands | Row crops |</v>
+        <v>| ISO-IEC-11179 Partes 1 a 7 | Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos. | Varias |</v>
       </c>
       <c r="R38" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 34 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |</v>
+        <v>| ISO-IEC-11179 Partes 1 a 7 | Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos. | Varias | https://www.iso.org/standard/61932.html
+ |</v>
       </c>
       <c r="S38" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 34 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Good |</v>
+        <v>| ISO-IEC-11179 Partes 1 a 7 | Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos. | Varias | https://www.iso.org/standard/61932.html
+ | |</v>
       </c>
       <c r="T38" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 34 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |61 |70 |77 |80 |</v>
+        <v>| ISO-IEC-11179 Partes 1 a 7 | Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos. | Varias | https://www.iso.org/standard/61932.html
+ | | | | | | |</v>
       </c>
       <c r="U38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 34 | Cultivated agricultural lands | Row crops | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |61 |70 |77 |80 | | | |</v>
-      </c>
-    </row>
-    <row r="39" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="4">
-        <v>35</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H39" s="4">
-        <v>65</v>
-      </c>
-      <c r="I39" s="4">
-        <v>76</v>
-      </c>
-      <c r="J39" s="4">
-        <v>84</v>
-      </c>
-      <c r="K39" s="4">
-        <v>88</v>
-      </c>
+        <v>| ISO-IEC-11179 Partes 1 a 7 | Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos. | Varias | https://www.iso.org/standard/61932.html
+ | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
       <c r="L39" s="4"/>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
       <c r="O39" s="4"/>
       <c r="P39" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 35 | Cultivated agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q39" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 35 | Cultivated agricultural lands | Small grain |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R39" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 35 | Cultivated agricultural lands | Small grain | Straight row (SR) |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S39" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 35 | Cultivated agricultural lands | Small grain | Straight row (SR) |Poor |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T39" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 35 | Cultivated agricultural lands | Small grain | Straight row (SR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |65 |76 |84 |88 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U39" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 35 | Cultivated agricultural lands | Small grain | Straight row (SR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |65 |76 |84 |88 | | | |</v>
-      </c>
-    </row>
-    <row r="40" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="4">
-        <v>36</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H40" s="4">
-        <v>63</v>
-      </c>
-      <c r="I40" s="4">
-        <v>75</v>
-      </c>
-      <c r="J40" s="4">
-        <v>83</v>
-      </c>
-      <c r="K40" s="4">
-        <v>87</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="40" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
       <c r="N40" s="5"/>
       <c r="O40" s="4"/>
       <c r="P40" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 36 | Cultivated agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q40" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 36 | Cultivated agricultural lands | Small grain |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R40" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 36 | Cultivated agricultural lands | Small grain | Straight row (SR) |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S40" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 36 | Cultivated agricultural lands | Small grain | Straight row (SR) |Good |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T40" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 36 | Cultivated agricultural lands | Small grain | Straight row (SR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |63 |75 |83 |87 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U40" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 36 | Cultivated agricultural lands | Small grain | Straight row (SR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |63 |75 |83 |87 | | | |</v>
-      </c>
-    </row>
-    <row r="41" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="4">
-        <v>37</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H41" s="4">
-        <v>64</v>
-      </c>
-      <c r="I41" s="4">
-        <v>75</v>
-      </c>
-      <c r="J41" s="4">
-        <v>83</v>
-      </c>
-      <c r="K41" s="4">
-        <v>86</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="41" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
       <c r="N41" s="5"/>
       <c r="O41" s="4"/>
       <c r="P41" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 37 | Cultivated agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q41" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 37 | Cultivated agricultural lands | Small grain |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R41" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 37 | Cultivated agricultural lands | Small grain | Straight row (SR) + Crop residue cover (CR) |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S41" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 37 | Cultivated agricultural lands | Small grain | Straight row (SR) + Crop residue cover (CR) |Poor |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T41" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 37 | Cultivated agricultural lands | Small grain | Straight row (SR) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |64 |75 |83 |86 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U41" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 37 | Cultivated agricultural lands | Small grain | Straight row (SR) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |64 |75 |83 |86 | | | |</v>
-      </c>
-    </row>
-    <row r="42" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="4">
-        <v>38</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H42" s="4">
-        <v>60</v>
-      </c>
-      <c r="I42" s="4">
-        <v>72</v>
-      </c>
-      <c r="J42" s="4">
-        <v>80</v>
-      </c>
-      <c r="K42" s="4">
-        <v>84</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
       <c r="P42" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 38 | Cultivated agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q42" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 38 | Cultivated agricultural lands | Small grain |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R42" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 38 | Cultivated agricultural lands | Small grain | Straight row (SR) + Crop residue cover (CR) |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S42" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 38 | Cultivated agricultural lands | Small grain | Straight row (SR) + Crop residue cover (CR) |Good |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T42" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 38 | Cultivated agricultural lands | Small grain | Straight row (SR) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |60 |72 |80 |84 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U42" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 38 | Cultivated agricultural lands | Small grain | Straight row (SR) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |60 |72 |80 |84 | | | |</v>
-      </c>
-    </row>
-    <row r="43" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="4">
-        <v>39</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H43" s="4">
-        <v>63</v>
-      </c>
-      <c r="I43" s="4">
-        <v>74</v>
-      </c>
-      <c r="J43" s="4">
-        <v>82</v>
-      </c>
-      <c r="K43" s="4">
-        <v>85</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
       <c r="P43" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 39 | Cultivated agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q43" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 39 | Cultivated agricultural lands | Small grain |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R43" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 39 | Cultivated agricultural lands | Small grain | Contoured (C) |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S43" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 39 | Cultivated agricultural lands | Small grain | Contoured (C) |Poor |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T43" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 39 | Cultivated agricultural lands | Small grain | Contoured (C) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |63 |74 |82 |85 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U43" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 39 | Cultivated agricultural lands | Small grain | Contoured (C) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |63 |74 |82 |85 | | | |</v>
-      </c>
-    </row>
-    <row r="44" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="4">
-        <v>40</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H44" s="4">
-        <v>61</v>
-      </c>
-      <c r="I44" s="4">
-        <v>73</v>
-      </c>
-      <c r="J44" s="4">
-        <v>81</v>
-      </c>
-      <c r="K44" s="4">
-        <v>84</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
       <c r="P44" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 40 | Cultivated agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q44" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 40 | Cultivated agricultural lands | Small grain |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R44" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 40 | Cultivated agricultural lands | Small grain | Contoured (C) |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S44" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 40 | Cultivated agricultural lands | Small grain | Contoured (C) |Good |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T44" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 40 | Cultivated agricultural lands | Small grain | Contoured (C) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |61 |73 |81 |84 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U44" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 40 | Cultivated agricultural lands | Small grain | Contoured (C) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |61 |73 |81 |84 | | | |</v>
-      </c>
-    </row>
-    <row r="45" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="4">
-        <v>41</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H45" s="4">
-        <v>62</v>
-      </c>
-      <c r="I45" s="4">
-        <v>73</v>
-      </c>
-      <c r="J45" s="4">
-        <v>81</v>
-      </c>
-      <c r="K45" s="4">
-        <v>84</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
       <c r="P45" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 41 | Cultivated agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q45" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 41 | Cultivated agricultural lands | Small grain |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R45" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 41 | Cultivated agricultural lands | Small grain | Contoured (C) + Crop residue cover (CR) |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S45" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 41 | Cultivated agricultural lands | Small grain | Contoured (C) + Crop residue cover (CR) |Poor |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T45" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 41 | Cultivated agricultural lands | Small grain | Contoured (C) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |62 |73 |81 |84 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U45" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 41 | Cultivated agricultural lands | Small grain | Contoured (C) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |62 |73 |81 |84 | | | |</v>
-      </c>
-    </row>
-    <row r="46" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="4">
-        <v>42</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H46" s="4">
-        <v>60</v>
-      </c>
-      <c r="I46" s="4">
-        <v>72</v>
-      </c>
-      <c r="J46" s="4">
-        <v>80</v>
-      </c>
-      <c r="K46" s="4">
-        <v>83</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
       <c r="P46" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 42 | Cultivated agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q46" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 42 | Cultivated agricultural lands | Small grain |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R46" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 42 | Cultivated agricultural lands | Small grain | Contoured (C) + Crop residue cover (CR) |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S46" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 42 | Cultivated agricultural lands | Small grain | Contoured (C) + Crop residue cover (CR) |Good |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T46" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 42 | Cultivated agricultural lands | Small grain | Contoured (C) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |60 |72 |80 |83 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U46" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 42 | Cultivated agricultural lands | Small grain | Contoured (C) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |60 |72 |80 |83 | | | |</v>
-      </c>
-    </row>
-    <row r="47" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="4">
-        <v>43</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H47" s="4">
-        <v>61</v>
-      </c>
-      <c r="I47" s="4">
-        <v>72</v>
-      </c>
-      <c r="J47" s="4">
-        <v>79</v>
-      </c>
-      <c r="K47" s="4">
-        <v>82</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
       <c r="P47" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 43 | Cultivated agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q47" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 43 | Cultivated agricultural lands | Small grain |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R47" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 43 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S47" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 43 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) |Poor |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T47" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 43 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |61 |72 |79 |82 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U47" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 43 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |61 |72 |79 |82 | | | |</v>
-      </c>
-    </row>
-    <row r="48" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="4">
-        <v>44</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H48" s="4">
-        <v>59</v>
-      </c>
-      <c r="I48" s="4">
-        <v>70</v>
-      </c>
-      <c r="J48" s="4">
-        <v>78</v>
-      </c>
-      <c r="K48" s="4">
-        <v>81</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
       <c r="P48" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 44 | Cultivated agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q48" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 44 | Cultivated agricultural lands | Small grain |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R48" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 44 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S48" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 44 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) |Good |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T48" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 44 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |59 |70 |78 |81 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U48" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 44 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |59 |70 |78 |81 | | | |</v>
-      </c>
-    </row>
-    <row r="49" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="4">
-        <v>45</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H49" s="4">
-        <v>60</v>
-      </c>
-      <c r="I49" s="4">
-        <v>71</v>
-      </c>
-      <c r="J49" s="4">
-        <v>78</v>
-      </c>
-      <c r="K49" s="4">
-        <v>81</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="49" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
       <c r="P49" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 45 | Cultivated agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q49" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 45 | Cultivated agricultural lands | Small grain |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R49" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 45 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S49" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 45 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Poor |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T49" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 45 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |60 |71 |78 |81 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U49" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 45 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |60 |71 |78 |81 | | | |</v>
-      </c>
-    </row>
-    <row r="50" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="4">
-        <v>46</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H50" s="4">
-        <v>58</v>
-      </c>
-      <c r="I50" s="4">
-        <v>69</v>
-      </c>
-      <c r="J50" s="4">
-        <v>77</v>
-      </c>
-      <c r="K50" s="4">
-        <v>80</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="50" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
       <c r="P50" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 46 | Cultivated agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q50" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 46 | Cultivated agricultural lands | Small grain |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R50" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 46 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S50" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 46 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Good |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T50" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 46 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |58 |69 |77 |80 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U50" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 46 | Cultivated agricultural lands | Small grain | Contoured &amp; terraced (C &amp; T) + Crop residue cover (CR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |58 |69 |77 |80 | | | |</v>
-      </c>
-    </row>
-    <row r="51" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="4">
-        <v>47</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H51" s="4">
-        <v>66</v>
-      </c>
-      <c r="I51" s="4">
-        <v>77</v>
-      </c>
-      <c r="J51" s="4">
-        <v>85</v>
-      </c>
-      <c r="K51" s="4">
-        <v>89</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="51" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
       <c r="P51" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 47 | Cultivated agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q51" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 47 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R51" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 47 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Straight row (SR) |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S51" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 47 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Straight row (SR) |Poor |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T51" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 47 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Straight row (SR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |66 |77 |85 |89 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U51" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 47 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Straight row (SR) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |66 |77 |85 |89 | | | |</v>
-      </c>
-    </row>
-    <row r="52" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="4">
-        <v>48</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H52" s="4">
-        <v>58</v>
-      </c>
-      <c r="I52" s="4">
-        <v>72</v>
-      </c>
-      <c r="J52" s="4">
-        <v>81</v>
-      </c>
-      <c r="K52" s="4">
-        <v>85</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="52" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
       <c r="P52" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 48 | Cultivated agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q52" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 48 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R52" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 48 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Straight row (SR) |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S52" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 48 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Straight row (SR) |Good |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T52" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 48 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Straight row (SR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |58 |72 |81 |85 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U52" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 48 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Straight row (SR) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |58 |72 |81 |85 | | | |</v>
-      </c>
-    </row>
-    <row r="53" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="4">
-        <v>49</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H53" s="4">
-        <v>64</v>
-      </c>
-      <c r="I53" s="4">
-        <v>75</v>
-      </c>
-      <c r="J53" s="4">
-        <v>83</v>
-      </c>
-      <c r="K53" s="4">
-        <v>85</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="53" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
       <c r="P53" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 49 | Cultivated agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q53" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 49 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R53" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 49 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured (C) |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S53" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 49 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured (C) |Poor |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T53" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 49 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured (C) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |64 |75 |83 |85 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U53" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 49 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured (C) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |64 |75 |83 |85 | | | |</v>
-      </c>
-    </row>
-    <row r="54" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="4">
-        <v>50</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H54" s="4">
-        <v>55</v>
-      </c>
-      <c r="I54" s="4">
-        <v>69</v>
-      </c>
-      <c r="J54" s="4">
-        <v>78</v>
-      </c>
-      <c r="K54" s="4">
-        <v>83</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="54" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
       <c r="P54" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 50 | Cultivated agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q54" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 50 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R54" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 50 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured (C) |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S54" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 50 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured (C) |Good |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T54" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 50 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured (C) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |55 |69 |78 |83 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U54" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 50 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured (C) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |55 |69 |78 |83 | | | |</v>
-      </c>
-    </row>
-    <row r="55" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="4">
-        <v>51</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H55" s="4">
-        <v>63</v>
-      </c>
-      <c r="I55" s="4">
-        <v>73</v>
-      </c>
-      <c r="J55" s="4">
-        <v>80</v>
-      </c>
-      <c r="K55" s="4">
-        <v>83</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="55" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
       <c r="P55" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 51 | Cultivated agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q55" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 51 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R55" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 51 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured &amp; terraced (C &amp; T) |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S55" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 51 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured &amp; terraced (C &amp; T) |Poor |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T55" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 51 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured &amp; terraced (C &amp; T) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |63 |73 |80 |83 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U55" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 51 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured &amp; terraced (C &amp; T) |Poor |&lt;sub&gt;Factors impair infiltration and tend to increase runoff.&lt;/sub&gt; |63 |73 |80 |83 | | | |</v>
-      </c>
-    </row>
-    <row r="56" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="4">
-        <v>52</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H56" s="4">
-        <v>51</v>
-      </c>
-      <c r="I56" s="4">
-        <v>67</v>
-      </c>
-      <c r="J56" s="4">
-        <v>76</v>
-      </c>
-      <c r="K56" s="4">
-        <v>80</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="56" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
       <c r="P56" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 52 | Cultivated agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q56" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 52 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R56" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 52 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured &amp; terraced (C &amp; T) |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S56" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 52 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured &amp; terraced (C &amp; T) |Good |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T56" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 52 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured &amp; terraced (C &amp; T) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |51 |67 |76 |80 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U56" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 52 | Cultivated agricultural lands | Close-seeded or broadcast legumes or rotation meadow | Contoured &amp; terraced (C &amp; T) |Good |&lt;sub&gt;Factors encourage average and better than average infiltration and tend to decrease runoff.&lt;/sub&gt; |51 |67 |76 |80 | | | |</v>
-      </c>
-    </row>
-    <row r="57" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="4">
-        <v>53</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>61</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="57" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
       <c r="E57" s="4"/>
-      <c r="F57" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H57" s="4">
-        <v>68</v>
-      </c>
-      <c r="I57" s="4">
-        <v>79</v>
-      </c>
-      <c r="J57" s="4">
-        <v>86</v>
-      </c>
-      <c r="K57" s="4">
-        <v>89</v>
-      </c>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
       <c r="N57" s="4"/>
       <c r="O57" s="4"/>
       <c r="P57" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 53 | Other agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q57" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 53 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R57" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 53 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S57" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 53 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Poor |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T57" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 53 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Poor |&lt;sub&gt;&lt;/sub&gt; |68 |79 |86 |89 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U57" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 53 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Poor |&lt;sub&gt;&lt;/sub&gt; |68 |79 |86 |89 | | | |</v>
-      </c>
-    </row>
-    <row r="58" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="4">
-        <v>54</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>61</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="58" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
       <c r="E58" s="4"/>
-      <c r="F58" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="H58" s="4">
-        <v>49</v>
-      </c>
-      <c r="I58" s="4">
-        <v>69</v>
-      </c>
-      <c r="J58" s="4">
-        <v>79</v>
-      </c>
-      <c r="K58" s="4">
-        <v>84</v>
-      </c>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
       <c r="P58" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 54 | Other agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q58" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 54 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R58" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 54 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S58" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 54 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Fair |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T58" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 54 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Fair |&lt;sub&gt;50 to 75% ground cover and not heavily grazed.&lt;/sub&gt; |49 |69 |79 |84 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U58" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 54 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Fair |&lt;sub&gt;50 to 75% ground cover and not heavily grazed.&lt;/sub&gt; |49 |69 |79 |84 | | | |</v>
-      </c>
-    </row>
-    <row r="59" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="4">
-        <v>55</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>61</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="59" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
       <c r="E59" s="4"/>
-      <c r="F59" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="H59" s="4">
-        <v>39</v>
-      </c>
-      <c r="I59" s="4">
-        <v>61</v>
-      </c>
-      <c r="J59" s="4">
-        <v>74</v>
-      </c>
-      <c r="K59" s="4">
-        <v>80</v>
-      </c>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
       <c r="P59" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 55 | Other agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q59" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 55 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R59" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 55 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S59" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 55 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Good |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T59" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 55 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Good |&lt;sub&gt;&gt;75% ground cover and lightly or only occasionally grazed.&lt;/sub&gt; |39 |61 |74 |80 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U59" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 55 | Other agricultural lands | Pasture, grassland, or range – continuous forage for graving |  |Good |&lt;sub&gt;&gt;75% ground cover and lightly or only occasionally grazed.&lt;/sub&gt; |39 |61 |74 |80 | | | |</v>
-      </c>
-    </row>
-    <row r="60" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="4">
-        <v>56</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>63</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="60" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
       <c r="E60" s="4"/>
-      <c r="F60" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H60" s="4">
-        <v>30</v>
-      </c>
-      <c r="I60" s="4">
-        <v>58</v>
-      </c>
-      <c r="J60" s="4">
-        <v>71</v>
-      </c>
-      <c r="K60" s="4">
-        <v>78</v>
-      </c>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
       <c r="P60" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 56 | Other agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q60" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 56 | Other agricultural lands | Meadow – continuous grass, protected from grazing and generally mowed for hay |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R60" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 56 | Other agricultural lands | Meadow – continuous grass, protected from grazing and generally mowed for hay |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S60" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 56 | Other agricultural lands | Meadow – continuous grass, protected from grazing and generally mowed for hay |  |Unique |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T60" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 56 | Other agricultural lands | Meadow – continuous grass, protected from grazing and generally mowed for hay |  |Unique |&lt;sub&gt;&lt;/sub&gt; |30 |58 |71 |78 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U60" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 56 | Other agricultural lands | Meadow – continuous grass, protected from grazing and generally mowed for hay |  |Unique |&lt;sub&gt;&lt;/sub&gt; |30 |58 |71 |78 | | | |</v>
-      </c>
-    </row>
-    <row r="61" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="4">
-        <v>57</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>64</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="61" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
       <c r="E61" s="4"/>
-      <c r="F61" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H61" s="4">
-        <v>48</v>
-      </c>
-      <c r="I61" s="4">
-        <v>67</v>
-      </c>
-      <c r="J61" s="4">
-        <v>77</v>
-      </c>
-      <c r="K61" s="4">
-        <v>83</v>
-      </c>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
       <c r="P61" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 57 | Other agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q61" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 57 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R61" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 57 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S61" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 57 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Poor |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T61" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 57 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Poor |&lt;sub&gt;&lt;/sub&gt; |48 |67 |77 |83 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U61" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 57 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Poor |&lt;sub&gt;&lt;/sub&gt; |48 |67 |77 |83 | | | |</v>
-      </c>
-    </row>
-    <row r="62" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="4">
-        <v>58</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>64</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="62" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
       <c r="E62" s="4"/>
-      <c r="F62" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="H62" s="4">
-        <v>35</v>
-      </c>
-      <c r="I62" s="4">
-        <v>56</v>
-      </c>
-      <c r="J62" s="4">
-        <v>70</v>
-      </c>
-      <c r="K62" s="4">
-        <v>77</v>
-      </c>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
       <c r="P62" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 58 | Other agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q62" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 58 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R62" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 58 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S62" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 58 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Fair |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T62" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 58 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Fair |&lt;sub&gt;50 to 75% ground cover.&lt;/sub&gt; |35 |56 |70 |77 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U62" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 58 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Fair |&lt;sub&gt;50 to 75% ground cover.&lt;/sub&gt; |35 |56 |70 |77 | | | |</v>
-      </c>
-    </row>
-    <row r="63" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B63" s="4">
-        <v>59</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>64</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="63" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
       <c r="E63" s="4"/>
-      <c r="F63" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>87</v>
-      </c>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
       <c r="H63" s="4"/>
-      <c r="I63" s="4">
-        <v>48</v>
-      </c>
-      <c r="J63" s="4">
-        <v>65</v>
-      </c>
-      <c r="K63" s="4">
-        <v>73</v>
-      </c>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
       <c r="N63" s="4"/>
       <c r="O63" s="4"/>
       <c r="P63" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 59 | Other agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q63" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 59 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R63" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 59 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S63" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 59 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Good |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T63" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 59 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Good |&lt;sub&gt;&gt;75% ground cover. Actual curve number is less than 30; use CN=30 for runoff computations.&lt;/sub&gt; | |48 |65 |73 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U63" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 59 | Other agricultural lands | Brush – brush-weed mixture with brush the major element |  |Good |&lt;sub&gt;&gt;75% ground cover. Actual curve number is less than 30; use CN=30 for runoff computations.&lt;/sub&gt; | |48 |65 |73 | | | |</v>
-      </c>
-    </row>
-    <row r="64" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="4">
-        <v>60</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>65</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="64" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
       <c r="E64" s="4"/>
-      <c r="F64" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="H64" s="4">
-        <v>57</v>
-      </c>
-      <c r="I64" s="4">
-        <v>73</v>
-      </c>
-      <c r="J64" s="4">
-        <v>82</v>
-      </c>
-      <c r="K64" s="4">
-        <v>86</v>
-      </c>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
       <c r="P64" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 60 | Other agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q64" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 60 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R64" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 60 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S64" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 60 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Poor |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T64" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 60 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Poor |&lt;sub&gt;CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture.&lt;/sub&gt; |57 |73 |82 |86 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U64" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 60 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Poor |&lt;sub&gt;CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture.&lt;/sub&gt; |57 |73 |82 |86 | | | |</v>
-      </c>
-    </row>
-    <row r="65" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="4">
-        <v>61</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>65</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
       <c r="E65" s="4"/>
-      <c r="F65" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="H65" s="4">
-        <v>43</v>
-      </c>
-      <c r="I65" s="4">
-        <v>65</v>
-      </c>
-      <c r="J65" s="4">
-        <v>76</v>
-      </c>
-      <c r="K65" s="4">
-        <v>82</v>
-      </c>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
       <c r="L65" s="4"/>
       <c r="M65" s="4"/>
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
       <c r="P65" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 61 | Other agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q65" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 61 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R65" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 61 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S65" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 61 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Fair |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T65" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 61 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Fair |&lt;sub&gt;CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture.&lt;/sub&gt; |43 |65 |76 |82 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U65" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 61 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Fair |&lt;sub&gt;CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture.&lt;/sub&gt; |43 |65 |76 |82 | | | |</v>
-      </c>
-    </row>
-    <row r="66" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="4">
-        <v>62</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>65</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
       <c r="E66" s="4"/>
-      <c r="F66" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="H66" s="4">
-        <v>32</v>
-      </c>
-      <c r="I66" s="4">
-        <v>58</v>
-      </c>
-      <c r="J66" s="4">
-        <v>72</v>
-      </c>
-      <c r="K66" s="4">
-        <v>79</v>
-      </c>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
       <c r="P66" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 62 | Other agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q66" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 62 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R66" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 62 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S66" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 62 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Good |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T66" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 62 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Good |&lt;sub&gt;CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture.&lt;/sub&gt; |32 |58 |72 |79 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U66" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 62 | Other agricultural lands | Woods – grass combination (orchard or tree farm) |  |Good |&lt;sub&gt;CN's shown were computed for areas with 50% woods and 50% grass (pasture) cover. Other combinations of conditions may be computed from the CN's for woods and pasture.&lt;/sub&gt; |32 |58 |72 |79 | | | |</v>
-      </c>
-    </row>
-    <row r="67" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="4">
-        <v>63</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
       <c r="E67" s="4"/>
-      <c r="F67" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H67" s="4">
-        <v>45</v>
-      </c>
-      <c r="I67" s="4">
-        <v>66</v>
-      </c>
-      <c r="J67" s="4">
-        <v>77</v>
-      </c>
-      <c r="K67" s="4">
-        <v>83</v>
-      </c>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
       <c r="P67" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 63 | Other agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q67" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 63 | Other agricultural lands | Woods |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R67" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| 63 | Other agricultural lands | Woods |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S67" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 63 | Other agricultural lands | Woods |  |Poor |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T67" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| 63 | Other agricultural lands | Woods |  |Poor |&lt;sub&gt;Forest litter, small trees, and brush are destroyed by heavy grazing or regular burning.&lt;/sub&gt; |45 |66 |77 |83 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U67" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 63 | Other agricultural lands | Woods |  |Poor |&lt;sub&gt;Forest litter, small trees, and brush are destroyed by heavy grazing or regular burning.&lt;/sub&gt; |45 |66 |77 |83 | | | |</v>
-      </c>
-    </row>
-    <row r="68" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="4">
-        <v>64</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="68" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
       <c r="E68" s="4"/>
-      <c r="F68" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="H68" s="4">
-        <v>36</v>
-      </c>
-      <c r="I68" s="4">
-        <v>60</v>
-      </c>
-      <c r="J68" s="4">
-        <v>73</v>
-      </c>
-      <c r="K68" s="4">
-        <v>79</v>
-      </c>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
       <c r="P68" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 64 | Other agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q68" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 64 | Other agricultural lands | Woods |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R68" s="5" t="str">
         <f t="shared" ref="R68:R103" si="8">_xlfn.CONCAT("| ",B68," | ",C68," | ",D68," | ",E68," |")</f>
-        <v>| 64 | Other agricultural lands | Woods |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S68" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 64 | Other agricultural lands | Woods |  |Fair |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T68" s="5" t="str">
         <f t="shared" ref="T68:T103" si="9">_xlfn.CONCAT("| ",B68," | ",C68," | ",D68," | ",E68," |",F68," |",G68," |",H68," |",I68," |",J68," |",K68," |")</f>
-        <v>| 64 | Other agricultural lands | Woods |  |Fair |&lt;sub&gt;Woods are grazed but not burned, and some forest litter covers the soil.&lt;/sub&gt; |36 |60 |73 |79 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U68" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 64 | Other agricultural lands | Woods |  |Fair |&lt;sub&gt;Woods are grazed but not burned, and some forest litter covers the soil.&lt;/sub&gt; |36 |60 |73 |79 | | | |</v>
-      </c>
-    </row>
-    <row r="69" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="4">
-        <v>65</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
       <c r="E69" s="4"/>
-      <c r="F69" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>91</v>
-      </c>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
       <c r="H69" s="4"/>
-      <c r="I69" s="4">
-        <v>55</v>
-      </c>
-      <c r="J69" s="4">
-        <v>70</v>
-      </c>
-      <c r="K69" s="4">
-        <v>77</v>
-      </c>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
       <c r="P69" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 65 | Other agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q69" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 65 | Other agricultural lands | Woods |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R69" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>| 65 | Other agricultural lands | Woods |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S69" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| 65 | Other agricultural lands | Woods |  |Good |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T69" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 65 | Other agricultural lands | Woods |  |Good |&lt;sub&gt;Woods are protected from grazing, and litter and brush adequately cover the soil. Actual curve number is less than 30; use CN=30 for runoff computations.&lt;/sub&gt; | |55 |70 |77 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U69" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| 65 | Other agricultural lands | Woods |  |Good |&lt;sub&gt;Woods are protected from grazing, and litter and brush adequately cover the soil. Actual curve number is less than 30; use CN=30 for runoff computations.&lt;/sub&gt; | |55 |70 |77 | | | |</v>
-      </c>
-    </row>
-    <row r="70" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="4">
-        <v>66</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>67</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
       <c r="E70" s="4"/>
-      <c r="F70" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H70" s="4">
-        <v>59</v>
-      </c>
-      <c r="I70" s="4">
-        <v>74</v>
-      </c>
-      <c r="J70" s="4">
-        <v>82</v>
-      </c>
-      <c r="K70" s="4">
-        <v>86</v>
-      </c>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
       <c r="P70" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 66 | Other agricultural lands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q70" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 66 | Other agricultural lands | Farmsteads – buildings, lanes, driveways, surrounding lots |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R70" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>| 66 | Other agricultural lands | Farmsteads – buildings, lanes, driveways, surrounding lots |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S70" s="5" t="str">
         <f t="shared" ref="S70:S103" si="10">_xlfn.CONCAT("| ",B70," | ",C70," | ",D70," | ",E70," |",F70," |")</f>
-        <v>| 66 | Other agricultural lands | Farmsteads – buildings, lanes, driveways, surrounding lots |  |Unique |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T70" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 66 | Other agricultural lands | Farmsteads – buildings, lanes, driveways, surrounding lots |  |Unique |&lt;sub&gt;&lt;/sub&gt; |59 |74 |82 |86 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U70" s="5" t="str">
         <f t="shared" ref="U70:U103" si="11">_xlfn.CONCAT("| ",B70," | ",C70," | ",D70," | ",E70," |",F70," |",G70," |",H70," |",I70," |",J70," |",K70," |",L70," |",M70," |",N70," |")</f>
-        <v>| 66 | Other agricultural lands | Farmsteads – buildings, lanes, driveways, surrounding lots |  |Unique |&lt;sub&gt;&lt;/sub&gt; |59 |74 |82 |86 | | | |</v>
-      </c>
-    </row>
-    <row r="71" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="4">
-        <v>67</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>69</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
       <c r="E71" s="4"/>
-      <c r="F71" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>78</v>
-      </c>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
       <c r="H71" s="4"/>
-      <c r="I71" s="4">
-        <v>80</v>
-      </c>
-      <c r="J71" s="4">
-        <v>87</v>
-      </c>
-      <c r="K71" s="4">
-        <v>93</v>
-      </c>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
       <c r="P71" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 67 | Arid and semiarid rangelands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q71" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 67 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R71" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>| 67 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S71" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>| 67 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Poor |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T71" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 67 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Poor |&lt;sub&gt;&lt;/sub&gt; | |80 |87 |93 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U71" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 67 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Poor |&lt;sub&gt;&lt;/sub&gt; | |80 |87 |93 | | | |</v>
-      </c>
-    </row>
-    <row r="72" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="4">
-        <v>68</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>69</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
       <c r="E72" s="4"/>
-      <c r="F72" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>92</v>
-      </c>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
       <c r="H72" s="4"/>
-      <c r="I72" s="4">
-        <v>71</v>
-      </c>
-      <c r="J72" s="4">
-        <v>81</v>
-      </c>
-      <c r="K72" s="4">
-        <v>89</v>
-      </c>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
       <c r="P72" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 68 | Arid and semiarid rangelands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q72" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 68 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R72" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>| 68 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S72" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>| 68 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Fair |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T72" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 68 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |71 |81 |89 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U72" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 68 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |71 |81 |89 | | | |</v>
-      </c>
-    </row>
-    <row r="73" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="4">
-        <v>69</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>69</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
       <c r="E73" s="4"/>
-      <c r="F73" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>93</v>
-      </c>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
       <c r="H73" s="4"/>
-      <c r="I73" s="4">
-        <v>62</v>
-      </c>
-      <c r="J73" s="4">
-        <v>74</v>
-      </c>
-      <c r="K73" s="4">
-        <v>85</v>
-      </c>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
       <c r="P73" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 69 | Arid and semiarid rangelands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q73" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 69 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R73" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>| 69 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S73" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>| 69 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Good |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T73" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 69 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Good |&lt;sub&gt;&gt;70% ground cover.&lt;/sub&gt; | |62 |74 |85 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U73" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 69 | Arid and semiarid rangelands | Herbaceous – mixture of grass, weeds, and low-growing brush, with brush the minor element |  |Good |&lt;sub&gt;&gt;70% ground cover.&lt;/sub&gt; | |62 |74 |85 | | | |</v>
-      </c>
-    </row>
-    <row r="74" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="4">
-        <v>70</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>70</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
       <c r="E74" s="4"/>
-      <c r="F74" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>78</v>
-      </c>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
       <c r="H74" s="4"/>
-      <c r="I74" s="4">
-        <v>66</v>
-      </c>
-      <c r="J74" s="4">
-        <v>74</v>
-      </c>
-      <c r="K74" s="4">
-        <v>79</v>
-      </c>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
       <c r="P74" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 70 | Arid and semiarid rangelands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q74" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 70 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R74" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>| 70 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S74" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>| 70 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Poor |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T74" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 70 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Poor |&lt;sub&gt;&lt;/sub&gt; | |66 |74 |79 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U74" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 70 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Poor |&lt;sub&gt;&lt;/sub&gt; | |66 |74 |79 | | | |</v>
-      </c>
-    </row>
-    <row r="75" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="4">
-        <v>71</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>70</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
       <c r="E75" s="4"/>
-      <c r="F75" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>92</v>
-      </c>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
       <c r="H75" s="4"/>
-      <c r="I75" s="4">
-        <v>48</v>
-      </c>
-      <c r="J75" s="4">
-        <v>57</v>
-      </c>
-      <c r="K75" s="4">
-        <v>63</v>
-      </c>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
       <c r="L75" s="4"/>
       <c r="M75" s="4"/>
       <c r="N75" s="4"/>
       <c r="O75" s="4"/>
       <c r="P75" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 71 | Arid and semiarid rangelands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q75" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 71 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R75" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>| 71 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S75" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>| 71 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Fair |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T75" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 71 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |48 |57 |63 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U75" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 71 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |48 |57 |63 | | | |</v>
-      </c>
-    </row>
-    <row r="76" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="4">
-        <v>72</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>70</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
       <c r="E76" s="4"/>
-      <c r="F76" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>94</v>
-      </c>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
       <c r="H76" s="4"/>
-      <c r="I76" s="4">
-        <v>30</v>
-      </c>
-      <c r="J76" s="4">
-        <v>41</v>
-      </c>
-      <c r="K76" s="4">
-        <v>48</v>
-      </c>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
       <c r="L76" s="4"/>
       <c r="M76" s="4"/>
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
       <c r="P76" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 72 | Arid and semiarid rangelands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q76" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 72 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R76" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>| 72 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S76" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>| 72 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Good |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T76" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 72 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Good |&lt;sub&gt;&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |30 |41 |48 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U76" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 72 | Arid and semiarid rangelands | Oak-aspen – mountain brush mixture of oak brush, aspen, mountain mahogany, bitter brush, maple, and other brush |  |Good |&lt;sub&gt;&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |30 |41 |48 | | | |</v>
-      </c>
-    </row>
-    <row r="77" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="4">
-        <v>73</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>71</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
       <c r="E77" s="4"/>
-      <c r="F77" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>78</v>
-      </c>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
       <c r="H77" s="4"/>
-      <c r="I77" s="4">
-        <v>75</v>
-      </c>
-      <c r="J77" s="4">
-        <v>85</v>
-      </c>
-      <c r="K77" s="4">
-        <v>89</v>
-      </c>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
       <c r="L77" s="4"/>
       <c r="M77" s="4"/>
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
       <c r="P77" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 73 | Arid and semiarid rangelands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q77" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 73 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R77" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>| 73 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S77" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>| 73 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Poor |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T77" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 73 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Poor |&lt;sub&gt;&lt;/sub&gt; | |75 |85 |89 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U77" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 73 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Poor |&lt;sub&gt;&lt;/sub&gt; | |75 |85 |89 | | | |</v>
-      </c>
-    </row>
-    <row r="78" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="4">
-        <v>74</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>71</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="78" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
       <c r="E78" s="4"/>
-      <c r="F78" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>92</v>
-      </c>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
       <c r="H78" s="4"/>
-      <c r="I78" s="4">
-        <v>58</v>
-      </c>
-      <c r="J78" s="4">
-        <v>73</v>
-      </c>
-      <c r="K78" s="4">
-        <v>80</v>
-      </c>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
       <c r="N78" s="4"/>
       <c r="O78" s="4"/>
       <c r="P78" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 74 | Arid and semiarid rangelands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q78" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 74 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R78" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>| 74 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S78" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>| 74 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Fair |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T78" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 74 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |58 |73 |80 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U78" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 74 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |58 |73 |80 | | | |</v>
-      </c>
-    </row>
-    <row r="79" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="4">
-        <v>75</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>71</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
       <c r="E79" s="4"/>
-      <c r="F79" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>94</v>
-      </c>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
       <c r="H79" s="4"/>
-      <c r="I79" s="4">
-        <v>41</v>
-      </c>
-      <c r="J79" s="4">
-        <v>61</v>
-      </c>
-      <c r="K79" s="4">
-        <v>71</v>
-      </c>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
       <c r="N79" s="4"/>
       <c r="O79" s="4"/>
       <c r="P79" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 75 | Arid and semiarid rangelands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q79" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 75 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R79" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>| 75 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S79" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>| 75 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Good |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T79" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 75 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Good |&lt;sub&gt;&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |41 |61 |71 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U79" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 75 | Arid and semiarid rangelands | Pinyon-juniper – pinyon, juniper, or both; grass understory |  |Good |&lt;sub&gt;&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |41 |61 |71 | | | |</v>
-      </c>
-    </row>
-    <row r="80" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="4">
-        <v>76</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>72</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="80" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
       <c r="E80" s="4"/>
-      <c r="F80" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>78</v>
-      </c>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
       <c r="H80" s="4"/>
-      <c r="I80" s="4">
-        <v>67</v>
-      </c>
-      <c r="J80" s="4">
-        <v>80</v>
-      </c>
-      <c r="K80" s="4">
-        <v>85</v>
-      </c>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
       <c r="N80" s="4"/>
       <c r="O80" s="4"/>
       <c r="P80" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 76 | Arid and semiarid rangelands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q80" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 76 | Arid and semiarid rangelands | Sagebrush with grass understory |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R80" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>| 76 | Arid and semiarid rangelands | Sagebrush with grass understory |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S80" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>| 76 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Poor |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T80" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 76 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Poor |&lt;sub&gt;&lt;/sub&gt; | |67 |80 |85 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U80" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 76 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Poor |&lt;sub&gt;&lt;/sub&gt; | |67 |80 |85 | | | |</v>
-      </c>
-    </row>
-    <row r="81" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" s="4">
-        <v>77</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>72</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="81" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
       <c r="E81" s="4"/>
-      <c r="F81" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>92</v>
-      </c>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
       <c r="H81" s="4"/>
-      <c r="I81" s="4">
-        <v>51</v>
-      </c>
-      <c r="J81" s="4">
-        <v>63</v>
-      </c>
-      <c r="K81" s="4">
-        <v>70</v>
-      </c>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
       <c r="P81" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 77 | Arid and semiarid rangelands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q81" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 77 | Arid and semiarid rangelands | Sagebrush with grass understory |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R81" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>| 77 | Arid and semiarid rangelands | Sagebrush with grass understory |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S81" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>| 77 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Fair |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T81" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 77 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |51 |63 |70 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U81" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 77 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |51 |63 |70 | | | |</v>
-      </c>
-    </row>
-    <row r="82" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" s="4">
-        <v>78</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>72</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="82" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
       <c r="E82" s="4"/>
-      <c r="F82" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>94</v>
-      </c>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
       <c r="H82" s="4"/>
-      <c r="I82" s="4">
-        <v>35</v>
-      </c>
-      <c r="J82" s="4">
-        <v>47</v>
-      </c>
-      <c r="K82" s="4">
-        <v>55</v>
-      </c>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
       <c r="P82" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 78 | Arid and semiarid rangelands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q82" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 78 | Arid and semiarid rangelands | Sagebrush with grass understory |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R82" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>| 78 | Arid and semiarid rangelands | Sagebrush with grass understory |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S82" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>| 78 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Good |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T82" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 78 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Good |&lt;sub&gt;&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |35 |47 |55 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U82" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 78 | Arid and semiarid rangelands | Sagebrush with grass understory |  |Good |&lt;sub&gt;&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; | |35 |47 |55 | | | |</v>
-      </c>
-    </row>
-    <row r="83" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" s="4">
-        <v>79</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>73</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="83" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
       <c r="E83" s="4"/>
-      <c r="F83" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H83" s="4">
-        <v>63</v>
-      </c>
-      <c r="I83" s="4">
-        <v>77</v>
-      </c>
-      <c r="J83" s="4">
-        <v>85</v>
-      </c>
-      <c r="K83" s="4">
-        <v>88</v>
-      </c>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
       <c r="P83" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 79 | Arid and semiarid rangelands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q83" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 79 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R83" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>| 79 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S83" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>| 79 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Poor |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T83" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 79 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Poor |&lt;sub&gt;&lt;/sub&gt; |63 |77 |85 |88 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U83" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 79 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Poor |&lt;sub&gt;&lt;/sub&gt; |63 |77 |85 |88 | | | |</v>
-      </c>
-    </row>
-    <row r="84" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" s="4">
-        <v>80</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>73</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="84" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
       <c r="E84" s="4"/>
-      <c r="F84" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H84" s="4">
-        <v>55</v>
-      </c>
-      <c r="I84" s="4">
-        <v>72</v>
-      </c>
-      <c r="J84" s="4">
-        <v>81</v>
-      </c>
-      <c r="K84" s="4">
-        <v>86</v>
-      </c>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
       <c r="P84" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 80 | Arid and semiarid rangelands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q84" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 80 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R84" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>| 80 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S84" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>| 80 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Fair |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T84" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 80 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; |55 |72 |81 |86 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U84" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 80 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Fair |&lt;sub&gt;30 to 70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; |55 |72 |81 |86 | | | |</v>
-      </c>
-    </row>
-    <row r="85" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" s="4">
-        <v>81</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>73</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="85" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
       <c r="E85" s="4"/>
-      <c r="F85" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="H85" s="4">
-        <v>49</v>
-      </c>
-      <c r="I85" s="4">
-        <v>68</v>
-      </c>
-      <c r="J85" s="4">
-        <v>79</v>
-      </c>
-      <c r="K85" s="4">
-        <v>84</v>
-      </c>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
       <c r="P85" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 81 | Arid and semiarid rangelands |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q85" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 81 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R85" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>| 81 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S85" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>| 81 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Good |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T85" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 81 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Good |&lt;sub&gt;&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; |49 |68 |79 |84 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U85" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 81 | Arid and semiarid rangelands | Desert shrub – major plants include saltbrush, greasewood, creosotebush, blackbrush, bursage, palo verde, mesquite, and cactus. |  |Good |&lt;sub&gt;&gt;70% ground cover. Curve numbers for group A have been developed only for desert shrub.&lt;/sub&gt; |49 |68 |79 |84 | | | |</v>
-      </c>
-    </row>
-    <row r="86" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="4">
-        <v>82</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="H86" s="4">
-        <v>96</v>
-      </c>
-      <c r="I86" s="4">
-        <v>96</v>
-      </c>
-      <c r="J86" s="4">
-        <v>96</v>
-      </c>
-      <c r="K86" s="4">
-        <v>96</v>
-      </c>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="86" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="4"/>
       <c r="L86" s="4"/>
       <c r="M86" s="4"/>
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
       <c r="P86" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| 82 | Unclassified |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q86" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| 82 | Unclassified | Water body |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R86" s="5" t="str">
         <f t="shared" si="8"/>
-        <v>| 82 | Unclassified | Water body | Water body |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S86" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>| 82 | Unclassified | Water body | Water body |Unique |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T86" s="5" t="str">
         <f t="shared" si="9"/>
-        <v>| 82 | Unclassified | Water body | Water body |Unique |&lt;sub&gt;rcfdtools&lt;/sub&gt; |96 |96 |96 |96 |</v>
+        <v>|  |  |  |  | | | | | | |</v>
       </c>
       <c r="U86" s="5" t="str">
         <f t="shared" si="11"/>
-        <v>| 82 | Unclassified | Water body | Water body |Unique |&lt;sub&gt;rcfdtools&lt;/sub&gt; |96 |96 |96 |96 | | | |</v>
-      </c>
-    </row>
-    <row r="87" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="87" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
@@ -6277,7 +5155,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="88" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
@@ -6317,7 +5195,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="89" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
@@ -6357,7 +5235,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="90" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -6397,7 +5275,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="91" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -6437,7 +5315,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="92" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -6477,7 +5355,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="93" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
@@ -6517,7 +5395,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="94" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
@@ -6557,7 +5435,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="95" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
@@ -6597,7 +5475,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="96" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
@@ -6637,7 +5515,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="97" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
@@ -6677,7 +5555,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="98" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
@@ -6717,7 +5595,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="99" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
@@ -6757,7 +5635,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="100" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
@@ -6797,7 +5675,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="101" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
@@ -6837,7 +5715,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="102" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
@@ -6877,7 +5755,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="103" spans="2:21" ht="21.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>

--- a/file/temp/ExcelTableToMarkDownSample2.xlsx
+++ b/file/temp/ExcelTableToMarkDownSample2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.HydroTools\file\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89E8000-A028-4283-BA8B-0BBC7853F13A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52ED6D72-41E3-426C-8412-67A5B03154AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{D94F812B-BC61-4A22-9692-634766FE0D40}"/>
+    <workbookView xWindow="-28920" yWindow="6990" windowWidth="29040" windowHeight="15720" xr2:uid="{D94F812B-BC61-4A22-9692-634766FE0D40}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="104">
   <si>
     <t>Creación de tablas en formato .md</t>
   </si>
@@ -73,319 +73,66 @@
     <t>Versión</t>
   </si>
   <si>
-    <t>Portal</t>
-  </si>
-  <si>
     <t>Archivo local</t>
   </si>
   <si>
-    <t>IDEAM</t>
-  </si>
-  <si>
-    <t>http://www.ideam.gov.co/</t>
-  </si>
-  <si>
-    <t>IDEAM.GuiaMonitoreoVertimiento.pdf</t>
-  </si>
-  <si>
     <t>Protocolo para el monitoreo y seguimiento del agua</t>
   </si>
   <si>
-    <t>IDEAM.ProtocoloMonitoreoSeguimientoAgua.2007.pdf</t>
-  </si>
-  <si>
-    <t>IDEAM.HIMAT.ManualObservadorMeteorologico.1987.pdf</t>
-  </si>
-  <si>
-    <t>IDEAM.DocumentoMetodologicoVariableMeteorologica.20180516.pdf</t>
-  </si>
-  <si>
-    <t>IGAC - Resolución 1562 año 2018</t>
-  </si>
-  <si>
-    <t>https://www.igac.gov.co/</t>
-  </si>
-  <si>
-    <t>Resolucion1562de2018.IGAC.pdf</t>
-  </si>
-  <si>
-    <t>IGAC - Resolución 471 de 2020</t>
-  </si>
-  <si>
-    <t>Resolucion471de2020.IGAC.pdf</t>
-  </si>
-  <si>
-    <t>IGAC - Resolución 715 del 2018</t>
-  </si>
-  <si>
-    <t>Resolucion715de2018.IGAC.pdf</t>
-  </si>
-  <si>
-    <t>OMM-N°0008</t>
-  </si>
-  <si>
-    <t>https://library.wmo.int/?lvl=notice_display&amp;id=5280</t>
-  </si>
-  <si>
-    <t>WMO.0008GuiaInstrumentoMetodoObservacionMeteorologico.2019.pdf</t>
-  </si>
-  <si>
-    <t>OMM-N°0100</t>
-  </si>
-  <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=10027</t>
-  </si>
-  <si>
-    <t>WMO.0100.GuiaPracticaClimatologica.2018.pdf</t>
-  </si>
-  <si>
-    <t>OMM-N°0168</t>
-  </si>
-  <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=10456</t>
-  </si>
-  <si>
-    <t>WMO.0168.GuiaPracticaHidrologicaVol1Hidrologia.2008.pdf</t>
-  </si>
-  <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=10038</t>
-  </si>
-  <si>
-    <t>WMO.0168.GuiaPracticaHidrologicaVol2Hidrologia.2011.pdf</t>
-  </si>
-  <si>
-    <t>OMM-N°0182</t>
-  </si>
-  <si>
     <t>Vocabulario Meteorológico Internacional</t>
   </si>
   <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=4712</t>
-  </si>
-  <si>
-    <t>WMO.0182.VocabularioMeteorologicoInternacional.1992.pdf</t>
-  </si>
-  <si>
-    <t>OMM-N°0386</t>
-  </si>
-  <si>
     <t>Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM</t>
   </si>
   <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=10470</t>
-  </si>
-  <si>
-    <t>WMO.0386.ManualSistemaMundialTelecomunicacion.2020.pdf</t>
-  </si>
-  <si>
-    <t>OMM-N°0488</t>
-  </si>
-  <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=5440</t>
-  </si>
-  <si>
-    <t>WMO.0488.GuiaSistemaMundialObservacion.2017.pdf</t>
-  </si>
-  <si>
-    <t>OMM-N°0544</t>
-  </si>
-  <si>
     <t>Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico</t>
   </si>
   <si>
-    <t>WMO.0544.ManualSistemaMundialObservacionVolumen1.2017.pdf</t>
-  </si>
-  <si>
-    <t>OMM-N°1061</t>
-  </si>
-  <si>
     <t>Guía del Sistema de Información de la OMM</t>
   </si>
   <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=10258</t>
-  </si>
-  <si>
-    <t>WMO.1061.GuiaSistemaInformacionOMM.2018.pdf</t>
-  </si>
-  <si>
-    <t>OMM-N°1091</t>
-  </si>
-  <si>
     <t>Directrices sobre los sistemas de predicción por conjuntos y la predicción</t>
   </si>
   <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=7774</t>
-  </si>
-  <si>
-    <t>WMO.1091.DirectricesSistemasPrediccionConjuntos.2012.pdf</t>
-  </si>
-  <si>
-    <t>OMM-N°1100</t>
-  </si>
-  <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=5742</t>
-  </si>
-  <si>
-    <t>WMO.1100.GuiaAplicacionSistemasGestionCalidadServicioMeteorologicoHidrologico.2017.pdf</t>
-  </si>
-  <si>
-    <t>OMM-N°1160</t>
-  </si>
-  <si>
     <t>Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM</t>
   </si>
   <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=10230</t>
-  </si>
-  <si>
-    <t>WMO.1160.ManualSistemaIntegradoObservacionOMM.2019.pdf</t>
-  </si>
-  <si>
-    <t>OMM-N°1165</t>
-  </si>
-  <si>
     <t>Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM</t>
   </si>
   <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=10042</t>
-  </si>
-  <si>
-    <t>WMO.1165.GuiaSistemaMundialIntegradoSistemaObservacionOMM.2019.pdf</t>
-  </si>
-  <si>
-    <t>OMM-N°1182</t>
-  </si>
-  <si>
     <t>Directrices sobre mejores prácticas para el rescate de datos climáticos</t>
   </si>
   <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=3529</t>
-  </si>
-  <si>
-    <t>WMO.1182.DirectrizRescateDatoClimatico.2016.pdf</t>
-  </si>
-  <si>
-    <t>OMM-N°1192</t>
-  </si>
-  <si>
     <t>Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM</t>
   </si>
   <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=10163</t>
-  </si>
-  <si>
-    <t>WMO.1192.NormaMetadatoSistemaMundialIntegradoObservacion.2019</t>
-  </si>
-  <si>
-    <t>OMM-N°1203</t>
-  </si>
-  <si>
     <t>Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas</t>
   </si>
   <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=4167</t>
-  </si>
-  <si>
-    <t>WMO.01203.DirectricezCalculoNormalClimatica.2017.pdf</t>
-  </si>
-  <si>
-    <t>WMO-N°0199</t>
-  </si>
-  <si>
     <t>Some Methods of Climatological Analysis</t>
   </si>
   <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=1961</t>
-  </si>
-  <si>
-    <t>WMO.0199.SomeMethodsClimatologicalAnalysis.1966.pdf</t>
-  </si>
-  <si>
-    <t>WMO-N°0415</t>
-  </si>
-  <si>
     <t>On The Statistical Analysis of Series of Observations</t>
   </si>
   <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=1065</t>
-  </si>
-  <si>
-    <t>WMO.0415.StatisticalAnalysisSerieObservation.1990.pdf</t>
-  </si>
-  <si>
-    <t>WMO-N°0485</t>
-  </si>
-  <si>
     <t>Manual del Sistema Mundial de Proceso de Datos y de Predicción</t>
   </si>
   <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=10281</t>
-  </si>
-  <si>
-    <t>WMO.0485.ManualSistemaMundialProcesoDatosPrediccion.2019.pdf</t>
-  </si>
-  <si>
-    <t>WMO-N°1131</t>
-  </si>
-  <si>
     <t>Climate Data Management System Specifications</t>
   </si>
   <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=7867</t>
-  </si>
-  <si>
-    <t>WMO.1131.ClimateDataManagementSystem.2014.pdf</t>
-  </si>
-  <si>
-    <t>WMO-N°1170</t>
-  </si>
-  <si>
     <t>Climate Services for Supporting Climate Change Adaptation</t>
   </si>
   <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=7936</t>
-  </si>
-  <si>
-    <t>WMO.1170.ClimateServiceForSupportingClimateChangeAdaptation.2016.pdf</t>
-  </si>
-  <si>
-    <t>WMO-N°1221</t>
-  </si>
-  <si>
     <t>Guidelines on Quality Management in Climate Services</t>
   </si>
   <si>
-    <t>https://library.wmo.int/doc_num.php?explnum_id=5174</t>
-  </si>
-  <si>
-    <t>WMO.1221.GuidelinesQualityManagementClimateServices.2018.pdf</t>
-  </si>
-  <si>
-    <t>https://public.wmo.int/</t>
-  </si>
-  <si>
-    <t>ISO-19115</t>
-  </si>
-  <si>
-    <t>https://www.iso.org/standard/26020.html</t>
-  </si>
-  <si>
-    <t>ISO-IEC-11179 Partes 1 a 7</t>
-  </si>
-  <si>
     <t>Varias</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.iso.org/standard/61932.html
-</t>
-  </si>
-  <si>
     <t>Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes</t>
   </si>
   <si>
-    <t>WMO</t>
-  </si>
-  <si>
     <t>Guía para el monitoreo de vertimientos</t>
   </si>
   <si>
@@ -425,13 +172,185 @@
     <t>Normas asociadas a metodologías para actividades hidrometeorológicas</t>
   </si>
   <si>
-    <t>https://wmo.int/wmo-no-544-manual-global-observing-system</t>
-  </si>
-  <si>
     <t>Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB</t>
   </si>
   <si>
-    <t>Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos.</t>
+    <t>Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos</t>
+  </si>
+  <si>
+    <t>[IDEAM](http://www.ideam.gov.co/)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](IDEAM.GuiaMonitoreoVertimiento.pdf)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](IDEAM.ProtocoloMonitoreoSeguimientoAgua.2007.pdf)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](IDEAM.HIMAT.ManualObservadorMeteorologico.1987.pdf)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](IDEAM.DocumentoMetodologicoVariableMeteorologica.20180516.pdf)</t>
+  </si>
+  <si>
+    <t>[IGAC - Resolución 1562 año 2018](https://www.igac.gov.co/)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](Resolucion1562de2018.IGAC.pdf)</t>
+  </si>
+  <si>
+    <t>[IGAC - Resolución 471 de 2020](https://www.igac.gov.co/)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](Resolucion471de2020.IGAC.pdf)</t>
+  </si>
+  <si>
+    <t>[IGAC - Resolución 715 del 2018](https://www.igac.gov.co/)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](Resolucion715de2018.IGAC.pdf)</t>
+  </si>
+  <si>
+    <t>[OMM-N°0008](https://library.wmo.int/?lvl=notice_display&amp;id=5280)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.0008GuiaInstrumentoMetodoObservacionMeteorologico.2019.pdf)</t>
+  </si>
+  <si>
+    <t>[OMM-N°0100](https://library.wmo.int/doc_num.php?explnum_id=10027)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.0100.GuiaPracticaClimatologica.2018.pdf)</t>
+  </si>
+  <si>
+    <t>[OMM-N°0168](https://library.wmo.int/doc_num.php?explnum_id=10456)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.0168.GuiaPracticaHidrologicaVol1Hidrologia.2008.pdf)</t>
+  </si>
+  <si>
+    <t>[OMM-N°0168](https://library.wmo.int/doc_num.php?explnum_id=10038)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.0168.GuiaPracticaHidrologicaVol2Hidrologia.2011.pdf)</t>
+  </si>
+  <si>
+    <t>[OMM-N°0182](https://library.wmo.int/doc_num.php?explnum_id=4712)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.0182.VocabularioMeteorologicoInternacional.1992.pdf)</t>
+  </si>
+  <si>
+    <t>[OMM-N°0386](https://library.wmo.int/doc_num.php?explnum_id=10470)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.0386.ManualSistemaMundialTelecomunicacion.2020.pdf)</t>
+  </si>
+  <si>
+    <t>[OMM-N°0488](https://library.wmo.int/doc_num.php?explnum_id=5440)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.0488.GuiaSistemaMundialObservacion.2017.pdf)</t>
+  </si>
+  <si>
+    <t>[OMM-N°0544](https://wmo.int/wmo-no-544-manual-global-observing-system)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.0544.ManualSistemaMundialObservacionVolumen1.2017.pdf)</t>
+  </si>
+  <si>
+    <t>[OMM-N°1061](https://library.wmo.int/doc_num.php?explnum_id=10258)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.1061.GuiaSistemaInformacionOMM.2018.pdf)</t>
+  </si>
+  <si>
+    <t>[OMM-N°1091](https://library.wmo.int/doc_num.php?explnum_id=7774)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.1091.DirectricesSistemasPrediccionConjuntos.2012.pdf)</t>
+  </si>
+  <si>
+    <t>[OMM-N°1100](https://library.wmo.int/doc_num.php?explnum_id=5742)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.1100.GuiaAplicacionSistemasGestionCalidadServicioMeteorologicoHidrologico.2017.pdf)</t>
+  </si>
+  <si>
+    <t>[OMM-N°1160](https://library.wmo.int/doc_num.php?explnum_id=10230)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.1160.ManualSistemaIntegradoObservacionOMM.2019.pdf)</t>
+  </si>
+  <si>
+    <t>[OMM-N°1165](https://library.wmo.int/doc_num.php?explnum_id=10042)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.1165.GuiaSistemaMundialIntegradoSistemaObservacionOMM.2019.pdf)</t>
+  </si>
+  <si>
+    <t>[OMM-N°1182](https://library.wmo.int/doc_num.php?explnum_id=3529)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.1182.DirectrizRescateDatoClimatico.2016.pdf)</t>
+  </si>
+  <si>
+    <t>[OMM-N°1192](https://library.wmo.int/doc_num.php?explnum_id=10163)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.1192.NormaMetadatoSistemaMundialIntegradoObservacion.2019)</t>
+  </si>
+  <si>
+    <t>[OMM-N°1203](https://library.wmo.int/doc_num.php?explnum_id=4167)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.01203.DirectricezCalculoNormalClimatica.2017.pdf)</t>
+  </si>
+  <si>
+    <t>[WMO-N°0199](https://library.wmo.int/doc_num.php?explnum_id=1961)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.0199.SomeMethodsClimatologicalAnalysis.1966.pdf)</t>
+  </si>
+  <si>
+    <t>[WMO-N°0415](https://library.wmo.int/doc_num.php?explnum_id=1065)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.0415.StatisticalAnalysisSerieObservation.1990.pdf)</t>
+  </si>
+  <si>
+    <t>[WMO-N°0485](https://library.wmo.int/doc_num.php?explnum_id=10281)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.0485.ManualSistemaMundialProcesoDatosPrediccion.2019.pdf)</t>
+  </si>
+  <si>
+    <t>[WMO-N°1131](https://library.wmo.int/doc_num.php?explnum_id=7867)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.1131.ClimateDataManagementSystem.2014.pdf)</t>
+  </si>
+  <si>
+    <t>[WMO-N°1170](https://library.wmo.int/doc_num.php?explnum_id=7936)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.1170.ClimateServiceForSupportingClimateChangeAdaptation.2016.pdf)</t>
+  </si>
+  <si>
+    <t>[WMO-N°1221](https://library.wmo.int/doc_num.php?explnum_id=5174)</t>
+  </si>
+  <si>
+    <t>[:bookmark_tabs:](WMO.1221.GuidelinesQualityManagementClimateServices.2018.pdf)</t>
+  </si>
+  <si>
+    <t>[WMO](https://public.wmo.int/)</t>
+  </si>
+  <si>
+    <t>[ISO-19115](https://www.iso.org/standard/26020.html)</t>
+  </si>
+  <si>
+    <t>[ISO-IEC-11179 Partes 1 a 7](https://www.iso.org/standard/61932.html
+)</t>
   </si>
 </sst>
 </file>
@@ -955,7 +874,7 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -983,6 +902,9 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="43" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="43" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -1346,7 +1268,7 @@
   <cols>
     <col min="1" max="1" width="2.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="38" style="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="104.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.5703125" style="1" customWidth="1"/>
     <col min="5" max="5" width="52.640625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="54.85546875" style="1" customWidth="1"/>
@@ -1408,9 +1330,7 @@
       <c r="E3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -1430,19 +1350,19 @@
       </c>
       <c r="R3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |")</f>
-        <v>| Referencia | Alcance | Versión | Portal |</v>
+        <v>| Referencia | Alcance | Versión | Archivo local |</v>
       </c>
       <c r="S3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |")</f>
-        <v>| Referencia | Alcance | Versión | Portal |Archivo local |</v>
+        <v>| Referencia | Alcance | Versión | Archivo local | |</v>
       </c>
       <c r="T3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |",G3," |",H3," |",I3," |",J3," |",K3," |")</f>
-        <v>| Referencia | Alcance | Versión | Portal |Archivo local | | | | | |</v>
+        <v>| Referencia | Alcance | Versión | Archivo local | | | | | | |</v>
       </c>
       <c r="U3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |",G3," |",H3," |",I3," |",J3," |",K3," |",L3," |",M3," |",N3," |")</f>
-        <v>| Referencia | Alcance | Versión | Portal |Archivo local | | | | | | | | |</v>
+        <v>| Referencia | Alcance | Versión | Archivo local | | | | | | | | | |</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.55000000000000004">
@@ -1511,20 +1431,18 @@
         <v>| --- | --- | --- | --- |--- |--- |--- |--- |--- |--- |--- |--- |--- |</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="5" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -1536,45 +1454,43 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B5," | ",C5," |")</f>
-        <v>| IDEAM | Guía para el monitoreo de vertimientos |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Guía para el monitoreo de vertimientos |</v>
       </c>
       <c r="Q5" s="5" t="str">
         <f t="shared" ref="Q5:Q24" si="1">_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," |")</f>
-        <v>| IDEAM | Guía para el monitoreo de vertimientos |  |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Guía para el monitoreo de vertimientos |  |</v>
       </c>
       <c r="R5" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," | ",E5," |")</f>
-        <v>| IDEAM | Guía para el monitoreo de vertimientos |  | http://www.ideam.gov.co/ |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Guía para el monitoreo de vertimientos |  | [:bookmark_tabs:](IDEAM.GuiaMonitoreoVertimiento.pdf) |</v>
       </c>
       <c r="S5" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," | ",E5," |",F5," |")</f>
-        <v>| IDEAM | Guía para el monitoreo de vertimientos |  | http://www.ideam.gov.co/ |IDEAM.GuiaMonitoreoVertimiento.pdf |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Guía para el monitoreo de vertimientos |  | [:bookmark_tabs:](IDEAM.GuiaMonitoreoVertimiento.pdf) | |</v>
       </c>
       <c r="T5" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| IDEAM | Guía para el monitoreo de vertimientos |  | http://www.ideam.gov.co/ |IDEAM.GuiaMonitoreoVertimiento.pdf | | | | | |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Guía para el monitoreo de vertimientos |  | [:bookmark_tabs:](IDEAM.GuiaMonitoreoVertimiento.pdf) | | | | | | |</v>
       </c>
       <c r="U5" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," | ",E5," |",F5," |",G5," |",H5," |",I5," |",J5," |",K5," |",L5," |",M5," |",N5," |")</f>
-        <v>| IDEAM | Guía para el monitoreo de vertimientos |  | http://www.ideam.gov.co/ |IDEAM.GuiaMonitoreoVertimiento.pdf | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="6" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Guía para el monitoreo de vertimientos |  | [:bookmark_tabs:](IDEAM.GuiaMonitoreoVertimiento.pdf) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="5" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D6" s="5">
         <v>2007</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>17</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -1586,40 +1502,38 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5" t="str">
         <f t="shared" ref="P6:P24" si="2">_xlfn.CONCAT("| ",B6," | ",C6," |")</f>
-        <v>| IDEAM | Protocolo para el monitoreo y seguimiento del agua |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Protocolo para el monitoreo y seguimiento del agua |</v>
       </c>
       <c r="Q6" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| IDEAM | Protocolo para el monitoreo y seguimiento del agua | 2007 |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Protocolo para el monitoreo y seguimiento del agua | 2007 |</v>
       </c>
       <c r="R6" s="5" t="str">
         <f t="shared" ref="R6:R67" si="3">_xlfn.CONCAT("| ",B6," | ",C6," | ",D6," | ",E6," |")</f>
-        <v>| IDEAM | Protocolo para el monitoreo y seguimiento del agua | 2007 | http://www.ideam.gov.co/ |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Protocolo para el monitoreo y seguimiento del agua | 2007 | [:bookmark_tabs:](IDEAM.ProtocoloMonitoreoSeguimientoAgua.2007.pdf) |</v>
       </c>
       <c r="S6" s="5" t="str">
         <f t="shared" ref="S6:S69" si="4">_xlfn.CONCAT("| ",B6," | ",C6," | ",D6," | ",E6," |",F6," |")</f>
-        <v>| IDEAM | Protocolo para el monitoreo y seguimiento del agua | 2007 | http://www.ideam.gov.co/ |IDEAM.ProtocoloMonitoreoSeguimientoAgua.2007.pdf |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Protocolo para el monitoreo y seguimiento del agua | 2007 | [:bookmark_tabs:](IDEAM.ProtocoloMonitoreoSeguimientoAgua.2007.pdf) | |</v>
       </c>
       <c r="T6" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| IDEAM | Protocolo para el monitoreo y seguimiento del agua | 2007 | http://www.ideam.gov.co/ |IDEAM.ProtocoloMonitoreoSeguimientoAgua.2007.pdf | | | | | |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Protocolo para el monitoreo y seguimiento del agua | 2007 | [:bookmark_tabs:](IDEAM.ProtocoloMonitoreoSeguimientoAgua.2007.pdf) | | | | | | |</v>
       </c>
       <c r="U6" s="5" t="str">
         <f t="shared" ref="U6:U69" si="5">_xlfn.CONCAT("| ",B6," | ",C6," | ",D6," | ",E6," |",F6," |",G6," |",H6," |",I6," |",J6," |",K6," |",L6," |",M6," |",N6," |")</f>
-        <v>| IDEAM | Protocolo para el monitoreo y seguimiento del agua | 2007 | http://www.ideam.gov.co/ |IDEAM.ProtocoloMonitoreoSeguimientoAgua.2007.pdf | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="7" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Protocolo para el monitoreo y seguimiento del agua | 2007 | [:bookmark_tabs:](IDEAM.ProtocoloMonitoreoSeguimientoAgua.2007.pdf) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="5" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="D7" s="5"/>
-      <c r="E7" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
@@ -1632,45 +1546,43 @@
       <c r="O7" s="5"/>
       <c r="P7" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| IDEAM | Normas, manuales, metodologías y procedimientos asociados a actividades hidrometeorológicas |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Normas, manuales, metodologías y procedimientos asociados a actividades hidrometeorológicas |</v>
       </c>
       <c r="Q7" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| IDEAM | Normas, manuales, metodologías y procedimientos asociados a actividades hidrometeorológicas |  |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Normas, manuales, metodologías y procedimientos asociados a actividades hidrometeorológicas |  |</v>
       </c>
       <c r="R7" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| IDEAM | Normas, manuales, metodologías y procedimientos asociados a actividades hidrometeorológicas |  | http://www.ideam.gov.co/ |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Normas, manuales, metodologías y procedimientos asociados a actividades hidrometeorológicas |  |  |</v>
       </c>
       <c r="S7" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| IDEAM | Normas, manuales, metodologías y procedimientos asociados a actividades hidrometeorológicas |  | http://www.ideam.gov.co/ | |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Normas, manuales, metodologías y procedimientos asociados a actividades hidrometeorológicas |  |  | |</v>
       </c>
       <c r="T7" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| IDEAM | Normas, manuales, metodologías y procedimientos asociados a actividades hidrometeorológicas |  | http://www.ideam.gov.co/ | | | | | | |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Normas, manuales, metodologías y procedimientos asociados a actividades hidrometeorológicas |  |  | | | | | | |</v>
       </c>
       <c r="U7" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| IDEAM | Normas, manuales, metodologías y procedimientos asociados a actividades hidrometeorológicas |  | http://www.ideam.gov.co/ | | | | | | | | | |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Normas, manuales, metodologías y procedimientos asociados a actividades hidrometeorológicas |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="8" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="5" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>117</v>
+        <v>33</v>
       </c>
       <c r="D8" s="5">
         <v>1987</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>18</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -1682,40 +1594,38 @@
       <c r="O8" s="5"/>
       <c r="P8" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| IDEAM | Manual del observador meteorológico |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Manual del observador meteorológico |</v>
       </c>
       <c r="Q8" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| IDEAM | Manual del observador meteorológico | 1987 |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Manual del observador meteorológico | 1987 |</v>
       </c>
       <c r="R8" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| IDEAM | Manual del observador meteorológico | 1987 | http://www.ideam.gov.co/ |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Manual del observador meteorológico | 1987 | [:bookmark_tabs:](IDEAM.HIMAT.ManualObservadorMeteorologico.1987.pdf) |</v>
       </c>
       <c r="S8" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| IDEAM | Manual del observador meteorológico | 1987 | http://www.ideam.gov.co/ |IDEAM.HIMAT.ManualObservadorMeteorologico.1987.pdf |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Manual del observador meteorológico | 1987 | [:bookmark_tabs:](IDEAM.HIMAT.ManualObservadorMeteorologico.1987.pdf) | |</v>
       </c>
       <c r="T8" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| IDEAM | Manual del observador meteorológico | 1987 | http://www.ideam.gov.co/ |IDEAM.HIMAT.ManualObservadorMeteorologico.1987.pdf | | | | | |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Manual del observador meteorológico | 1987 | [:bookmark_tabs:](IDEAM.HIMAT.ManualObservadorMeteorologico.1987.pdf) | | | | | | |</v>
       </c>
       <c r="U8" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| IDEAM | Manual del observador meteorológico | 1987 | http://www.ideam.gov.co/ |IDEAM.HIMAT.ManualObservadorMeteorologico.1987.pdf | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="9" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Manual del observador meteorológico | 1987 | [:bookmark_tabs:](IDEAM.HIMAT.ManualObservadorMeteorologico.1987.pdf) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="5" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="D9" s="5"/>
-      <c r="E9" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -1728,43 +1638,41 @@
       <c r="O9" s="5"/>
       <c r="P9" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| IDEAM | Manual de operaciones de la red hidrometeorológica |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Manual de operaciones de la red hidrometeorológica |</v>
       </c>
       <c r="Q9" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| IDEAM | Manual de operaciones de la red hidrometeorológica |  |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Manual de operaciones de la red hidrometeorológica |  |</v>
       </c>
       <c r="R9" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| IDEAM | Manual de operaciones de la red hidrometeorológica |  | http://www.ideam.gov.co/ |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Manual de operaciones de la red hidrometeorológica |  |  |</v>
       </c>
       <c r="S9" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| IDEAM | Manual de operaciones de la red hidrometeorológica |  | http://www.ideam.gov.co/ | |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Manual de operaciones de la red hidrometeorológica |  |  | |</v>
       </c>
       <c r="T9" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| IDEAM | Manual de operaciones de la red hidrometeorológica |  | http://www.ideam.gov.co/ | | | | | | |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Manual de operaciones de la red hidrometeorológica |  |  | | | | | | |</v>
       </c>
       <c r="U9" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| IDEAM | Manual de operaciones de la red hidrometeorológica |  | http://www.ideam.gov.co/ | | | | | | | | | |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) | Manual de operaciones de la red hidrometeorológica |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="10" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="5" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5">
         <v>2018</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>19</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -1776,45 +1684,43 @@
       <c r="O10" s="5"/>
       <c r="P10" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| IDEAM |  |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) |  |</v>
       </c>
       <c r="Q10" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| IDEAM |  | 2018 |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) |  | 2018 |</v>
       </c>
       <c r="R10" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| IDEAM |  | 2018 | http://www.ideam.gov.co/ |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) |  | 2018 | [:bookmark_tabs:](IDEAM.DocumentoMetodologicoVariableMeteorologica.20180516.pdf) |</v>
       </c>
       <c r="S10" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| IDEAM |  | 2018 | http://www.ideam.gov.co/ |IDEAM.DocumentoMetodologicoVariableMeteorologica.20180516.pdf |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) |  | 2018 | [:bookmark_tabs:](IDEAM.DocumentoMetodologicoVariableMeteorologica.20180516.pdf) | |</v>
       </c>
       <c r="T10" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| IDEAM |  | 2018 | http://www.ideam.gov.co/ |IDEAM.DocumentoMetodologicoVariableMeteorologica.20180516.pdf | | | | | |</v>
+        <v>| [IDEAM](http://www.ideam.gov.co/) |  | 2018 | [:bookmark_tabs:](IDEAM.DocumentoMetodologicoVariableMeteorologica.20180516.pdf) | | | | | | |</v>
       </c>
       <c r="U10" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| IDEAM |  | 2018 | http://www.ideam.gov.co/ |IDEAM.DocumentoMetodologicoVariableMeteorologica.20180516.pdf | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="11" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+        <v>| [IDEAM](http://www.ideam.gov.co/) |  | 2018 | [:bookmark_tabs:](IDEAM.DocumentoMetodologicoVariableMeteorologica.20180516.pdf) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="11" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="5" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="D11" s="5">
         <v>2018</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>22</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -1826,45 +1732,43 @@
       <c r="O11" s="5"/>
       <c r="P11" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| IGAC - Resolución 1562 año 2018 | Por medio de la cual se definen los valores que representan la calidad de los puntos medidos en redes geodésicas y levantamientos geodésicos |</v>
+        <v>| [IGAC - Resolución 1562 año 2018](https://www.igac.gov.co/) | Por medio de la cual se definen los valores que representan la calidad de los puntos medidos en redes geodésicas y levantamientos geodésicos |</v>
       </c>
       <c r="Q11" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| IGAC - Resolución 1562 año 2018 | Por medio de la cual se definen los valores que representan la calidad de los puntos medidos en redes geodésicas y levantamientos geodésicos | 2018 |</v>
+        <v>| [IGAC - Resolución 1562 año 2018](https://www.igac.gov.co/) | Por medio de la cual se definen los valores que representan la calidad de los puntos medidos en redes geodésicas y levantamientos geodésicos | 2018 |</v>
       </c>
       <c r="R11" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| IGAC - Resolución 1562 año 2018 | Por medio de la cual se definen los valores que representan la calidad de los puntos medidos en redes geodésicas y levantamientos geodésicos | 2018 | https://www.igac.gov.co/ |</v>
+        <v>| [IGAC - Resolución 1562 año 2018](https://www.igac.gov.co/) | Por medio de la cual se definen los valores que representan la calidad de los puntos medidos en redes geodésicas y levantamientos geodésicos | 2018 | [:bookmark_tabs:](Resolucion1562de2018.IGAC.pdf) |</v>
       </c>
       <c r="S11" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| IGAC - Resolución 1562 año 2018 | Por medio de la cual se definen los valores que representan la calidad de los puntos medidos en redes geodésicas y levantamientos geodésicos | 2018 | https://www.igac.gov.co/ |Resolucion1562de2018.IGAC.pdf |</v>
+        <v>| [IGAC - Resolución 1562 año 2018](https://www.igac.gov.co/) | Por medio de la cual se definen los valores que representan la calidad de los puntos medidos en redes geodésicas y levantamientos geodésicos | 2018 | [:bookmark_tabs:](Resolucion1562de2018.IGAC.pdf) | |</v>
       </c>
       <c r="T11" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| IGAC - Resolución 1562 año 2018 | Por medio de la cual se definen los valores que representan la calidad de los puntos medidos en redes geodésicas y levantamientos geodésicos | 2018 | https://www.igac.gov.co/ |Resolucion1562de2018.IGAC.pdf | | | | | |</v>
+        <v>| [IGAC - Resolución 1562 año 2018](https://www.igac.gov.co/) | Por medio de la cual se definen los valores que representan la calidad de los puntos medidos en redes geodésicas y levantamientos geodésicos | 2018 | [:bookmark_tabs:](Resolucion1562de2018.IGAC.pdf) | | | | | | |</v>
       </c>
       <c r="U11" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| IGAC - Resolución 1562 año 2018 | Por medio de la cual se definen los valores que representan la calidad de los puntos medidos en redes geodésicas y levantamientos geodésicos | 2018 | https://www.igac.gov.co/ |Resolucion1562de2018.IGAC.pdf | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="12" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+        <v>| [IGAC - Resolución 1562 año 2018](https://www.igac.gov.co/) | Por medio de la cual se definen los valores que representan la calidad de los puntos medidos en redes geodésicas y levantamientos geodésicos | 2018 | [:bookmark_tabs:](Resolucion1562de2018.IGAC.pdf) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="5" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="D12" s="5">
         <v>2020</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>24</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -1876,45 +1780,43 @@
       <c r="O12" s="5"/>
       <c r="P12" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| IGAC - Resolución 471 de 2020 | Por medio de la cual se establecen las especificaciones técnicas mínimas que deben tener los Productos de la cartografía básica oficial de Colombia |</v>
+        <v>| [IGAC - Resolución 471 de 2020](https://www.igac.gov.co/) | Por medio de la cual se establecen las especificaciones técnicas mínimas que deben tener los Productos de la cartografía básica oficial de Colombia |</v>
       </c>
       <c r="Q12" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| IGAC - Resolución 471 de 2020 | Por medio de la cual se establecen las especificaciones técnicas mínimas que deben tener los Productos de la cartografía básica oficial de Colombia | 2020 |</v>
+        <v>| [IGAC - Resolución 471 de 2020](https://www.igac.gov.co/) | Por medio de la cual se establecen las especificaciones técnicas mínimas que deben tener los Productos de la cartografía básica oficial de Colombia | 2020 |</v>
       </c>
       <c r="R12" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| IGAC - Resolución 471 de 2020 | Por medio de la cual se establecen las especificaciones técnicas mínimas que deben tener los Productos de la cartografía básica oficial de Colombia | 2020 | https://www.igac.gov.co/ |</v>
+        <v>| [IGAC - Resolución 471 de 2020](https://www.igac.gov.co/) | Por medio de la cual se establecen las especificaciones técnicas mínimas que deben tener los Productos de la cartografía básica oficial de Colombia | 2020 | [:bookmark_tabs:](Resolucion471de2020.IGAC.pdf) |</v>
       </c>
       <c r="S12" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| IGAC - Resolución 471 de 2020 | Por medio de la cual se establecen las especificaciones técnicas mínimas que deben tener los Productos de la cartografía básica oficial de Colombia | 2020 | https://www.igac.gov.co/ |Resolucion471de2020.IGAC.pdf |</v>
+        <v>| [IGAC - Resolución 471 de 2020](https://www.igac.gov.co/) | Por medio de la cual se establecen las especificaciones técnicas mínimas que deben tener los Productos de la cartografía básica oficial de Colombia | 2020 | [:bookmark_tabs:](Resolucion471de2020.IGAC.pdf) | |</v>
       </c>
       <c r="T12" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| IGAC - Resolución 471 de 2020 | Por medio de la cual se establecen las especificaciones técnicas mínimas que deben tener los Productos de la cartografía básica oficial de Colombia | 2020 | https://www.igac.gov.co/ |Resolucion471de2020.IGAC.pdf | | | | | |</v>
+        <v>| [IGAC - Resolución 471 de 2020](https://www.igac.gov.co/) | Por medio de la cual se establecen las especificaciones técnicas mínimas que deben tener los Productos de la cartografía básica oficial de Colombia | 2020 | [:bookmark_tabs:](Resolucion471de2020.IGAC.pdf) | | | | | | |</v>
       </c>
       <c r="U12" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| IGAC - Resolución 471 de 2020 | Por medio de la cual se establecen las especificaciones técnicas mínimas que deben tener los Productos de la cartografía básica oficial de Colombia | 2020 | https://www.igac.gov.co/ |Resolucion471de2020.IGAC.pdf | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="13" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+        <v>| [IGAC - Resolución 471 de 2020](https://www.igac.gov.co/) | Por medio de la cual se establecen las especificaciones técnicas mínimas que deben tener los Productos de la cartografía básica oficial de Colombia | 2020 | [:bookmark_tabs:](Resolucion471de2020.IGAC.pdf) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="5" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>121</v>
+        <v>37</v>
       </c>
       <c r="D13" s="5">
         <v>2018</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>26</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -1926,45 +1828,43 @@
       <c r="O13" s="5"/>
       <c r="P13" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| IGAC - Resolución 715 del 2018 | Por la cual se actualiza el Sistema de Referencia Geocéntrico para Las Américas (SIRGAS) |</v>
+        <v>| [IGAC - Resolución 715 del 2018](https://www.igac.gov.co/) | Por la cual se actualiza el Sistema de Referencia Geocéntrico para Las Américas (SIRGAS) |</v>
       </c>
       <c r="Q13" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| IGAC - Resolución 715 del 2018 | Por la cual se actualiza el Sistema de Referencia Geocéntrico para Las Américas (SIRGAS) | 2018 |</v>
+        <v>| [IGAC - Resolución 715 del 2018](https://www.igac.gov.co/) | Por la cual se actualiza el Sistema de Referencia Geocéntrico para Las Américas (SIRGAS) | 2018 |</v>
       </c>
       <c r="R13" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| IGAC - Resolución 715 del 2018 | Por la cual se actualiza el Sistema de Referencia Geocéntrico para Las Américas (SIRGAS) | 2018 | https://www.igac.gov.co/ |</v>
+        <v>| [IGAC - Resolución 715 del 2018](https://www.igac.gov.co/) | Por la cual se actualiza el Sistema de Referencia Geocéntrico para Las Américas (SIRGAS) | 2018 | [:bookmark_tabs:](Resolucion715de2018.IGAC.pdf) |</v>
       </c>
       <c r="S13" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| IGAC - Resolución 715 del 2018 | Por la cual se actualiza el Sistema de Referencia Geocéntrico para Las Américas (SIRGAS) | 2018 | https://www.igac.gov.co/ |Resolucion715de2018.IGAC.pdf |</v>
+        <v>| [IGAC - Resolución 715 del 2018](https://www.igac.gov.co/) | Por la cual se actualiza el Sistema de Referencia Geocéntrico para Las Américas (SIRGAS) | 2018 | [:bookmark_tabs:](Resolucion715de2018.IGAC.pdf) | |</v>
       </c>
       <c r="T13" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| IGAC - Resolución 715 del 2018 | Por la cual se actualiza el Sistema de Referencia Geocéntrico para Las Américas (SIRGAS) | 2018 | https://www.igac.gov.co/ |Resolucion715de2018.IGAC.pdf | | | | | |</v>
+        <v>| [IGAC - Resolución 715 del 2018](https://www.igac.gov.co/) | Por la cual se actualiza el Sistema de Referencia Geocéntrico para Las Américas (SIRGAS) | 2018 | [:bookmark_tabs:](Resolucion715de2018.IGAC.pdf) | | | | | | |</v>
       </c>
       <c r="U13" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| IGAC - Resolución 715 del 2018 | Por la cual se actualiza el Sistema de Referencia Geocéntrico para Las Américas (SIRGAS) | 2018 | https://www.igac.gov.co/ |Resolucion715de2018.IGAC.pdf | | | | | | | | |</v>
+        <v>| [IGAC - Resolución 715 del 2018](https://www.igac.gov.co/) | Por la cual se actualiza el Sistema de Referencia Geocéntrico para Las Américas (SIRGAS) | 2018 | [:bookmark_tabs:](Resolucion715de2018.IGAC.pdf) | | | | | | | | | |</v>
       </c>
     </row>
     <row r="14" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="5" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>122</v>
+        <v>38</v>
       </c>
       <c r="D14" s="5">
         <v>2019</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>29</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
@@ -1976,45 +1876,43 @@
       <c r="O14" s="5"/>
       <c r="P14" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| OMM-N°0008 | Guía de Instrumentos y Métodos de Observación Meteorológicos |</v>
+        <v>| [OMM-N°0008](https://library.wmo.int/?lvl=notice_display&amp;id=5280) | Guía de Instrumentos y Métodos de Observación Meteorológicos |</v>
       </c>
       <c r="Q14" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| OMM-N°0008 | Guía de Instrumentos y Métodos de Observación Meteorológicos | 2019 |</v>
+        <v>| [OMM-N°0008](https://library.wmo.int/?lvl=notice_display&amp;id=5280) | Guía de Instrumentos y Métodos de Observación Meteorológicos | 2019 |</v>
       </c>
       <c r="R14" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| OMM-N°0008 | Guía de Instrumentos y Métodos de Observación Meteorológicos | 2019 | https://library.wmo.int/?lvl=notice_display&amp;id=5280 |</v>
+        <v>| [OMM-N°0008](https://library.wmo.int/?lvl=notice_display&amp;id=5280) | Guía de Instrumentos y Métodos de Observación Meteorológicos | 2019 | [:bookmark_tabs:](WMO.0008GuiaInstrumentoMetodoObservacionMeteorologico.2019.pdf) |</v>
       </c>
       <c r="S14" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| OMM-N°0008 | Guía de Instrumentos y Métodos de Observación Meteorológicos | 2019 | https://library.wmo.int/?lvl=notice_display&amp;id=5280 |WMO.0008GuiaInstrumentoMetodoObservacionMeteorologico.2019.pdf |</v>
+        <v>| [OMM-N°0008](https://library.wmo.int/?lvl=notice_display&amp;id=5280) | Guía de Instrumentos y Métodos de Observación Meteorológicos | 2019 | [:bookmark_tabs:](WMO.0008GuiaInstrumentoMetodoObservacionMeteorologico.2019.pdf) | |</v>
       </c>
       <c r="T14" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| OMM-N°0008 | Guía de Instrumentos y Métodos de Observación Meteorológicos | 2019 | https://library.wmo.int/?lvl=notice_display&amp;id=5280 |WMO.0008GuiaInstrumentoMetodoObservacionMeteorologico.2019.pdf | | | | | |</v>
+        <v>| [OMM-N°0008](https://library.wmo.int/?lvl=notice_display&amp;id=5280) | Guía de Instrumentos y Métodos de Observación Meteorológicos | 2019 | [:bookmark_tabs:](WMO.0008GuiaInstrumentoMetodoObservacionMeteorologico.2019.pdf) | | | | | | |</v>
       </c>
       <c r="U14" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| OMM-N°0008 | Guía de Instrumentos y Métodos de Observación Meteorológicos | 2019 | https://library.wmo.int/?lvl=notice_display&amp;id=5280 |WMO.0008GuiaInstrumentoMetodoObservacionMeteorologico.2019.pdf | | | | | | | | |</v>
+        <v>| [OMM-N°0008](https://library.wmo.int/?lvl=notice_display&amp;id=5280) | Guía de Instrumentos y Métodos de Observación Meteorológicos | 2019 | [:bookmark_tabs:](WMO.0008GuiaInstrumentoMetodoObservacionMeteorologico.2019.pdf) | | | | | | | | | |</v>
       </c>
     </row>
     <row r="15" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="5" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>123</v>
+        <v>39</v>
       </c>
       <c r="D15" s="5">
         <v>2018</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>32</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
@@ -2026,45 +1924,43 @@
       <c r="O15" s="5"/>
       <c r="P15" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| OMM-N°0100 | Guía de prácticas climatológicas |</v>
+        <v>| [OMM-N°0100](https://library.wmo.int/doc_num.php?explnum_id=10027) | Guía de prácticas climatológicas |</v>
       </c>
       <c r="Q15" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| OMM-N°0100 | Guía de prácticas climatológicas | 2018 |</v>
+        <v>| [OMM-N°0100](https://library.wmo.int/doc_num.php?explnum_id=10027) | Guía de prácticas climatológicas | 2018 |</v>
       </c>
       <c r="R15" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| OMM-N°0100 | Guía de prácticas climatológicas | 2018 | https://library.wmo.int/doc_num.php?explnum_id=10027 |</v>
+        <v>| [OMM-N°0100](https://library.wmo.int/doc_num.php?explnum_id=10027) | Guía de prácticas climatológicas | 2018 | [:bookmark_tabs:](WMO.0100.GuiaPracticaClimatologica.2018.pdf) |</v>
       </c>
       <c r="S15" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| OMM-N°0100 | Guía de prácticas climatológicas | 2018 | https://library.wmo.int/doc_num.php?explnum_id=10027 |WMO.0100.GuiaPracticaClimatologica.2018.pdf |</v>
+        <v>| [OMM-N°0100](https://library.wmo.int/doc_num.php?explnum_id=10027) | Guía de prácticas climatológicas | 2018 | [:bookmark_tabs:](WMO.0100.GuiaPracticaClimatologica.2018.pdf) | |</v>
       </c>
       <c r="T15" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| OMM-N°0100 | Guía de prácticas climatológicas | 2018 | https://library.wmo.int/doc_num.php?explnum_id=10027 |WMO.0100.GuiaPracticaClimatologica.2018.pdf | | | | | |</v>
+        <v>| [OMM-N°0100](https://library.wmo.int/doc_num.php?explnum_id=10027) | Guía de prácticas climatológicas | 2018 | [:bookmark_tabs:](WMO.0100.GuiaPracticaClimatologica.2018.pdf) | | | | | | |</v>
       </c>
       <c r="U15" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| OMM-N°0100 | Guía de prácticas climatológicas | 2018 | https://library.wmo.int/doc_num.php?explnum_id=10027 |WMO.0100.GuiaPracticaClimatologica.2018.pdf | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="16" spans="2:21" ht="61.5" x14ac:dyDescent="0.55000000000000004">
+        <v>| [OMM-N°0100](https://library.wmo.int/doc_num.php?explnum_id=10027) | Guía de prácticas climatológicas | 2018 | [:bookmark_tabs:](WMO.0100.GuiaPracticaClimatologica.2018.pdf) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="5" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>124</v>
+        <v>40</v>
       </c>
       <c r="D16" s="5">
         <v>2008</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>35</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
@@ -2076,45 +1972,43 @@
       <c r="O16" s="5"/>
       <c r="P16" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen I Hidrología - De la medición a la información hidrológica. Edición 2008. Actualización 2020 |</v>
+        <v>| [OMM-N°0168](https://library.wmo.int/doc_num.php?explnum_id=10456) | Guía de prácticas hidrológicas. Volumen I Hidrología - De la medición a la información hidrológica. Edición 2008. Actualización 2020 |</v>
       </c>
       <c r="Q16" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen I Hidrología - De la medición a la información hidrológica. Edición 2008. Actualización 2020 | 2008 |</v>
+        <v>| [OMM-N°0168](https://library.wmo.int/doc_num.php?explnum_id=10456) | Guía de prácticas hidrológicas. Volumen I Hidrología - De la medición a la información hidrológica. Edición 2008. Actualización 2020 | 2008 |</v>
       </c>
       <c r="R16" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen I Hidrología - De la medición a la información hidrológica. Edición 2008. Actualización 2020 | 2008 | https://library.wmo.int/doc_num.php?explnum_id=10456 |</v>
+        <v>| [OMM-N°0168](https://library.wmo.int/doc_num.php?explnum_id=10456) | Guía de prácticas hidrológicas. Volumen I Hidrología - De la medición a la información hidrológica. Edición 2008. Actualización 2020 | 2008 | [:bookmark_tabs:](WMO.0168.GuiaPracticaHidrologicaVol1Hidrologia.2008.pdf) |</v>
       </c>
       <c r="S16" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen I Hidrología - De la medición a la información hidrológica. Edición 2008. Actualización 2020 | 2008 | https://library.wmo.int/doc_num.php?explnum_id=10456 |WMO.0168.GuiaPracticaHidrologicaVol1Hidrologia.2008.pdf |</v>
+        <v>| [OMM-N°0168](https://library.wmo.int/doc_num.php?explnum_id=10456) | Guía de prácticas hidrológicas. Volumen I Hidrología - De la medición a la información hidrológica. Edición 2008. Actualización 2020 | 2008 | [:bookmark_tabs:](WMO.0168.GuiaPracticaHidrologicaVol1Hidrologia.2008.pdf) | |</v>
       </c>
       <c r="T16" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen I Hidrología - De la medición a la información hidrológica. Edición 2008. Actualización 2020 | 2008 | https://library.wmo.int/doc_num.php?explnum_id=10456 |WMO.0168.GuiaPracticaHidrologicaVol1Hidrologia.2008.pdf | | | | | |</v>
+        <v>| [OMM-N°0168](https://library.wmo.int/doc_num.php?explnum_id=10456) | Guía de prácticas hidrológicas. Volumen I Hidrología - De la medición a la información hidrológica. Edición 2008. Actualización 2020 | 2008 | [:bookmark_tabs:](WMO.0168.GuiaPracticaHidrologicaVol1Hidrologia.2008.pdf) | | | | | | |</v>
       </c>
       <c r="U16" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen I Hidrología - De la medición a la información hidrológica. Edición 2008. Actualización 2020 | 2008 | https://library.wmo.int/doc_num.php?explnum_id=10456 |WMO.0168.GuiaPracticaHidrologicaVol1Hidrologia.2008.pdf | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="17" spans="2:21" ht="61.5" x14ac:dyDescent="0.55000000000000004">
+        <v>| [OMM-N°0168](https://library.wmo.int/doc_num.php?explnum_id=10456) | Guía de prácticas hidrológicas. Volumen I Hidrología - De la medición a la información hidrológica. Edición 2008. Actualización 2020 | 2008 | [:bookmark_tabs:](WMO.0168.GuiaPracticaHidrologicaVol1Hidrologia.2008.pdf) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="17" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="5" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
       <c r="D17" s="5">
         <v>2011</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>37</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
@@ -2126,45 +2020,43 @@
       <c r="O17" s="5"/>
       <c r="P17" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen II Hidrología - Gestión de recursos hídricos y aplicación de prácticas hidrológicas. Sexta Edición, 2011 |</v>
+        <v>| [OMM-N°0168](https://library.wmo.int/doc_num.php?explnum_id=10038) | Guía de prácticas hidrológicas. Volumen II Hidrología - Gestión de recursos hídricos y aplicación de prácticas hidrológicas. Sexta Edición, 2011 |</v>
       </c>
       <c r="Q17" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen II Hidrología - Gestión de recursos hídricos y aplicación de prácticas hidrológicas. Sexta Edición, 2011 | 2011 |</v>
+        <v>| [OMM-N°0168](https://library.wmo.int/doc_num.php?explnum_id=10038) | Guía de prácticas hidrológicas. Volumen II Hidrología - Gestión de recursos hídricos y aplicación de prácticas hidrológicas. Sexta Edición, 2011 | 2011 |</v>
       </c>
       <c r="R17" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen II Hidrología - Gestión de recursos hídricos y aplicación de prácticas hidrológicas. Sexta Edición, 2011 | 2011 | https://library.wmo.int/doc_num.php?explnum_id=10038 |</v>
+        <v>| [OMM-N°0168](https://library.wmo.int/doc_num.php?explnum_id=10038) | Guía de prácticas hidrológicas. Volumen II Hidrología - Gestión de recursos hídricos y aplicación de prácticas hidrológicas. Sexta Edición, 2011 | 2011 | [:bookmark_tabs:](WMO.0168.GuiaPracticaHidrologicaVol2Hidrologia.2011.pdf) |</v>
       </c>
       <c r="S17" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen II Hidrología - Gestión de recursos hídricos y aplicación de prácticas hidrológicas. Sexta Edición, 2011 | 2011 | https://library.wmo.int/doc_num.php?explnum_id=10038 |WMO.0168.GuiaPracticaHidrologicaVol2Hidrologia.2011.pdf |</v>
+        <v>| [OMM-N°0168](https://library.wmo.int/doc_num.php?explnum_id=10038) | Guía de prácticas hidrológicas. Volumen II Hidrología - Gestión de recursos hídricos y aplicación de prácticas hidrológicas. Sexta Edición, 2011 | 2011 | [:bookmark_tabs:](WMO.0168.GuiaPracticaHidrologicaVol2Hidrologia.2011.pdf) | |</v>
       </c>
       <c r="T17" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen II Hidrología - Gestión de recursos hídricos y aplicación de prácticas hidrológicas. Sexta Edición, 2011 | 2011 | https://library.wmo.int/doc_num.php?explnum_id=10038 |WMO.0168.GuiaPracticaHidrologicaVol2Hidrologia.2011.pdf | | | | | |</v>
+        <v>| [OMM-N°0168](https://library.wmo.int/doc_num.php?explnum_id=10038) | Guía de prácticas hidrológicas. Volumen II Hidrología - Gestión de recursos hídricos y aplicación de prácticas hidrológicas. Sexta Edición, 2011 | 2011 | [:bookmark_tabs:](WMO.0168.GuiaPracticaHidrologicaVol2Hidrologia.2011.pdf) | | | | | | |</v>
       </c>
       <c r="U17" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| OMM-N°0168 | Guía de prácticas hidrológicas. Volumen II Hidrología - Gestión de recursos hídricos y aplicación de prácticas hidrológicas. Sexta Edición, 2011 | 2011 | https://library.wmo.int/doc_num.php?explnum_id=10038 |WMO.0168.GuiaPracticaHidrologicaVol2Hidrologia.2011.pdf | | | | | | | | |</v>
+        <v>| [OMM-N°0168](https://library.wmo.int/doc_num.php?explnum_id=10038) | Guía de prácticas hidrológicas. Volumen II Hidrología - Gestión de recursos hídricos y aplicación de prácticas hidrológicas. Sexta Edición, 2011 | 2011 | [:bookmark_tabs:](WMO.0168.GuiaPracticaHidrologicaVol2Hidrologia.2011.pdf) | | | | | | | | | |</v>
       </c>
     </row>
     <row r="18" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="5" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="D18" s="5">
         <v>1992</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>41</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -2176,45 +2068,43 @@
       <c r="O18" s="5"/>
       <c r="P18" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| OMM-N°0182 | Vocabulario Meteorológico Internacional |</v>
+        <v>| [OMM-N°0182](https://library.wmo.int/doc_num.php?explnum_id=4712) | Vocabulario Meteorológico Internacional |</v>
       </c>
       <c r="Q18" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| OMM-N°0182 | Vocabulario Meteorológico Internacional | 1992 |</v>
+        <v>| [OMM-N°0182](https://library.wmo.int/doc_num.php?explnum_id=4712) | Vocabulario Meteorológico Internacional | 1992 |</v>
       </c>
       <c r="R18" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| OMM-N°0182 | Vocabulario Meteorológico Internacional | 1992 | https://library.wmo.int/doc_num.php?explnum_id=4712 |</v>
+        <v>| [OMM-N°0182](https://library.wmo.int/doc_num.php?explnum_id=4712) | Vocabulario Meteorológico Internacional | 1992 | [:bookmark_tabs:](WMO.0182.VocabularioMeteorologicoInternacional.1992.pdf) |</v>
       </c>
       <c r="S18" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| OMM-N°0182 | Vocabulario Meteorológico Internacional | 1992 | https://library.wmo.int/doc_num.php?explnum_id=4712 |WMO.0182.VocabularioMeteorologicoInternacional.1992.pdf |</v>
+        <v>| [OMM-N°0182](https://library.wmo.int/doc_num.php?explnum_id=4712) | Vocabulario Meteorológico Internacional | 1992 | [:bookmark_tabs:](WMO.0182.VocabularioMeteorologicoInternacional.1992.pdf) | |</v>
       </c>
       <c r="T18" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| OMM-N°0182 | Vocabulario Meteorológico Internacional | 1992 | https://library.wmo.int/doc_num.php?explnum_id=4712 |WMO.0182.VocabularioMeteorologicoInternacional.1992.pdf | | | | | |</v>
+        <v>| [OMM-N°0182](https://library.wmo.int/doc_num.php?explnum_id=4712) | Vocabulario Meteorológico Internacional | 1992 | [:bookmark_tabs:](WMO.0182.VocabularioMeteorologicoInternacional.1992.pdf) | | | | | | |</v>
       </c>
       <c r="U18" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| OMM-N°0182 | Vocabulario Meteorológico Internacional | 1992 | https://library.wmo.int/doc_num.php?explnum_id=4712 |WMO.0182.VocabularioMeteorologicoInternacional.1992.pdf | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="19" spans="2:21" ht="61.5" x14ac:dyDescent="0.55000000000000004">
+        <v>| [OMM-N°0182](https://library.wmo.int/doc_num.php?explnum_id=4712) | Vocabulario Meteorológico Internacional | 1992 | [:bookmark_tabs:](WMO.0182.VocabularioMeteorologicoInternacional.1992.pdf) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="19" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="5" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="D19" s="5">
         <v>2020</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>45</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -2226,45 +2116,43 @@
       <c r="O19" s="5"/>
       <c r="P19" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| OMM-N°0386 | Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM |</v>
+        <v>| [OMM-N°0386](https://library.wmo.int/doc_num.php?explnum_id=10470) | Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM |</v>
       </c>
       <c r="Q19" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| OMM-N°0386 | Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM | 2020 |</v>
+        <v>| [OMM-N°0386](https://library.wmo.int/doc_num.php?explnum_id=10470) | Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM | 2020 |</v>
       </c>
       <c r="R19" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| OMM-N°0386 | Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM | 2020 | https://library.wmo.int/doc_num.php?explnum_id=10470 |</v>
+        <v>| [OMM-N°0386](https://library.wmo.int/doc_num.php?explnum_id=10470) | Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM | 2020 | [:bookmark_tabs:](WMO.0386.ManualSistemaMundialTelecomunicacion.2020.pdf) |</v>
       </c>
       <c r="S19" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| OMM-N°0386 | Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM | 2020 | https://library.wmo.int/doc_num.php?explnum_id=10470 |WMO.0386.ManualSistemaMundialTelecomunicacion.2020.pdf |</v>
+        <v>| [OMM-N°0386](https://library.wmo.int/doc_num.php?explnum_id=10470) | Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM | 2020 | [:bookmark_tabs:](WMO.0386.ManualSistemaMundialTelecomunicacion.2020.pdf) | |</v>
       </c>
       <c r="T19" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| OMM-N°0386 | Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM | 2020 | https://library.wmo.int/doc_num.php?explnum_id=10470 |WMO.0386.ManualSistemaMundialTelecomunicacion.2020.pdf | | | | | |</v>
+        <v>| [OMM-N°0386](https://library.wmo.int/doc_num.php?explnum_id=10470) | Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM | 2020 | [:bookmark_tabs:](WMO.0386.ManualSistemaMundialTelecomunicacion.2020.pdf) | | | | | | |</v>
       </c>
       <c r="U19" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| OMM-N°0386 | Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM | 2020 | https://library.wmo.int/doc_num.php?explnum_id=10470 |WMO.0386.ManualSistemaMundialTelecomunicacion.2020.pdf | | | | | | | | |</v>
+        <v>| [OMM-N°0386](https://library.wmo.int/doc_num.php?explnum_id=10470) | Manual del Sistema Mundial de Telecomunicación. Anexo III al Reglamento Técnico de la OMM | 2020 | [:bookmark_tabs:](WMO.0386.ManualSistemaMundialTelecomunicacion.2020.pdf) | | | | | | | | | |</v>
       </c>
     </row>
     <row r="20" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="5" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="D20" s="5">
         <v>2017</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>48</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
@@ -2276,45 +2164,43 @@
       <c r="O20" s="5"/>
       <c r="P20" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| OMM-N°0488 | Guía del Sistema Mundial de Observación. Edición 2010. Actualización 2017 |</v>
+        <v>| [OMM-N°0488](https://library.wmo.int/doc_num.php?explnum_id=5440) | Guía del Sistema Mundial de Observación. Edición 2010. Actualización 2017 |</v>
       </c>
       <c r="Q20" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| OMM-N°0488 | Guía del Sistema Mundial de Observación. Edición 2010. Actualización 2017 | 2017 |</v>
+        <v>| [OMM-N°0488](https://library.wmo.int/doc_num.php?explnum_id=5440) | Guía del Sistema Mundial de Observación. Edición 2010. Actualización 2017 | 2017 |</v>
       </c>
       <c r="R20" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| OMM-N°0488 | Guía del Sistema Mundial de Observación. Edición 2010. Actualización 2017 | 2017 | https://library.wmo.int/doc_num.php?explnum_id=5440 |</v>
+        <v>| [OMM-N°0488](https://library.wmo.int/doc_num.php?explnum_id=5440) | Guía del Sistema Mundial de Observación. Edición 2010. Actualización 2017 | 2017 | [:bookmark_tabs:](WMO.0488.GuiaSistemaMundialObservacion.2017.pdf) |</v>
       </c>
       <c r="S20" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| OMM-N°0488 | Guía del Sistema Mundial de Observación. Edición 2010. Actualización 2017 | 2017 | https://library.wmo.int/doc_num.php?explnum_id=5440 |WMO.0488.GuiaSistemaMundialObservacion.2017.pdf |</v>
+        <v>| [OMM-N°0488](https://library.wmo.int/doc_num.php?explnum_id=5440) | Guía del Sistema Mundial de Observación. Edición 2010. Actualización 2017 | 2017 | [:bookmark_tabs:](WMO.0488.GuiaSistemaMundialObservacion.2017.pdf) | |</v>
       </c>
       <c r="T20" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| OMM-N°0488 | Guía del Sistema Mundial de Observación. Edición 2010. Actualización 2017 | 2017 | https://library.wmo.int/doc_num.php?explnum_id=5440 |WMO.0488.GuiaSistemaMundialObservacion.2017.pdf | | | | | |</v>
+        <v>| [OMM-N°0488](https://library.wmo.int/doc_num.php?explnum_id=5440) | Guía del Sistema Mundial de Observación. Edición 2010. Actualización 2017 | 2017 | [:bookmark_tabs:](WMO.0488.GuiaSistemaMundialObservacion.2017.pdf) | | | | | | |</v>
       </c>
       <c r="U20" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| OMM-N°0488 | Guía del Sistema Mundial de Observación. Edición 2010. Actualización 2017 | 2017 | https://library.wmo.int/doc_num.php?explnum_id=5440 |WMO.0488.GuiaSistemaMundialObservacion.2017.pdf | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="21" spans="2:21" ht="61.5" x14ac:dyDescent="0.55000000000000004">
+        <v>| [OMM-N°0488](https://library.wmo.int/doc_num.php?explnum_id=5440) | Guía del Sistema Mundial de Observación. Edición 2010. Actualización 2017 | 2017 | [:bookmark_tabs:](WMO.0488.GuiaSistemaMundialObservacion.2017.pdf) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="5" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="D21" s="5">
         <v>2017</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
@@ -2326,45 +2212,43 @@
       <c r="O21" s="5"/>
       <c r="P21" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| OMM-N°0544 | Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico |</v>
+        <v>| [OMM-N°0544](https://wmo.int/wmo-no-544-manual-global-observing-system) | Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico |</v>
       </c>
       <c r="Q21" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| OMM-N°0544 | Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico | 2017 |</v>
+        <v>| [OMM-N°0544](https://wmo.int/wmo-no-544-manual-global-observing-system) | Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico | 2017 |</v>
       </c>
       <c r="R21" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| OMM-N°0544 | Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico | 2017 | https://wmo.int/wmo-no-544-manual-global-observing-system |</v>
+        <v>| [OMM-N°0544](https://wmo.int/wmo-no-544-manual-global-observing-system) | Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico | 2017 | [:bookmark_tabs:](WMO.0544.ManualSistemaMundialObservacionVolumen1.2017.pdf) |</v>
       </c>
       <c r="S21" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| OMM-N°0544 | Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico | 2017 | https://wmo.int/wmo-no-544-manual-global-observing-system |WMO.0544.ManualSistemaMundialObservacionVolumen1.2017.pdf |</v>
+        <v>| [OMM-N°0544](https://wmo.int/wmo-no-544-manual-global-observing-system) | Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico | 2017 | [:bookmark_tabs:](WMO.0544.ManualSistemaMundialObservacionVolumen1.2017.pdf) | |</v>
       </c>
       <c r="T21" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| OMM-N°0544 | Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico | 2017 | https://wmo.int/wmo-no-544-manual-global-observing-system |WMO.0544.ManualSistemaMundialObservacionVolumen1.2017.pdf | | | | | |</v>
+        <v>| [OMM-N°0544](https://wmo.int/wmo-no-544-manual-global-observing-system) | Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico | 2017 | [:bookmark_tabs:](WMO.0544.ManualSistemaMundialObservacionVolumen1.2017.pdf) | | | | | | |</v>
       </c>
       <c r="U21" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| OMM-N°0544 | Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico | 2017 | https://wmo.int/wmo-no-544-manual-global-observing-system |WMO.0544.ManualSistemaMundialObservacionVolumen1.2017.pdf | | | | | | | | |</v>
+        <v>| [OMM-N°0544](https://wmo.int/wmo-no-544-manual-global-observing-system) | Manual del Sistema Mundial de Observación. Volumen I – Aspectos mundiales. Anexo V del Reglamento Técnico | 2017 | [:bookmark_tabs:](WMO.0544.ManualSistemaMundialObservacionVolumen1.2017.pdf) | | | | | | | | | |</v>
       </c>
     </row>
     <row r="22" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="5" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="D22" s="5">
         <v>2018</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>55</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -2376,45 +2260,43 @@
       <c r="O22" s="5"/>
       <c r="P22" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| OMM-N°1061 | Guía del Sistema de Información de la OMM |</v>
+        <v>| [OMM-N°1061](https://library.wmo.int/doc_num.php?explnum_id=10258) | Guía del Sistema de Información de la OMM |</v>
       </c>
       <c r="Q22" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| OMM-N°1061 | Guía del Sistema de Información de la OMM | 2018 |</v>
+        <v>| [OMM-N°1061](https://library.wmo.int/doc_num.php?explnum_id=10258) | Guía del Sistema de Información de la OMM | 2018 |</v>
       </c>
       <c r="R22" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| OMM-N°1061 | Guía del Sistema de Información de la OMM | 2018 | https://library.wmo.int/doc_num.php?explnum_id=10258 |</v>
+        <v>| [OMM-N°1061](https://library.wmo.int/doc_num.php?explnum_id=10258) | Guía del Sistema de Información de la OMM | 2018 | [:bookmark_tabs:](WMO.1061.GuiaSistemaInformacionOMM.2018.pdf) |</v>
       </c>
       <c r="S22" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| OMM-N°1061 | Guía del Sistema de Información de la OMM | 2018 | https://library.wmo.int/doc_num.php?explnum_id=10258 |WMO.1061.GuiaSistemaInformacionOMM.2018.pdf |</v>
+        <v>| [OMM-N°1061](https://library.wmo.int/doc_num.php?explnum_id=10258) | Guía del Sistema de Información de la OMM | 2018 | [:bookmark_tabs:](WMO.1061.GuiaSistemaInformacionOMM.2018.pdf) | |</v>
       </c>
       <c r="T22" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| OMM-N°1061 | Guía del Sistema de Información de la OMM | 2018 | https://library.wmo.int/doc_num.php?explnum_id=10258 |WMO.1061.GuiaSistemaInformacionOMM.2018.pdf | | | | | |</v>
+        <v>| [OMM-N°1061](https://library.wmo.int/doc_num.php?explnum_id=10258) | Guía del Sistema de Información de la OMM | 2018 | [:bookmark_tabs:](WMO.1061.GuiaSistemaInformacionOMM.2018.pdf) | | | | | | |</v>
       </c>
       <c r="U22" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| OMM-N°1061 | Guía del Sistema de Información de la OMM | 2018 | https://library.wmo.int/doc_num.php?explnum_id=10258 |WMO.1061.GuiaSistemaInformacionOMM.2018.pdf | | | | | | | | |</v>
+        <v>| [OMM-N°1061](https://library.wmo.int/doc_num.php?explnum_id=10258) | Guía del Sistema de Información de la OMM | 2018 | [:bookmark_tabs:](WMO.1061.GuiaSistemaInformacionOMM.2018.pdf) | | | | | | | | | |</v>
       </c>
     </row>
     <row r="23" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="5" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="D23" s="5">
         <v>2012</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>59</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
@@ -2426,45 +2308,43 @@
       <c r="O23" s="5"/>
       <c r="P23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| OMM-N°1091 | Directrices sobre los sistemas de predicción por conjuntos y la predicción |</v>
+        <v>| [OMM-N°1091](https://library.wmo.int/doc_num.php?explnum_id=7774) | Directrices sobre los sistemas de predicción por conjuntos y la predicción |</v>
       </c>
       <c r="Q23" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| OMM-N°1091 | Directrices sobre los sistemas de predicción por conjuntos y la predicción | 2012 |</v>
+        <v>| [OMM-N°1091](https://library.wmo.int/doc_num.php?explnum_id=7774) | Directrices sobre los sistemas de predicción por conjuntos y la predicción | 2012 |</v>
       </c>
       <c r="R23" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| OMM-N°1091 | Directrices sobre los sistemas de predicción por conjuntos y la predicción | 2012 | https://library.wmo.int/doc_num.php?explnum_id=7774 |</v>
+        <v>| [OMM-N°1091](https://library.wmo.int/doc_num.php?explnum_id=7774) | Directrices sobre los sistemas de predicción por conjuntos y la predicción | 2012 | [:bookmark_tabs:](WMO.1091.DirectricesSistemasPrediccionConjuntos.2012.pdf) |</v>
       </c>
       <c r="S23" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| OMM-N°1091 | Directrices sobre los sistemas de predicción por conjuntos y la predicción | 2012 | https://library.wmo.int/doc_num.php?explnum_id=7774 |WMO.1091.DirectricesSistemasPrediccionConjuntos.2012.pdf |</v>
+        <v>| [OMM-N°1091](https://library.wmo.int/doc_num.php?explnum_id=7774) | Directrices sobre los sistemas de predicción por conjuntos y la predicción | 2012 | [:bookmark_tabs:](WMO.1091.DirectricesSistemasPrediccionConjuntos.2012.pdf) | |</v>
       </c>
       <c r="T23" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| OMM-N°1091 | Directrices sobre los sistemas de predicción por conjuntos y la predicción | 2012 | https://library.wmo.int/doc_num.php?explnum_id=7774 |WMO.1091.DirectricesSistemasPrediccionConjuntos.2012.pdf | | | | | |</v>
+        <v>| [OMM-N°1091](https://library.wmo.int/doc_num.php?explnum_id=7774) | Directrices sobre los sistemas de predicción por conjuntos y la predicción | 2012 | [:bookmark_tabs:](WMO.1091.DirectricesSistemasPrediccionConjuntos.2012.pdf) | | | | | | |</v>
       </c>
       <c r="U23" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| OMM-N°1091 | Directrices sobre los sistemas de predicción por conjuntos y la predicción | 2012 | https://library.wmo.int/doc_num.php?explnum_id=7774 |WMO.1091.DirectricesSistemasPrediccionConjuntos.2012.pdf | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="24" spans="2:21" ht="76.900000000000006" x14ac:dyDescent="0.55000000000000004">
+        <v>| [OMM-N°1091](https://library.wmo.int/doc_num.php?explnum_id=7774) | Directrices sobre los sistemas de predicción por conjuntos y la predicción | 2012 | [:bookmark_tabs:](WMO.1091.DirectricesSistemasPrediccionConjuntos.2012.pdf) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="5" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="D24" s="5">
         <v>2017</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>62</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
@@ -2476,45 +2356,43 @@
       <c r="O24" s="5"/>
       <c r="P24" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| OMM-N°1100 | Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes |</v>
+        <v>| [OMM-N°1100](https://library.wmo.int/doc_num.php?explnum_id=5742) | Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes |</v>
       </c>
       <c r="Q24" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| OMM-N°1100 | Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes | 2017 |</v>
+        <v>| [OMM-N°1100](https://library.wmo.int/doc_num.php?explnum_id=5742) | Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes | 2017 |</v>
       </c>
       <c r="R24" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| OMM-N°1100 | Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes | 2017 | https://library.wmo.int/doc_num.php?explnum_id=5742 |</v>
+        <v>| [OMM-N°1100](https://library.wmo.int/doc_num.php?explnum_id=5742) | Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes | 2017 | [:bookmark_tabs:](WMO.1100.GuiaAplicacionSistemasGestionCalidadServicioMeteorologicoHidrologico.2017.pdf) |</v>
       </c>
       <c r="S24" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| OMM-N°1100 | Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes | 2017 | https://library.wmo.int/doc_num.php?explnum_id=5742 |WMO.1100.GuiaAplicacionSistemasGestionCalidadServicioMeteorologicoHidrologico.2017.pdf |</v>
+        <v>| [OMM-N°1100](https://library.wmo.int/doc_num.php?explnum_id=5742) | Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes | 2017 | [:bookmark_tabs:](WMO.1100.GuiaAplicacionSistemasGestionCalidadServicioMeteorologicoHidrologico.2017.pdf) | |</v>
       </c>
       <c r="T24" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| OMM-N°1100 | Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes | 2017 | https://library.wmo.int/doc_num.php?explnum_id=5742 |WMO.1100.GuiaAplicacionSistemasGestionCalidadServicioMeteorologicoHidrologico.2017.pdf | | | | | |</v>
+        <v>| [OMM-N°1100](https://library.wmo.int/doc_num.php?explnum_id=5742) | Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes | 2017 | [:bookmark_tabs:](WMO.1100.GuiaAplicacionSistemasGestionCalidadServicioMeteorologicoHidrologico.2017.pdf) | | | | | | |</v>
       </c>
       <c r="U24" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| OMM-N°1100 | Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes | 2017 | https://library.wmo.int/doc_num.php?explnum_id=5742 |WMO.1100.GuiaAplicacionSistemasGestionCalidadServicioMeteorologicoHidrologico.2017.pdf | | | | | | | | |</v>
+        <v>| [OMM-N°1100](https://library.wmo.int/doc_num.php?explnum_id=5742) | Guía para la aplicación de sistemas de gestión de la calidad para los Servicios Meteorológicos e Hidrológicos Nacionales y otros proveedores de servicios pertinentes | 2017 | [:bookmark_tabs:](WMO.1100.GuiaAplicacionSistemasGestionCalidadServicioMeteorologicoHidrologico.2017.pdf) | | | | | | | | | |</v>
       </c>
     </row>
     <row r="25" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="5" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="D25" s="5">
         <v>2019</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>66</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
@@ -2526,45 +2404,43 @@
       <c r="O25" s="4"/>
       <c r="P25" s="5" t="str">
         <f t="shared" ref="P25:P88" si="6">_xlfn.CONCAT("| ",B25," | ",C25," |")</f>
-        <v>| OMM-N°1160 | Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM |</v>
+        <v>| [OMM-N°1160](https://library.wmo.int/doc_num.php?explnum_id=10230) | Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM |</v>
       </c>
       <c r="Q25" s="5" t="str">
         <f t="shared" ref="Q25:Q88" si="7">_xlfn.CONCAT("| ",B25," | ",C25," | ",D25," |")</f>
-        <v>| OMM-N°1160 | Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 |</v>
+        <v>| [OMM-N°1160](https://library.wmo.int/doc_num.php?explnum_id=10230) | Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 |</v>
       </c>
       <c r="R25" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| OMM-N°1160 | Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10230 |</v>
+        <v>| [OMM-N°1160](https://library.wmo.int/doc_num.php?explnum_id=10230) | Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | [:bookmark_tabs:](WMO.1160.ManualSistemaIntegradoObservacionOMM.2019.pdf) |</v>
       </c>
       <c r="S25" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| OMM-N°1160 | Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10230 |WMO.1160.ManualSistemaIntegradoObservacionOMM.2019.pdf |</v>
+        <v>| [OMM-N°1160](https://library.wmo.int/doc_num.php?explnum_id=10230) | Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | [:bookmark_tabs:](WMO.1160.ManualSistemaIntegradoObservacionOMM.2019.pdf) | |</v>
       </c>
       <c r="T25" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| OMM-N°1160 | Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10230 |WMO.1160.ManualSistemaIntegradoObservacionOMM.2019.pdf | | | | | |</v>
+        <v>| [OMM-N°1160](https://library.wmo.int/doc_num.php?explnum_id=10230) | Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | [:bookmark_tabs:](WMO.1160.ManualSistemaIntegradoObservacionOMM.2019.pdf) | | | | | | |</v>
       </c>
       <c r="U25" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| OMM-N°1160 | Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10230 |WMO.1160.ManualSistemaIntegradoObservacionOMM.2019.pdf | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="26" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+        <v>| [OMM-N°1160](https://library.wmo.int/doc_num.php?explnum_id=10230) | Manual del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | [:bookmark_tabs:](WMO.1160.ManualSistemaIntegradoObservacionOMM.2019.pdf) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="26" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="4" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="D26" s="4">
         <v>2019</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>70</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
@@ -2576,45 +2452,43 @@
       <c r="O26" s="4"/>
       <c r="P26" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| OMM-N°1165 | Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM |</v>
+        <v>| [OMM-N°1165](https://library.wmo.int/doc_num.php?explnum_id=10042) | Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM |</v>
       </c>
       <c r="Q26" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| OMM-N°1165 | Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 |</v>
+        <v>| [OMM-N°1165](https://library.wmo.int/doc_num.php?explnum_id=10042) | Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 |</v>
       </c>
       <c r="R26" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| OMM-N°1165 | Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10042 |</v>
+        <v>| [OMM-N°1165](https://library.wmo.int/doc_num.php?explnum_id=10042) | Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | [:bookmark_tabs:](WMO.1165.GuiaSistemaMundialIntegradoSistemaObservacionOMM.2019.pdf) |</v>
       </c>
       <c r="S26" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| OMM-N°1165 | Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10042 |WMO.1165.GuiaSistemaMundialIntegradoSistemaObservacionOMM.2019.pdf |</v>
+        <v>| [OMM-N°1165](https://library.wmo.int/doc_num.php?explnum_id=10042) | Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | [:bookmark_tabs:](WMO.1165.GuiaSistemaMundialIntegradoSistemaObservacionOMM.2019.pdf) | |</v>
       </c>
       <c r="T26" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| OMM-N°1165 | Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10042 |WMO.1165.GuiaSistemaMundialIntegradoSistemaObservacionOMM.2019.pdf | | | | | |</v>
+        <v>| [OMM-N°1165](https://library.wmo.int/doc_num.php?explnum_id=10042) | Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | [:bookmark_tabs:](WMO.1165.GuiaSistemaMundialIntegradoSistemaObservacionOMM.2019.pdf) | | | | | | |</v>
       </c>
       <c r="U26" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| OMM-N°1165 | Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10042 |WMO.1165.GuiaSistemaMundialIntegradoSistemaObservacionOMM.2019.pdf | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="27" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+        <v>| [OMM-N°1165](https://library.wmo.int/doc_num.php?explnum_id=10042) | Guía del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | [:bookmark_tabs:](WMO.1165.GuiaSistemaMundialIntegradoSistemaObservacionOMM.2019.pdf) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="27" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="4" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="D27" s="4">
         <v>2016</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>74</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
@@ -2626,45 +2500,43 @@
       <c r="O27" s="4"/>
       <c r="P27" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| OMM-N°1182 | Directrices sobre mejores prácticas para el rescate de datos climáticos |</v>
+        <v>| [OMM-N°1182](https://library.wmo.int/doc_num.php?explnum_id=3529) | Directrices sobre mejores prácticas para el rescate de datos climáticos |</v>
       </c>
       <c r="Q27" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| OMM-N°1182 | Directrices sobre mejores prácticas para el rescate de datos climáticos | 2016 |</v>
+        <v>| [OMM-N°1182](https://library.wmo.int/doc_num.php?explnum_id=3529) | Directrices sobre mejores prácticas para el rescate de datos climáticos | 2016 |</v>
       </c>
       <c r="R27" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| OMM-N°1182 | Directrices sobre mejores prácticas para el rescate de datos climáticos | 2016 | https://library.wmo.int/doc_num.php?explnum_id=3529 |</v>
+        <v>| [OMM-N°1182](https://library.wmo.int/doc_num.php?explnum_id=3529) | Directrices sobre mejores prácticas para el rescate de datos climáticos | 2016 | [:bookmark_tabs:](WMO.1182.DirectrizRescateDatoClimatico.2016.pdf) |</v>
       </c>
       <c r="S27" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| OMM-N°1182 | Directrices sobre mejores prácticas para el rescate de datos climáticos | 2016 | https://library.wmo.int/doc_num.php?explnum_id=3529 |WMO.1182.DirectrizRescateDatoClimatico.2016.pdf |</v>
+        <v>| [OMM-N°1182](https://library.wmo.int/doc_num.php?explnum_id=3529) | Directrices sobre mejores prácticas para el rescate de datos climáticos | 2016 | [:bookmark_tabs:](WMO.1182.DirectrizRescateDatoClimatico.2016.pdf) | |</v>
       </c>
       <c r="T27" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| OMM-N°1182 | Directrices sobre mejores prácticas para el rescate de datos climáticos | 2016 | https://library.wmo.int/doc_num.php?explnum_id=3529 |WMO.1182.DirectrizRescateDatoClimatico.2016.pdf | | | | | |</v>
+        <v>| [OMM-N°1182](https://library.wmo.int/doc_num.php?explnum_id=3529) | Directrices sobre mejores prácticas para el rescate de datos climáticos | 2016 | [:bookmark_tabs:](WMO.1182.DirectrizRescateDatoClimatico.2016.pdf) | | | | | | |</v>
       </c>
       <c r="U27" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| OMM-N°1182 | Directrices sobre mejores prácticas para el rescate de datos climáticos | 2016 | https://library.wmo.int/doc_num.php?explnum_id=3529 |WMO.1182.DirectrizRescateDatoClimatico.2016.pdf | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="28" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+        <v>| [OMM-N°1182](https://library.wmo.int/doc_num.php?explnum_id=3529) | Directrices sobre mejores prácticas para el rescate de datos climáticos | 2016 | [:bookmark_tabs:](WMO.1182.DirectrizRescateDatoClimatico.2016.pdf) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="28" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="4" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="D28" s="4">
         <v>2019</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>78</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
@@ -2676,45 +2548,43 @@
       <c r="O28" s="4"/>
       <c r="P28" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| OMM-N°1192 | Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM |</v>
+        <v>| [OMM-N°1192](https://library.wmo.int/doc_num.php?explnum_id=10163) | Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM |</v>
       </c>
       <c r="Q28" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| OMM-N°1192 | Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 |</v>
+        <v>| [OMM-N°1192](https://library.wmo.int/doc_num.php?explnum_id=10163) | Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 |</v>
       </c>
       <c r="R28" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| OMM-N°1192 | Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10163 |</v>
+        <v>| [OMM-N°1192](https://library.wmo.int/doc_num.php?explnum_id=10163) | Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | [:bookmark_tabs:](WMO.1192.NormaMetadatoSistemaMundialIntegradoObservacion.2019) |</v>
       </c>
       <c r="S28" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| OMM-N°1192 | Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10163 |WMO.1192.NormaMetadatoSistemaMundialIntegradoObservacion.2019 |</v>
+        <v>| [OMM-N°1192](https://library.wmo.int/doc_num.php?explnum_id=10163) | Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | [:bookmark_tabs:](WMO.1192.NormaMetadatoSistemaMundialIntegradoObservacion.2019) | |</v>
       </c>
       <c r="T28" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| OMM-N°1192 | Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10163 |WMO.1192.NormaMetadatoSistemaMundialIntegradoObservacion.2019 | | | | | |</v>
+        <v>| [OMM-N°1192](https://library.wmo.int/doc_num.php?explnum_id=10163) | Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | [:bookmark_tabs:](WMO.1192.NormaMetadatoSistemaMundialIntegradoObservacion.2019) | | | | | | |</v>
       </c>
       <c r="U28" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| OMM-N°1192 | Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10163 |WMO.1192.NormaMetadatoSistemaMundialIntegradoObservacion.2019 | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="29" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+        <v>| [OMM-N°1192](https://library.wmo.int/doc_num.php?explnum_id=10163) | Norma sobre metadatos del Sistema Mundial Integrado de Sistemas de Observación de la OMM | 2019 | [:bookmark_tabs:](WMO.1192.NormaMetadatoSistemaMundialIntegradoObservacion.2019) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="29" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="4" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="D29" s="4">
         <v>2017</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>82</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
@@ -2726,45 +2596,43 @@
       <c r="O29" s="4"/>
       <c r="P29" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| OMM-N°1203 | Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas |</v>
+        <v>| [OMM-N°1203](https://library.wmo.int/doc_num.php?explnum_id=4167) | Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas |</v>
       </c>
       <c r="Q29" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| OMM-N°1203 | Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas | 2017 |</v>
+        <v>| [OMM-N°1203](https://library.wmo.int/doc_num.php?explnum_id=4167) | Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas | 2017 |</v>
       </c>
       <c r="R29" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| OMM-N°1203 | Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas | 2017 | https://library.wmo.int/doc_num.php?explnum_id=4167 |</v>
+        <v>| [OMM-N°1203](https://library.wmo.int/doc_num.php?explnum_id=4167) | Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas | 2017 | [:bookmark_tabs:](WMO.01203.DirectricezCalculoNormalClimatica.2017.pdf) |</v>
       </c>
       <c r="S29" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| OMM-N°1203 | Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas | 2017 | https://library.wmo.int/doc_num.php?explnum_id=4167 |WMO.01203.DirectricezCalculoNormalClimatica.2017.pdf |</v>
+        <v>| [OMM-N°1203](https://library.wmo.int/doc_num.php?explnum_id=4167) | Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas | 2017 | [:bookmark_tabs:](WMO.01203.DirectricezCalculoNormalClimatica.2017.pdf) | |</v>
       </c>
       <c r="T29" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| OMM-N°1203 | Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas | 2017 | https://library.wmo.int/doc_num.php?explnum_id=4167 |WMO.01203.DirectricezCalculoNormalClimatica.2017.pdf | | | | | |</v>
+        <v>| [OMM-N°1203](https://library.wmo.int/doc_num.php?explnum_id=4167) | Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas | 2017 | [:bookmark_tabs:](WMO.01203.DirectricezCalculoNormalClimatica.2017.pdf) | | | | | | |</v>
       </c>
       <c r="U29" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| OMM-N°1203 | Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas | 2017 | https://library.wmo.int/doc_num.php?explnum_id=4167 |WMO.01203.DirectricezCalculoNormalClimatica.2017.pdf | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="30" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+        <v>| [OMM-N°1203](https://library.wmo.int/doc_num.php?explnum_id=4167) | Directrices de la Organización Meteorológica Mundial sobre el cálculo de las normales climáticas | 2017 | [:bookmark_tabs:](WMO.01203.DirectricezCalculoNormalClimatica.2017.pdf) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="30" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="D30" s="4">
         <v>1966</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>86</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
@@ -2776,45 +2644,43 @@
       <c r="O30" s="4"/>
       <c r="P30" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| WMO-N°0199 | Some Methods of Climatological Analysis |</v>
+        <v>| [WMO-N°0199](https://library.wmo.int/doc_num.php?explnum_id=1961) | Some Methods of Climatological Analysis |</v>
       </c>
       <c r="Q30" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| WMO-N°0199 | Some Methods of Climatological Analysis | 1966 |</v>
+        <v>| [WMO-N°0199](https://library.wmo.int/doc_num.php?explnum_id=1961) | Some Methods of Climatological Analysis | 1966 |</v>
       </c>
       <c r="R30" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| WMO-N°0199 | Some Methods of Climatological Analysis | 1966 | https://library.wmo.int/doc_num.php?explnum_id=1961 |</v>
+        <v>| [WMO-N°0199](https://library.wmo.int/doc_num.php?explnum_id=1961) | Some Methods of Climatological Analysis | 1966 | [:bookmark_tabs:](WMO.0199.SomeMethodsClimatologicalAnalysis.1966.pdf) |</v>
       </c>
       <c r="S30" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| WMO-N°0199 | Some Methods of Climatological Analysis | 1966 | https://library.wmo.int/doc_num.php?explnum_id=1961 |WMO.0199.SomeMethodsClimatologicalAnalysis.1966.pdf |</v>
+        <v>| [WMO-N°0199](https://library.wmo.int/doc_num.php?explnum_id=1961) | Some Methods of Climatological Analysis | 1966 | [:bookmark_tabs:](WMO.0199.SomeMethodsClimatologicalAnalysis.1966.pdf) | |</v>
       </c>
       <c r="T30" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| WMO-N°0199 | Some Methods of Climatological Analysis | 1966 | https://library.wmo.int/doc_num.php?explnum_id=1961 |WMO.0199.SomeMethodsClimatologicalAnalysis.1966.pdf | | | | | |</v>
+        <v>| [WMO-N°0199](https://library.wmo.int/doc_num.php?explnum_id=1961) | Some Methods of Climatological Analysis | 1966 | [:bookmark_tabs:](WMO.0199.SomeMethodsClimatologicalAnalysis.1966.pdf) | | | | | | |</v>
       </c>
       <c r="U30" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| WMO-N°0199 | Some Methods of Climatological Analysis | 1966 | https://library.wmo.int/doc_num.php?explnum_id=1961 |WMO.0199.SomeMethodsClimatologicalAnalysis.1966.pdf | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="31" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+        <v>| [WMO-N°0199](https://library.wmo.int/doc_num.php?explnum_id=1961) | Some Methods of Climatological Analysis | 1966 | [:bookmark_tabs:](WMO.0199.SomeMethodsClimatologicalAnalysis.1966.pdf) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="31" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="D31" s="4">
         <v>1990</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>90</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
@@ -2826,45 +2692,43 @@
       <c r="O31" s="4"/>
       <c r="P31" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| WMO-N°0415 | On The Statistical Analysis of Series of Observations |</v>
+        <v>| [WMO-N°0415](https://library.wmo.int/doc_num.php?explnum_id=1065) | On The Statistical Analysis of Series of Observations |</v>
       </c>
       <c r="Q31" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| WMO-N°0415 | On The Statistical Analysis of Series of Observations | 1990 |</v>
+        <v>| [WMO-N°0415](https://library.wmo.int/doc_num.php?explnum_id=1065) | On The Statistical Analysis of Series of Observations | 1990 |</v>
       </c>
       <c r="R31" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| WMO-N°0415 | On The Statistical Analysis of Series of Observations | 1990 | https://library.wmo.int/doc_num.php?explnum_id=1065 |</v>
+        <v>| [WMO-N°0415](https://library.wmo.int/doc_num.php?explnum_id=1065) | On The Statistical Analysis of Series of Observations | 1990 | [:bookmark_tabs:](WMO.0415.StatisticalAnalysisSerieObservation.1990.pdf) |</v>
       </c>
       <c r="S31" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| WMO-N°0415 | On The Statistical Analysis of Series of Observations | 1990 | https://library.wmo.int/doc_num.php?explnum_id=1065 |WMO.0415.StatisticalAnalysisSerieObservation.1990.pdf |</v>
+        <v>| [WMO-N°0415](https://library.wmo.int/doc_num.php?explnum_id=1065) | On The Statistical Analysis of Series of Observations | 1990 | [:bookmark_tabs:](WMO.0415.StatisticalAnalysisSerieObservation.1990.pdf) | |</v>
       </c>
       <c r="T31" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| WMO-N°0415 | On The Statistical Analysis of Series of Observations | 1990 | https://library.wmo.int/doc_num.php?explnum_id=1065 |WMO.0415.StatisticalAnalysisSerieObservation.1990.pdf | | | | | |</v>
+        <v>| [WMO-N°0415](https://library.wmo.int/doc_num.php?explnum_id=1065) | On The Statistical Analysis of Series of Observations | 1990 | [:bookmark_tabs:](WMO.0415.StatisticalAnalysisSerieObservation.1990.pdf) | | | | | | |</v>
       </c>
       <c r="U31" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| WMO-N°0415 | On The Statistical Analysis of Series of Observations | 1990 | https://library.wmo.int/doc_num.php?explnum_id=1065 |WMO.0415.StatisticalAnalysisSerieObservation.1990.pdf | | | | | | | | |</v>
+        <v>| [WMO-N°0415](https://library.wmo.int/doc_num.php?explnum_id=1065) | On The Statistical Analysis of Series of Observations | 1990 | [:bookmark_tabs:](WMO.0415.StatisticalAnalysisSerieObservation.1990.pdf) | | | | | | | | | |</v>
       </c>
     </row>
     <row r="32" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="D32" s="4">
         <v>2019</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F32" s="4" t="s">
         <v>94</v>
       </c>
+      <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -2876,27 +2740,27 @@
       <c r="O32" s="4"/>
       <c r="P32" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| WMO-N°0485 | Manual del Sistema Mundial de Proceso de Datos y de Predicción |</v>
+        <v>| [WMO-N°0485](https://library.wmo.int/doc_num.php?explnum_id=10281) | Manual del Sistema Mundial de Proceso de Datos y de Predicción |</v>
       </c>
       <c r="Q32" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| WMO-N°0485 | Manual del Sistema Mundial de Proceso de Datos y de Predicción | 2019 |</v>
+        <v>| [WMO-N°0485](https://library.wmo.int/doc_num.php?explnum_id=10281) | Manual del Sistema Mundial de Proceso de Datos y de Predicción | 2019 |</v>
       </c>
       <c r="R32" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| WMO-N°0485 | Manual del Sistema Mundial de Proceso de Datos y de Predicción | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10281 |</v>
+        <v>| [WMO-N°0485](https://library.wmo.int/doc_num.php?explnum_id=10281) | Manual del Sistema Mundial de Proceso de Datos y de Predicción | 2019 | [:bookmark_tabs:](WMO.0485.ManualSistemaMundialProcesoDatosPrediccion.2019.pdf) |</v>
       </c>
       <c r="S32" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| WMO-N°0485 | Manual del Sistema Mundial de Proceso de Datos y de Predicción | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10281 |WMO.0485.ManualSistemaMundialProcesoDatosPrediccion.2019.pdf |</v>
+        <v>| [WMO-N°0485](https://library.wmo.int/doc_num.php?explnum_id=10281) | Manual del Sistema Mundial de Proceso de Datos y de Predicción | 2019 | [:bookmark_tabs:](WMO.0485.ManualSistemaMundialProcesoDatosPrediccion.2019.pdf) | |</v>
       </c>
       <c r="T32" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| WMO-N°0485 | Manual del Sistema Mundial de Proceso de Datos y de Predicción | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10281 |WMO.0485.ManualSistemaMundialProcesoDatosPrediccion.2019.pdf | | | | | |</v>
+        <v>| [WMO-N°0485](https://library.wmo.int/doc_num.php?explnum_id=10281) | Manual del Sistema Mundial de Proceso de Datos y de Predicción | 2019 | [:bookmark_tabs:](WMO.0485.ManualSistemaMundialProcesoDatosPrediccion.2019.pdf) | | | | | | |</v>
       </c>
       <c r="U32" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| WMO-N°0485 | Manual del Sistema Mundial de Proceso de Datos y de Predicción | 2019 | https://library.wmo.int/doc_num.php?explnum_id=10281 |WMO.0485.ManualSistemaMundialProcesoDatosPrediccion.2019.pdf | | | | | | | | |</v>
+        <v>| [WMO-N°0485](https://library.wmo.int/doc_num.php?explnum_id=10281) | Manual del Sistema Mundial de Proceso de Datos y de Predicción | 2019 | [:bookmark_tabs:](WMO.0485.ManualSistemaMundialProcesoDatosPrediccion.2019.pdf) | | | | | | | | | |</v>
       </c>
     </row>
     <row r="33" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
@@ -2904,17 +2768,15 @@
         <v>95</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="D33" s="4">
         <v>2014</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>98</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
@@ -2926,45 +2788,43 @@
       <c r="O33" s="4"/>
       <c r="P33" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| WMO-N°1131 | Climate Data Management System Specifications |</v>
+        <v>| [WMO-N°1131](https://library.wmo.int/doc_num.php?explnum_id=7867) | Climate Data Management System Specifications |</v>
       </c>
       <c r="Q33" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| WMO-N°1131 | Climate Data Management System Specifications | 2014 |</v>
+        <v>| [WMO-N°1131](https://library.wmo.int/doc_num.php?explnum_id=7867) | Climate Data Management System Specifications | 2014 |</v>
       </c>
       <c r="R33" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| WMO-N°1131 | Climate Data Management System Specifications | 2014 | https://library.wmo.int/doc_num.php?explnum_id=7867 |</v>
+        <v>| [WMO-N°1131](https://library.wmo.int/doc_num.php?explnum_id=7867) | Climate Data Management System Specifications | 2014 | [:bookmark_tabs:](WMO.1131.ClimateDataManagementSystem.2014.pdf) |</v>
       </c>
       <c r="S33" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| WMO-N°1131 | Climate Data Management System Specifications | 2014 | https://library.wmo.int/doc_num.php?explnum_id=7867 |WMO.1131.ClimateDataManagementSystem.2014.pdf |</v>
+        <v>| [WMO-N°1131](https://library.wmo.int/doc_num.php?explnum_id=7867) | Climate Data Management System Specifications | 2014 | [:bookmark_tabs:](WMO.1131.ClimateDataManagementSystem.2014.pdf) | |</v>
       </c>
       <c r="T33" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| WMO-N°1131 | Climate Data Management System Specifications | 2014 | https://library.wmo.int/doc_num.php?explnum_id=7867 |WMO.1131.ClimateDataManagementSystem.2014.pdf | | | | | |</v>
+        <v>| [WMO-N°1131](https://library.wmo.int/doc_num.php?explnum_id=7867) | Climate Data Management System Specifications | 2014 | [:bookmark_tabs:](WMO.1131.ClimateDataManagementSystem.2014.pdf) | | | | | | |</v>
       </c>
       <c r="U33" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| WMO-N°1131 | Climate Data Management System Specifications | 2014 | https://library.wmo.int/doc_num.php?explnum_id=7867 |WMO.1131.ClimateDataManagementSystem.2014.pdf | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="34" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+        <v>| [WMO-N°1131](https://library.wmo.int/doc_num.php?explnum_id=7867) | Climate Data Management System Specifications | 2014 | [:bookmark_tabs:](WMO.1131.ClimateDataManagementSystem.2014.pdf) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="D34" s="4">
         <v>2016</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>102</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
@@ -2976,45 +2836,43 @@
       <c r="O34" s="4"/>
       <c r="P34" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| WMO-N°1170 | Climate Services for Supporting Climate Change Adaptation |</v>
+        <v>| [WMO-N°1170](https://library.wmo.int/doc_num.php?explnum_id=7936) | Climate Services for Supporting Climate Change Adaptation |</v>
       </c>
       <c r="Q34" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| WMO-N°1170 | Climate Services for Supporting Climate Change Adaptation | 2016 |</v>
+        <v>| [WMO-N°1170](https://library.wmo.int/doc_num.php?explnum_id=7936) | Climate Services for Supporting Climate Change Adaptation | 2016 |</v>
       </c>
       <c r="R34" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| WMO-N°1170 | Climate Services for Supporting Climate Change Adaptation | 2016 | https://library.wmo.int/doc_num.php?explnum_id=7936 |</v>
+        <v>| [WMO-N°1170](https://library.wmo.int/doc_num.php?explnum_id=7936) | Climate Services for Supporting Climate Change Adaptation | 2016 | [:bookmark_tabs:](WMO.1170.ClimateServiceForSupportingClimateChangeAdaptation.2016.pdf) |</v>
       </c>
       <c r="S34" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| WMO-N°1170 | Climate Services for Supporting Climate Change Adaptation | 2016 | https://library.wmo.int/doc_num.php?explnum_id=7936 |WMO.1170.ClimateServiceForSupportingClimateChangeAdaptation.2016.pdf |</v>
+        <v>| [WMO-N°1170](https://library.wmo.int/doc_num.php?explnum_id=7936) | Climate Services for Supporting Climate Change Adaptation | 2016 | [:bookmark_tabs:](WMO.1170.ClimateServiceForSupportingClimateChangeAdaptation.2016.pdf) | |</v>
       </c>
       <c r="T34" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| WMO-N°1170 | Climate Services for Supporting Climate Change Adaptation | 2016 | https://library.wmo.int/doc_num.php?explnum_id=7936 |WMO.1170.ClimateServiceForSupportingClimateChangeAdaptation.2016.pdf | | | | | |</v>
+        <v>| [WMO-N°1170](https://library.wmo.int/doc_num.php?explnum_id=7936) | Climate Services for Supporting Climate Change Adaptation | 2016 | [:bookmark_tabs:](WMO.1170.ClimateServiceForSupportingClimateChangeAdaptation.2016.pdf) | | | | | | |</v>
       </c>
       <c r="U34" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| WMO-N°1170 | Climate Services for Supporting Climate Change Adaptation | 2016 | https://library.wmo.int/doc_num.php?explnum_id=7936 |WMO.1170.ClimateServiceForSupportingClimateChangeAdaptation.2016.pdf | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="35" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
+        <v>| [WMO-N°1170](https://library.wmo.int/doc_num.php?explnum_id=7936) | Climate Services for Supporting Climate Change Adaptation | 2016 | [:bookmark_tabs:](WMO.1170.ClimateServiceForSupportingClimateChangeAdaptation.2016.pdf) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="D35" s="4">
         <v>2018</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>106</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F35" s="4"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
@@ -3026,40 +2884,38 @@
       <c r="O35" s="4"/>
       <c r="P35" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| WMO-N°1221 | Guidelines on Quality Management in Climate Services |</v>
+        <v>| [WMO-N°1221](https://library.wmo.int/doc_num.php?explnum_id=5174) | Guidelines on Quality Management in Climate Services |</v>
       </c>
       <c r="Q35" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| WMO-N°1221 | Guidelines on Quality Management in Climate Services | 2018 |</v>
+        <v>| [WMO-N°1221](https://library.wmo.int/doc_num.php?explnum_id=5174) | Guidelines on Quality Management in Climate Services | 2018 |</v>
       </c>
       <c r="R35" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| WMO-N°1221 | Guidelines on Quality Management in Climate Services | 2018 | https://library.wmo.int/doc_num.php?explnum_id=5174 |</v>
+        <v>| [WMO-N°1221](https://library.wmo.int/doc_num.php?explnum_id=5174) | Guidelines on Quality Management in Climate Services | 2018 | [:bookmark_tabs:](WMO.1221.GuidelinesQualityManagementClimateServices.2018.pdf) |</v>
       </c>
       <c r="S35" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| WMO-N°1221 | Guidelines on Quality Management in Climate Services | 2018 | https://library.wmo.int/doc_num.php?explnum_id=5174 |WMO.1221.GuidelinesQualityManagementClimateServices.2018.pdf |</v>
+        <v>| [WMO-N°1221](https://library.wmo.int/doc_num.php?explnum_id=5174) | Guidelines on Quality Management in Climate Services | 2018 | [:bookmark_tabs:](WMO.1221.GuidelinesQualityManagementClimateServices.2018.pdf) | |</v>
       </c>
       <c r="T35" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| WMO-N°1221 | Guidelines on Quality Management in Climate Services | 2018 | https://library.wmo.int/doc_num.php?explnum_id=5174 |WMO.1221.GuidelinesQualityManagementClimateServices.2018.pdf | | | | | |</v>
+        <v>| [WMO-N°1221](https://library.wmo.int/doc_num.php?explnum_id=5174) | Guidelines on Quality Management in Climate Services | 2018 | [:bookmark_tabs:](WMO.1221.GuidelinesQualityManagementClimateServices.2018.pdf) | | | | | | |</v>
       </c>
       <c r="U35" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| WMO-N°1221 | Guidelines on Quality Management in Climate Services | 2018 | https://library.wmo.int/doc_num.php?explnum_id=5174 |WMO.1221.GuidelinesQualityManagementClimateServices.2018.pdf | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="36" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+        <v>| [WMO-N°1221](https://library.wmo.int/doc_num.php?explnum_id=5174) | Guidelines on Quality Management in Climate Services | 2018 | [:bookmark_tabs:](WMO.1221.GuidelinesQualityManagementClimateServices.2018.pdf) | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="36" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" s="4" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>127</v>
+        <v>43</v>
       </c>
       <c r="D36" s="4"/>
-      <c r="E36" s="4" t="s">
-        <v>107</v>
-      </c>
+      <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
@@ -3072,42 +2928,40 @@
       <c r="O36" s="4"/>
       <c r="P36" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| WMO | Normas asociadas a metodologías para actividades hidrometeorológicas |</v>
+        <v>| [WMO](https://public.wmo.int/) | Normas asociadas a metodologías para actividades hidrometeorológicas |</v>
       </c>
       <c r="Q36" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| WMO | Normas asociadas a metodologías para actividades hidrometeorológicas |  |</v>
+        <v>| [WMO](https://public.wmo.int/) | Normas asociadas a metodologías para actividades hidrometeorológicas |  |</v>
       </c>
       <c r="R36" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| WMO | Normas asociadas a metodologías para actividades hidrometeorológicas |  | https://public.wmo.int/ |</v>
+        <v>| [WMO](https://public.wmo.int/) | Normas asociadas a metodologías para actividades hidrometeorológicas |  |  |</v>
       </c>
       <c r="S36" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| WMO | Normas asociadas a metodologías para actividades hidrometeorológicas |  | https://public.wmo.int/ | |</v>
+        <v>| [WMO](https://public.wmo.int/) | Normas asociadas a metodologías para actividades hidrometeorológicas |  |  | |</v>
       </c>
       <c r="T36" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| WMO | Normas asociadas a metodologías para actividades hidrometeorológicas |  | https://public.wmo.int/ | | | | | | |</v>
+        <v>| [WMO](https://public.wmo.int/) | Normas asociadas a metodologías para actividades hidrometeorológicas |  |  | | | | | | |</v>
       </c>
       <c r="U36" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| WMO | Normas asociadas a metodologías para actividades hidrometeorológicas |  | https://public.wmo.int/ | | | | | | | | | |</v>
+        <v>| [WMO](https://public.wmo.int/) | Normas asociadas a metodologías para actividades hidrometeorológicas |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="37" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>129</v>
+        <v>44</v>
       </c>
       <c r="D37" s="4">
         <v>2014</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>109</v>
-      </c>
+      <c r="E37" s="10"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
@@ -3120,42 +2974,40 @@
       <c r="O37" s="4"/>
       <c r="P37" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| ISO-19115 | Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB |</v>
+        <v>| [ISO-19115](https://www.iso.org/standard/26020.html) | Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB |</v>
       </c>
       <c r="Q37" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| ISO-19115 | Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB | 2014 |</v>
+        <v>| [ISO-19115](https://www.iso.org/standard/26020.html) | Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB | 2014 |</v>
       </c>
       <c r="R37" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| ISO-19115 | Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB | 2014 | https://www.iso.org/standard/26020.html |</v>
+        <v>| [ISO-19115](https://www.iso.org/standard/26020.html) | Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB | 2014 |  |</v>
       </c>
       <c r="S37" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| ISO-19115 | Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB | 2014 | https://www.iso.org/standard/26020.html | |</v>
+        <v>| [ISO-19115](https://www.iso.org/standard/26020.html) | Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB | 2014 |  | |</v>
       </c>
       <c r="T37" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| ISO-19115 | Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB | 2014 | https://www.iso.org/standard/26020.html | | | | | | |</v>
+        <v>| [ISO-19115](https://www.iso.org/standard/26020.html) | Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB | 2014 |  | | | | | | |</v>
       </c>
       <c r="U37" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| ISO-19115 | Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB | 2014 | https://www.iso.org/standard/26020.html | | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="38" spans="2:21" ht="92.25" x14ac:dyDescent="0.55000000000000004">
+        <v>| [ISO-19115](https://www.iso.org/standard/26020.html) | Metadatos para Información Geográfica, ISO - International Organization for Standardization. Descrito en la NS-030 de la EAAB | 2014 |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="38" spans="2:21" ht="46.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>130</v>
+        <v>45</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>112</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="E38" s="5"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -3168,34 +3020,36 @@
       <c r="O38" s="4"/>
       <c r="P38" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| ISO-IEC-11179 Partes 1 a 7 | Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos. |</v>
+        <v>| [ISO-IEC-11179 Partes 1 a 7](https://www.iso.org/standard/61932.html
+) | Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos |</v>
       </c>
       <c r="Q38" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>| ISO-IEC-11179 Partes 1 a 7 | Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos. | Varias |</v>
+        <v>| [ISO-IEC-11179 Partes 1 a 7](https://www.iso.org/standard/61932.html
+) | Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos | Varias |</v>
       </c>
       <c r="R38" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| ISO-IEC-11179 Partes 1 a 7 | Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos. | Varias | https://www.iso.org/standard/61932.html
- |</v>
+        <v>| [ISO-IEC-11179 Partes 1 a 7](https://www.iso.org/standard/61932.html
+) | Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos | Varias |  |</v>
       </c>
       <c r="S38" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| ISO-IEC-11179 Partes 1 a 7 | Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos. | Varias | https://www.iso.org/standard/61932.html
- | |</v>
+        <v>| [ISO-IEC-11179 Partes 1 a 7](https://www.iso.org/standard/61932.html
+) | Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos | Varias |  | |</v>
       </c>
       <c r="T38" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| ISO-IEC-11179 Partes 1 a 7 | Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos. | Varias | https://www.iso.org/standard/61932.html
- | | | | | | |</v>
+        <v>| [ISO-IEC-11179 Partes 1 a 7](https://www.iso.org/standard/61932.html
+) | Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos | Varias |  | | | | | | |</v>
       </c>
       <c r="U38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| ISO-IEC-11179 Partes 1 a 7 | Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos. | Varias | https://www.iso.org/standard/61932.html
- | | | | | | | | | |</v>
-      </c>
-    </row>
-    <row r="39" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+        <v>| [ISO-IEC-11179 Partes 1 a 7](https://www.iso.org/standard/61932.html
+) | Tecnologías de la Información - Medatatos en sistemas de información: Framework, Classification, Registry metamodel and basic attributes, Formulation of data definitions, Naming and Identification Principle, Registration. ISO - International Organization for Standardization. Aplicable para diccionarios de datos | Varias |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -3235,7 +3089,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="40" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -3275,7 +3129,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="41" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -3315,7 +3169,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="42" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -3355,7 +3209,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="43" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -3395,7 +3249,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="44" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -3435,7 +3289,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="45" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -3475,7 +3329,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="46" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
@@ -3515,7 +3369,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="47" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
@@ -3555,7 +3409,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="48" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
@@ -3595,7 +3449,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="49" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
@@ -3635,7 +3489,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="50" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -3675,7 +3529,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="51" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -3715,7 +3569,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="52" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
@@ -3755,7 +3609,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="53" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
@@ -3795,7 +3649,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="54" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
@@ -3835,7 +3689,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="55" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
@@ -3875,7 +3729,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="56" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
@@ -3915,7 +3769,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="57" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
@@ -3955,7 +3809,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="58" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
@@ -3995,7 +3849,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="59" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
@@ -4035,7 +3889,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="60" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
@@ -4075,7 +3929,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="61" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
@@ -4115,7 +3969,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="62" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
@@ -4155,7 +4009,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="63" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
@@ -4195,7 +4049,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="64" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
@@ -4235,7 +4089,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="65" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
@@ -4275,7 +4129,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="66" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
@@ -4315,7 +4169,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="67" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
@@ -4355,7 +4209,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="68" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
@@ -4395,7 +4249,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="69" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
@@ -4435,7 +4289,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="70" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
@@ -4475,7 +4329,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="71" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
@@ -4515,7 +4369,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="72" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
@@ -4555,7 +4409,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="73" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
@@ -4595,7 +4449,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="74" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
@@ -4635,7 +4489,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="75" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -4675,7 +4529,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="76" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -4715,7 +4569,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="77" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
@@ -4755,7 +4609,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="78" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
@@ -4795,7 +4649,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="79" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
@@ -4835,7 +4689,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="80" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
@@ -4875,7 +4729,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="81" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
@@ -4915,7 +4769,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="82" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
@@ -4955,7 +4809,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="83" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
@@ -4995,7 +4849,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="84" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
@@ -5035,7 +4889,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="85" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
@@ -5075,7 +4929,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="86" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
@@ -5115,7 +4969,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="87" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
@@ -5155,7 +5009,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="88" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
@@ -5195,7 +5049,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="89" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
@@ -5235,7 +5089,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="90" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -5275,7 +5129,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="91" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -5315,7 +5169,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="92" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -5355,7 +5209,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="93" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
@@ -5395,7 +5249,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="94" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
@@ -5435,7 +5289,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="95" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
@@ -5475,7 +5329,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="96" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
@@ -5515,7 +5369,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="97" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
@@ -5555,7 +5409,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="98" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
@@ -5595,7 +5449,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="99" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
@@ -5635,7 +5489,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="100" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
@@ -5675,7 +5529,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="101" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
@@ -5715,7 +5569,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="102" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
@@ -5755,7 +5609,7 @@
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="103" spans="2:21" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
